--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>64151.60546875</v>
+      </c>
+      <c r="G2" t="n">
+        <v>64504.55859375</v>
+      </c>
+      <c r="H2" t="n">
+        <v>352.953125</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5471754751829252</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6639377354114765</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-19 18:09:31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>64377.1953125</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>64237.812500,64233.898438,64235.843750,64243.542969,64218.066406,64213.648438,64203.390625,64216.187500,64202.707031,64175.757812,64153.378906,64159.179688,64143.750000,64129.570312,64149.171875,64157.855469,64152.492188,64132.039062,64136.191406,64139.171875,64162.992188,64153.722656,64145.734375,64151.605469</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>64468.238281,64515.480469,64654.578125,64692.011719,64764.320312,64793.761719,64732.941406,64725.000000,64784.089844,64670.121094,64681.468750,64682.210938,64668.089844,64678.000000,64668.449219,64470.320312,64553.648438,64426.699219,64398.000000,64432.671875,64547.199219,64540.031250,64495.078125,64504.558594</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>230.425781,281.582031,418.734375,448.468750,546.253907,580.113281,529.550781,508.812500,581.382813,494.363282,528.089844,523.031250,524.339844,548.429688,519.277344,312.464843,401.156250,294.660157,261.808594,293.500000,384.207031,386.308594,349.343750,352.953125</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.357425,0.436457,0.647648,0.693237,0.843449,0.895323,0.818055,0.786114,0.897416,0.764438,0.816447,0.808617,0.810817,0.847939,0.802984,0.484665,0.621431,0.457357,0.406548,0.455514,0.595234,0.598557,0.541660,0.547175</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6639377354114765</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>64175.054688,64222.277344,64212.648438,64201.207031,64169.703125,64181.406250,64132.976562,64154.878906,64103.027344,64140.699219,64055.023438,64051.117188,64026.972656,64041.714844,64045.125000,64091.968750,64023.328125,64025.625000,64012.140625,64015.937500,64012.468750,64040.507812,64045.968750,64015.785156</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>64112.683594,64055.820312,64016.390625,63994.914062,63923.203125,63896.550781,63855.750000,63860.433594,63822.328125,63776.988281,63722.328125,63702.269531,63662.898438,63631.468750,63624.023438,63621.304688,63574.171875,63531.195312,63505.703125,63505.453125,63520.035156,63469.636719,63464.015625,63448.343750</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-19 18:09:31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>64420.777344,64420.535156,64412.777344,64427.851562,64421.523438,64427.371094,64428.804688,64429.843750,64432.250000,64413.683594,64400.339844,64410.023438,64396.777344,64400.421875,64397.546875,64392.957031,64387.546875,64391.507812,64399.628906,64397.726562,64400.875000,64386.023438,64381.562500,64377.195312</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>64378.656250,64410.808594,64384.367188,64403.648438,64395.648438,64386.535156,64431.585938,64425.710938,64357.453125,64366.750000,64317.789062,64314.070312,64294.742188,64306.320312,64320.468750,64353.750000,64337.589844,64341.031250,64297.750000,64301.132812,64322.890625,64300.484375,64283.488281,64237.984375</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>64223.500000,64181.183594,64114.148438,64093.343750,64032.187500,63972.847656,63929.414062,63878.359375,63823.335938,63771.281250,63723.160156,63691.273438,63649.210938,63629.718750,63584.644531,63546.000000,63501.460938,63489.417969,63414.761719,63379.570312,63355.500000,63344.742188,63302.765625,63267.578125</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>64314.968750,64282.226562,64241.500000,64238.304688,64187.390625,64171.882812,64142.523438,64120.132812,64090.992188,64047.250000,64008.972656,64017.773438,63981.644531,63965.328125,63950.984375,63940.632812,63891.726562,63891.250000,63863.742188,63850.386719,63833.960938,63790.937500,63775.234375,63765.898438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>64635.0234375</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65422.140625</v>
+      </c>
+      <c r="H2" t="n">
+        <v>787.1171875</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.203135788557821</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8860382810603645</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>65198.55859375</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>64800.281250,64800.203125,64779.367188,64792.257812,64794.046875,64786.816406,64793.960938,64788.718750,64785.757812,64763.226562,64755.148438,64765.808594,64746.812500,64742.742188,64743.148438,64725.484375,64719.593750,64720.914062,64704.414062,64696.187500,64687.601562,64664.625000,64646.527344,64635.023438</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>64493.660156,64072.468750,63859.031250,64214.238281,63997.351562,64138.718750,64242.351562,64944.011719,64585.988281,64274.640625,64346.628906,65551.007812,65454.011719,65533.519531,65192.320312,65085.019531,65327.988281,65241.691406,65105.441406,65213.050781,65522.308594,65193.531250,65366.949219,65422.140625</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>306.621094,727.734375,920.335938,578.019531,796.695312,648.097656,551.609375,155.292969,199.769531,488.585937,408.519532,785.199218,707.199219,790.777343,449.171875,359.535156,608.394531,520.777344,401.027344,516.863281,834.707032,528.906250,720.421875,787.117187</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.475428,1.135799,1.441199,0.900142,1.244888,1.010462,0.858638,0.239118,0.309308,0.760154,0.634873,1.197845,1.080452,1.206676,0.688995,0.552408,0.931292,0.798228,0.615966,0.792576,1.273928,0.811286,1.102119,1.203136</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8860382810603645</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>64804.351562,64791.648438,64756.558594,64777.296875,64765.066406,64744.273438,64774.382812,64778.953125,64732.890625,64731.867188,64656.250000,64656.140625,64641.960938,64672.421875,64660.023438,64657.175781,64630.984375,64602.054688,64592.886719,64566.902344,64564.703125,64567.609375,64483.105469,64464.261719</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>64714.066406,64679.734375,64628.890625,64625.210938,64582.835938,64558.304688,64536.281250,64505.062500,64470.984375,64425.871094,64387.609375,64387.406250,64352.976562,64309.445312,64310.882812,64281.964844,64237.164062,64225.238281,64165.945312,64138.070312,64106.875000,64047.035156,64012.707031,63991.207031</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>65401.429688,65363.785156,65343.812500,65333.695312,65323.593750,65310.921875,65324.203125,65319.328125,65332.039062,65310.851562,65323.742188,65328.589844,65308.500000,65303.632812,65317.738281,65300.921875,65292.378906,65276.402344,65268.843750,65260.476562,65232.421875,65217.820312,65211.781250,65198.558594</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>65386.128906,65327.519531,65294.578125,65292.742188,65237.699219,65241.070312,65238.421875,65234.945312,65205.328125,65267.101562,65199.062500,65179.683594,65134.914062,65170.015625,65152.710938,65188.562500,65170.898438,65096.972656,65113.359375,65072.191406,65072.789062,65104.644531,64997.089844,65029.453125</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>65024.542969,64908.769531,64796.343750,64728.945312,64659.218750,64579.054688,64550.000000,64489.750000,64451.718750,64383.632812,64362.113281,64306.960938,64272.933594,64213.273438,64209.972656,64146.156250,64119.109375,64084.234375,64001.812500,63962.734375,63894.097656,63862.527344,63819.714844,63785.523438</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>65175.089844,65077.371094,65009.375000,64980.722656,64904.191406,64877.460938,64863.578125,64829.226562,64822.687500,64766.082031,64744.265625,64739.945312,64699.746094,64655.210938,64675.351562,64639.164062,64595.414062,64574.078125,64525.281250,64514.714844,64455.734375,64399.601562,64389.160156,64356.007812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,44 @@
       </c>
       <c r="F3" t="n">
         <v>65198.55859375</v>
+      </c>
+      <c r="G3" t="n">
+        <v>66269.9609375</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1071.40234375</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.616723970548968</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.498600226790953</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>66008.59375</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +740,24 @@
           <t>65401.429688,65363.785156,65343.812500,65333.695312,65323.593750,65310.921875,65324.203125,65319.328125,65332.039062,65310.851562,65323.742188,65328.589844,65308.500000,65303.632812,65317.738281,65300.921875,65292.378906,65276.402344,65268.843750,65260.476562,65232.421875,65217.820312,65211.781250,65198.558594</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>65472.011719,65704.101562,65874.679688,66143.031250,66186.390625,66250.781250,66148.210938,66309.468750,66508.851562,66742.921875,66809.718750,66648.398438,66512.632812,66170.421875,66282.007812,66415.437500,66370.007812,66346.906250,66268.007812,66405.007812,66586.687500,66389.179688,66268.007812,66269.960938</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>70.582031,340.316407,530.867188,809.335938,862.796875,939.859375,824.007812,990.140625,1176.812500,1432.070313,1485.976562,1319.808593,1204.132812,866.789063,964.269532,1114.515625,1077.628907,1070.503906,999.164062,1144.531250,1354.265625,1171.359375,1056.226562,1071.402343</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.107805,0.517953,0.805874,1.223615,1.303587,1.418639,1.245699,1.493212,1.769407,2.145651,2.224192,1.980256,1.810382,1.309934,1.454798,1.678097,1.623668,1.613495,1.507762,1.723562,2.033838,1.764383,1.593871,1.616724</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.498600226790953</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>65386.128906,65327.519531,65294.578125,65292.742188,65237.699219,65241.070312,65238.421875,65234.945312,65205.328125,65267.101562,65199.062500,65179.683594,65134.914062,65170.015625,65152.710938,65188.562500,65170.898438,65096.972656,65113.359375,65072.191406,65072.789062,65104.644531,64997.089844,65029.453125</t>
@@ -715,6 +771,49 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>65175.089844,65077.371094,65009.375000,64980.722656,64904.191406,64877.460938,64863.578125,64829.226562,64822.687500,64766.082031,64744.265625,64739.945312,64699.746094,64655.210938,64675.351562,64639.164062,64595.414062,64574.078125,64525.281250,64514.714844,64455.734375,64399.601562,64389.160156,64356.007812</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>66262.890625,66246.226562,66237.500000,66246.601562,66225.257812,66227.937500,66233.343750,66211.859375,66231.953125,66195.093750,66192.570312,66200.093750,66172.140625,66136.343750,66140.578125,66142.515625,66130.945312,66107.203125,66084.296875,66066.406250,66045.390625,66023.648438,66027.531250,66008.593750</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>66196.796875,66195.250000,66182.578125,66178.539062,66115.015625,66083.453125,66111.132812,66138.390625,66079.398438,66078.859375,66004.851562,66031.804688,65969.937500,65924.015625,65914.429688,65994.507812,65948.062500,65836.968750,65807.929688,65835.984375,65839.078125,65809.078125,65722.796875,65711.570312</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>65975.500000,65894.664062,65781.992188,65719.234375,65619.992188,65556.578125,65501.300781,65425.523438,65414.718750,65295.750000,65214.648438,65135.109375,65091.500000,64966.476562,64898.359375,64865.000000,64809.820312,64759.421875,64587.718750,64523.570312,64469.101562,64403.890625,64374.320312,64339.285156</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>66113.718750,66042.007812,65976.164062,65959.812500,65879.546875,65851.070312,65834.742188,65783.765625,65797.468750,65713.562500,65659.015625,65629.382812,65559.414062,65465.625000,65425.632812,65441.468750,65385.976562,65333.023438,65247.984375,65215.281250,65168.484375,65069.570312,65084.316406,65037.460938</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,44 @@
       </c>
       <c r="F4" t="n">
         <v>66008.59375</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65628.546875</v>
+      </c>
+      <c r="H4" t="n">
+        <v>380.046875</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5790877493049781</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3648229845180515</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>65498.0703125</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +839,24 @@
           <t>66262.890625,66246.226562,66237.500000,66246.601562,66225.257812,66227.937500,66233.343750,66211.859375,66231.953125,66195.093750,66192.570312,66200.093750,66172.140625,66136.343750,66140.578125,66142.515625,66130.945312,66107.203125,66084.296875,66066.406250,66045.390625,66023.648438,66027.531250,66008.593750</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>66336.000000,65937.328125,65891.273438,65795.273438,65940.476562,65884.273438,66008.992188,65972.500000,65587.757812,65914.742188,65760.953125,66020.039062,66208.523438,66001.640625,65858.296875,65900.992188,65892.421875,66040.257812,66014.382812,66086.609375,66033.593750,65799.007812,65777.226562,65628.546875</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>73.109375,308.898437,346.226562,451.328124,284.781249,343.664062,224.351562,239.359375,644.195312,280.351562,431.617187,180.054688,36.382812,134.703125,282.281250,241.523438,238.523437,66.945312,69.914062,20.203125,11.796875,224.640626,250.304688,380.046875</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.110211,0.468473,0.525451,0.685958,0.431876,0.521618,0.339880,0.362817,0.982188,0.425325,0.656343,0.272727,0.054952,0.204091,0.428619,0.366494,0.361989,0.101370,0.105907,0.030571,0.017865,0.341404,0.380534,0.579088</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3648229845180515</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>66196.796875,66195.250000,66182.578125,66178.539062,66115.015625,66083.453125,66111.132812,66138.390625,66079.398438,66078.859375,66004.851562,66031.804688,65969.937500,65924.015625,65914.429688,65994.507812,65948.062500,65836.968750,65807.929688,65835.984375,65839.078125,65809.078125,65722.796875,65711.570312</t>
@@ -814,6 +870,49 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>66113.718750,66042.007812,65976.164062,65959.812500,65879.546875,65851.070312,65834.742188,65783.765625,65797.468750,65713.562500,65659.015625,65629.382812,65559.414062,65465.625000,65425.632812,65441.468750,65385.976562,65333.023438,65247.984375,65215.281250,65168.484375,65069.570312,65084.316406,65037.460938</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>65607.125000,65584.562500,65575.218750,65568.312500,65565.312500,65575.648438,65573.171875,65568.062500,65579.226562,65585.007812,65577.718750,65589.359375,65586.929688,65575.289062,65587.968750,65586.484375,65593.085938,65582.023438,65556.664062,65560.789062,65523.039062,65522.578125,65515.480469,65498.070312</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>65544.109375,65560.695312,65548.226562,65499.351562,65481.132812,65504.789062,65493.578125,65505.390625,65456.433594,65531.640625,65469.535156,65464.097656,65470.664062,65451.421875,65481.968750,65491.914062,65482.046875,65441.695312,65402.246094,65437.507812,65432.546875,65379.925781,65356.785156,65340.425781</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>65349.648438,65258.714844,65154.179688,65091.445312,65011.085938,64962.101562,64891.148438,64844.394531,64813.265625,64766.179688,64701.851562,64689.312500,64673.789062,64596.207031,64564.171875,64513.500000,64499.960938,64472.265625,64313.921875,64291.429688,64234.984375,64241.863281,64201.335938,64159.250000</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>65472.792969,65388.171875,65318.953125,65286.386719,65236.773438,65207.695312,65168.953125,65134.035156,65122.847656,65097.960938,65065.714844,65064.539062,65029.046875,64988.257812,64971.398438,64963.535156,64941.117188,64910.042969,64845.464844,64833.578125,64786.445312,64732.593750,64748.953125,64713.187500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,44 @@
       </c>
       <c r="F5" t="n">
         <v>65498.0703125</v>
+      </c>
+      <c r="G5" t="n">
+        <v>65292.44921875</v>
+      </c>
+      <c r="H5" t="n">
+        <v>205.62109375</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3149232357038796</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6669710688997356</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="n">
+        <v>65176.5234375</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +938,24 @@
           <t>65607.125000,65584.562500,65575.218750,65568.312500,65565.312500,65575.648438,65573.171875,65568.062500,65579.226562,65585.007812,65577.718750,65589.359375,65586.929688,65575.289062,65587.968750,65586.484375,65593.085938,65582.023438,65556.664062,65560.789062,65523.039062,65522.578125,65515.480469,65498.070312</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>65570.539062,65660.203125,65758.109375,65394.808594,65619.226562,65607.070312,65708.562500,65525.218750,65132.140625,64836.000000,64868.199219,64898.250000,64691.011719,64619.121094,64807.578125,64778.218750,65095.281250,65120.191406,65142.511719,65051.230469,64925.851562,65030.000000,65066.980469,65292.449219</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>36.585938,75.640625,182.890625,173.503906,53.914062,31.421874,135.390625,42.843750,447.085937,749.007812,709.519531,691.109375,895.917969,956.167968,780.390625,808.265625,497.804688,461.832032,414.152343,509.558593,597.187500,492.578125,448.500000,205.621093</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.055796,0.115200,0.278126,0.265318,0.082162,0.047894,0.206047,0.065385,0.686429,1.155234,1.093786,1.064912,1.384919,1.479698,1.204166,1.247743,0.764732,0.709199,0.635764,0.783319,0.919799,0.757463,0.689290,0.314923</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6669710688997356</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>65544.109375,65560.695312,65548.226562,65499.351562,65481.132812,65504.789062,65493.578125,65505.390625,65456.433594,65531.640625,65469.535156,65464.097656,65470.664062,65451.421875,65481.968750,65491.914062,65482.046875,65441.695312,65402.246094,65437.507812,65432.546875,65379.925781,65356.785156,65340.425781</t>
@@ -913,6 +969,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>65472.792969,65388.171875,65318.953125,65286.386719,65236.773438,65207.695312,65168.953125,65134.035156,65122.847656,65097.960938,65065.714844,65064.539062,65029.046875,64988.257812,64971.398438,64963.535156,64941.117188,64910.042969,64845.464844,64833.578125,64786.445312,64732.593750,64748.953125,64713.187500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>65242.843750,65221.617188,65213.945312,65221.894531,65222.503906,65238.382812,65226.476562,65195.625000,65187.187500,65187.179688,65184.152344,65195.546875,65203.800781,65195.023438,65207.929688,65183.750000,65200.949219,65201.734375,65175.937500,65228.039062,65180.160156,65186.265625,65180.820312,65176.523438</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>65227.195312,65224.710938,65181.234375,65178.085938,65196.960938,65216.894531,65173.554688,65132.355469,65110.894531,65165.695312,65086.343750,65069.460938,65129.406250,65145.445312,65147.914062,65103.148438,65112.550781,65104.757812,65106.253906,65104.304688,65093.125000,65031.593750,65101.917969,65093.648438</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>64931.109375,64822.507812,64731.414062,64677.746094,64612.437500,64573.335938,64505.109375,64432.507812,64394.820312,64357.812500,64319.273438,64282.402344,64272.921875,64206.554688,64208.527344,64143.042969,64140.625000,64095.960938,63967.007812,64003.718750,63934.378906,63927.609375,63877.507812,63845.117188</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>65063.500000,64975.175781,64911.617188,64897.671875,64840.539062,64818.851562,64774.253906,64722.343750,64700.433594,64672.164062,64651.636719,64650.484375,64629.671875,64575.242188,64596.406250,64547.851562,64552.902344,64507.671875,64461.382812,64494.695312,64443.800781,64404.910156,64400.804688,64374.187500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,44 @@
       </c>
       <c r="F6" t="n">
         <v>65176.5234375</v>
+      </c>
+      <c r="G6" t="n">
+        <v>64017.01953125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1159.50390625</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.811243189295913</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.215303712308126</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>63956.51953125</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +1037,24 @@
           <t>65242.843750,65221.617188,65213.945312,65221.894531,65222.503906,65238.382812,65226.476562,65195.625000,65187.187500,65187.179688,65184.152344,65195.546875,65203.800781,65195.023438,65207.929688,65183.750000,65200.949219,65201.734375,65175.937500,65228.039062,65180.160156,65186.265625,65180.820312,65176.523438</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>65240.968750,65268.421875,65426.941406,65453.988281,65259.019531,65064.289062,64903.089844,65027.648438,64715.980469,64063.070312,63990.910156,64031.101562,63889.839844,64117.050781,64210.898438,64158.339844,64102.601562,64088.089844,64100.519531,64083.320312,64009.011719,64005.011719,63980.570312,64017.019531</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.875000,46.804687,212.996094,232.093750,36.515625,174.093750,323.386718,167.976562,471.207031,1124.109375,1193.242188,1164.445312,1313.960937,1077.972657,997.031250,1025.410156,1098.347657,1113.644531,1075.417969,1144.718750,1171.148437,1181.253906,1200.250000,1159.503907</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.002874,0.071711,0.325548,0.354591,0.055955,0.267572,0.498261,0.258316,0.728115,1.754692,1.864706,1.818562,2.056604,1.681257,1.552745,1.598249,1.713421,1.737678,1.677706,1.786298,1.829662,1.845565,1.875960,1.811243</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.215303712308126</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>65227.195312,65224.710938,65181.234375,65178.085938,65196.960938,65216.894531,65173.554688,65132.355469,65110.894531,65165.695312,65086.343750,65069.460938,65129.406250,65145.445312,65147.914062,65103.148438,65112.550781,65104.757812,65106.253906,65104.304688,65093.125000,65031.593750,65101.917969,65093.648438</t>
@@ -1012,6 +1068,49 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>65063.500000,64975.175781,64911.617188,64897.671875,64840.539062,64818.851562,64774.253906,64722.343750,64700.433594,64672.164062,64651.636719,64650.484375,64629.671875,64575.242188,64596.406250,64547.851562,64552.902344,64507.671875,64461.382812,64494.695312,64443.800781,64404.910156,64400.804688,64374.187500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>64010.507812,64007.781250,64011.203125,64005.546875,64022.546875,64017.300781,64011.167969,64001.468750,63988.351562,63972.535156,63959.992188,63969.464844,63969.207031,63968.671875,63981.820312,63985.898438,63996.000000,63986.597656,63993.746094,64018.421875,63986.300781,63977.328125,63957.359375,63956.519531</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>64026.160156,64056.164062,63973.265625,63990.718750,64037.570312,64056.382812,64004.277344,63978.527344,64022.195312,63992.335938,63951.812500,63981.359375,63980.781250,63998.703125,64013.250000,63937.464844,64005.558594,64050.371094,64022.894531,63991.527344,63990.367188,63900.210938,63974.566406,63938.281250</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>63783.949219,63706.273438,63610.835938,63548.898438,63486.414062,63401.765625,63342.078125,63274.265625,63189.695312,63110.117188,63049.683594,63014.062500,62971.023438,62917.410156,62918.562500,62868.703125,62865.460938,62810.351562,62724.843750,62769.250000,62694.867188,62676.070312,62637.250000,62597.382812</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>63892.687500,63829.210938,63766.250000,63725.132812,63685.605469,63639.117188,63600.738281,63544.628906,63514.335938,63449.453125,63385.382812,63384.476562,63355.328125,63313.484375,63348.367188,63320.472656,63306.359375,63228.699219,63238.843750,63267.945312,63218.218750,63155.734375,63172.804688,63148.429688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,44 @@
       </c>
       <c r="F7" t="n">
         <v>63956.51953125</v>
+      </c>
+      <c r="G7" t="n">
+        <v>64507.12890625</v>
+      </c>
+      <c r="H7" t="n">
+        <v>550.609375</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8535636050400195</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3529095985360836</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:41:57</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>64600.8984375</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1136,24 @@
           <t>64010.507812,64007.781250,64011.203125,64005.546875,64022.546875,64017.300781,64011.167969,64001.468750,63988.351562,63972.535156,63959.992188,63969.464844,63969.207031,63968.671875,63981.820312,63985.898438,63996.000000,63986.597656,63993.746094,64018.421875,63986.300781,63977.328125,63957.359375,63956.519531</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>64117.191406,63959.488281,63952.210938,63951.750000,63808.550781,63939.371094,64000.078125,64005.738281,64055.980469,64103.890625,64149.070312,64117.691406,64151.308594,64203.289062,64353.789062,64328.718750,64275.050781,64288.011719,64352.269531,64339.281250,64450.000000,64402.820312,64460.898438,64507.128906</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>106.683594,48.292969,58.992188,53.796875,213.996094,77.929687,11.089844,4.269531,67.628907,131.355469,189.078125,148.226562,182.101563,234.617188,371.968750,342.820312,279.050781,301.414063,358.523437,320.859375,463.699219,425.492188,503.539062,550.609375</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.166388,0.075506,0.092244,0.084121,0.335372,0.121881,0.017328,0.006671,0.105578,0.204910,0.294748,0.231179,0.283863,0.365429,0.578006,0.532920,0.434151,0.468850,0.557126,0.498699,0.719471,0.660673,0.781154,0.853564</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3529095985360836</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>64026.160156,64056.164062,63973.265625,63990.718750,64037.570312,64056.382812,64004.277344,63978.527344,64022.195312,63992.335938,63951.812500,63981.359375,63980.781250,63998.703125,64013.250000,63937.464844,64005.558594,64050.371094,64022.894531,63991.527344,63990.367188,63900.210938,63974.566406,63938.281250</t>
@@ -1111,6 +1167,49 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>63892.687500,63829.210938,63766.250000,63725.132812,63685.605469,63639.117188,63600.738281,63544.628906,63514.335938,63449.453125,63385.382812,63384.476562,63355.328125,63313.484375,63348.367188,63320.472656,63306.359375,63228.699219,63238.843750,63267.945312,63218.218750,63155.734375,63172.804688,63148.429688</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:41:57</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>64514.023438,64524.617188,64538.882812,64554.421875,64570.164062,64585.156250,64583.925781,64587.160156,64600.421875,64598.218750,64602.609375,64597.117188,64607.648438,64619.398438,64620.578125,64617.640625,64638.093750,64621.070312,64625.261719,64616.531250,64600.960938,64593.460938,64602.933594,64600.898438</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>64526.039062,64504.285156,64530.414062,64528.265625,64591.601562,64570.671875,64543.375000,64572.976562,64566.933594,64575.078125,64529.226562,64558.523438,64603.234375,64612.117188,64600.734375,64582.390625,64584.968750,64595.128906,64577.226562,64554.179688,64550.617188,64515.761719,64553.449219,64539.558594</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>64343.128906,64291.093750,64210.464844,64175.191406,64136.710938,64093.296875,64049.660156,64011.953125,63970.871094,63908.859375,63877.710938,63807.054688,63794.296875,63757.277344,63730.824219,63688.039062,63686.835938,63641.984375,63546.105469,63521.835938,63475.492188,63442.640625,63414.882812,63392.562500</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>64427.281250,64391.914062,64348.789062,64326.328125,64292.101562,64283.156250,64268.738281,64241.460938,64239.062500,64191.449219,64151.359375,64133.226562,64131.527344,64080.429688,64095.957031,64081.957031,64065.824219,64010.242188,63983.828125,63966.296875,63931.859375,63884.914062,63903.058594,63891.238281</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,44 @@
       </c>
       <c r="F8" t="n">
         <v>64600.8984375</v>
+      </c>
+      <c r="G8" t="n">
+        <v>65236.6015625</v>
+      </c>
+      <c r="H8" t="n">
+        <v>635.703125</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9744577580286181</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3620401896339773</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>65185.265625</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1235,24 @@
           <t>64514.023438,64524.617188,64538.882812,64554.421875,64570.164062,64585.156250,64583.925781,64587.160156,64600.421875,64598.218750,64602.609375,64597.117188,64607.648438,64619.398438,64620.578125,64617.640625,64638.093750,64621.070312,64625.261719,64616.531250,64600.960938,64593.460938,64602.933594,64600.898438</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>64465.078125,64352.941406,64375.730469,64309.421875,64423.011719,64481.640625,64454.171875,64450.480469,64405.031250,64466.460938,64658.980469,64710.281250,64674.941406,64644.058594,64686.191406,64641.089844,64595.261719,64791.121094,65347.960938,65336.308594,65069.988281,65141.429688,65115.390625,65236.601562</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>48.945313,171.675782,163.152343,245.000000,147.152343,103.515625,129.753906,136.679687,195.390625,131.757812,56.371094,113.164062,67.292968,24.660156,65.613281,23.449219,42.832031,170.050782,722.699218,719.777344,469.027343,547.968750,512.457031,635.703125</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.075925,0.266772,0.253438,0.380971,0.228416,0.160535,0.201312,0.212069,0.303378,0.204382,0.087182,0.174878,0.104048,0.038148,0.101433,0.036276,0.066308,0.262460,1.105925,1.101650,0.720804,0.841199,0.786998,0.974458</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3620401896339773</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>64526.039062,64504.285156,64530.414062,64528.265625,64591.601562,64570.671875,64543.375000,64572.976562,64566.933594,64575.078125,64529.226562,64558.523438,64603.234375,64612.117188,64600.734375,64582.390625,64584.968750,64595.128906,64577.226562,64554.179688,64550.617188,64515.761719,64553.449219,64539.558594</t>
@@ -1210,6 +1266,49 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>64427.281250,64391.914062,64348.789062,64326.328125,64292.101562,64283.156250,64268.738281,64241.460938,64239.062500,64191.449219,64151.359375,64133.226562,64131.527344,64080.429688,64095.957031,64081.957031,64065.824219,64010.242188,63983.828125,63966.296875,63931.859375,63884.914062,63903.058594,63891.238281</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>65242.773438,65228.406250,65242.445312,65257.484375,65266.847656,65272.625000,65269.914062,65259.722656,65266.992188,65250.152344,65255.644531,65254.218750,65268.601562,65253.261719,65258.437500,65245.429688,65276.031250,65270.679688,65256.156250,65244.546875,65220.515625,65198.308594,65194.000000,65185.265625</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>65194.765625,65194.781250,65237.613281,65238.398438,65252.632812,65218.984375,65239.390625,65244.355469,65171.500000,65240.148438,65182.125000,65179.500000,65188.429688,65196.078125,65221.375000,65233.195312,65205.945312,65172.414062,65146.417969,65183.015625,65138.789062,65135.511719,65093.929688,65081.457031</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>64977.929688,64903.363281,64842.789062,64812.429688,64765.335938,64717.195312,64675.484375,64632.718750,64603.507812,64530.976562,64512.417969,64455.824219,64446.296875,64395.175781,64368.941406,64319.484375,64315.726562,64281.539062,64146.757812,64092.562500,64052.582031,64022.929688,63980.320312,63929.164062</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>65092.328125,65040.914062,64996.023438,64993.914062,64948.070312,64923.179688,64913.015625,64874.328125,64876.593750,64823.195312,64791.074219,64772.414062,64768.957031,64715.500000,64720.484375,64718.117188,64698.531250,64678.308594,64604.156250,64574.593750,64534.617188,64469.007812,64464.757812,64432.710938</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,44 @@
       </c>
       <c r="F9" t="n">
         <v>65185.265625</v>
+      </c>
+      <c r="G9" t="n">
+        <v>63244.33984375</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1940.92578125</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.068931996199511</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.040294871145218</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:35</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>63423.015625</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1334,24 @@
           <t>65242.773438,65228.406250,65242.445312,65257.484375,65266.847656,65272.625000,65269.914062,65259.722656,65266.992188,65250.152344,65255.644531,65254.218750,65268.601562,65253.261719,65258.437500,65245.429688,65276.031250,65270.679688,65256.156250,65244.546875,65220.515625,65198.308594,65194.000000,65185.265625</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>65229.531250,65403.988281,65358.000000,65165.101562,65104.488281,65203.000000,65277.988281,65040.320312,65024.179688,65150.718750,64611.750000,64475.171875,64828.300781,64951.078125,64801.300781,64919.308594,64903.488281,64760.648438,63746.238281,63693.570312,63423.460938,63170.480469,63115.558594,63244.339844</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>13.242188,175.582031,115.554688,92.382812,162.359375,69.625000,8.074219,219.402343,242.812500,99.433594,643.894531,779.046875,440.300781,302.183594,457.136719,326.121094,372.542969,510.031250,1509.917969,1550.976562,1797.054688,2027.828125,2078.441406,1940.925781</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.020301,0.268458,0.176803,0.141767,0.249383,0.106782,0.012369,0.337333,0.373419,0.152621,0.996559,1.208290,0.679180,0.465248,0.705444,0.502348,0.573995,0.787564,2.368639,2.435060,2.833423,3.210088,3.293073,3.068932</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.040294871145218</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>65194.765625,65194.781250,65237.613281,65238.398438,65252.632812,65218.984375,65239.390625,65244.355469,65171.500000,65240.148438,65182.125000,65179.500000,65188.429688,65196.078125,65221.375000,65233.195312,65205.945312,65172.414062,65146.417969,65183.015625,65138.789062,65135.511719,65093.929688,65081.457031</t>
@@ -1309,6 +1365,49 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>65092.328125,65040.914062,64996.023438,64993.914062,64948.070312,64923.179688,64913.015625,64874.328125,64876.593750,64823.195312,64791.074219,64772.414062,64768.957031,64715.500000,64720.484375,64718.117188,64698.531250,64678.308594,64604.156250,64574.593750,64534.617188,64469.007812,64464.757812,64432.710938</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:35</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>63251.148438,63246.269531,63262.066406,63263.890625,63271.503906,63281.003906,63302.250000,63312.468750,63316.921875,63325.375000,63368.796875,63393.199219,63410.191406,63417.980469,63437.343750,63446.000000,63438.882812,63451.289062,63449.109375,63438.699219,63421.773438,63420.500000,63414.363281,63423.015625</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>63240.550781,63287.132812,63281.968750,63309.414062,63307.437500,63336.695312,63354.367188,63322.820312,63391.355469,63376.023438,63383.062500,63458.617188,63434.117188,63445.718750,63463.015625,63469.441406,63491.617188,63445.476562,63458.437500,63468.691406,63439.097656,63385.707031,63375.921875,63424.023438</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>62817.718750,62712.101562,62622.847656,62550.023438,62483.125000,62424.507812,62390.832031,62332.875000,62291.445312,62233.613281,62235.445312,62222.132812,62187.703125,62142.312500,62129.539062,62082.851562,62043.242188,61998.589844,61880.460938,61860.664062,61805.382812,61802.894531,61779.132812,61746.414062</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>62994.042969,62922.128906,62861.070312,62830.296875,62766.835938,62741.250000,62728.726562,62698.937500,62700.218750,62656.199219,62647.425781,62671.406250,62658.953125,62633.031250,62645.140625,62614.367188,62585.203125,62545.179688,62509.960938,62494.125000,62458.335938,62425.882812,62422.261719,62412.812500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,44 @@
       </c>
       <c r="F10" t="n">
         <v>63423.015625</v>
+      </c>
+      <c r="G10" t="n">
+        <v>63831.23828125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>408.22265625</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6395342895453631</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3925273729559332</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:32</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>63897.9765625</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1433,24 @@
           <t>63251.148438,63246.269531,63262.066406,63263.890625,63271.503906,63281.003906,63302.250000,63312.468750,63316.921875,63325.375000,63368.796875,63393.199219,63410.191406,63417.980469,63437.343750,63446.000000,63438.882812,63451.289062,63449.109375,63438.699219,63421.773438,63420.500000,63414.363281,63423.015625</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>63285.460938,63385.519531,63564.289062,63435.800781,63353.511719,63322.281250,63401.109375,63414.078125,63475.121094,63026.070312,63336.050781,63857.589844,63973.398438,63615.921875,63656.578125,63817.558594,63834.480469,63892.890625,63704.941406,63533.089844,63883.000000,63619.078125,63883.011719,63831.238281</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>34.312500,139.250000,302.222657,171.910156,82.007813,41.277344,98.859375,101.609375,158.199219,299.304688,32.746094,464.390625,563.207032,197.941406,219.234375,371.558594,395.597657,441.601563,255.832031,94.390625,461.226562,198.578125,468.648438,408.222656</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.054219,0.219687,0.475460,0.270999,0.129445,0.065186,0.155927,0.160232,0.249230,0.474890,0.051702,0.727229,0.880377,0.311151,0.344402,0.582220,0.619724,0.691159,0.401589,0.148569,0.721986,0.312136,0.733604,0.639534</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3925273729559332</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>63240.550781,63287.132812,63281.968750,63309.414062,63307.437500,63336.695312,63354.367188,63322.820312,63391.355469,63376.023438,63383.062500,63458.617188,63434.117188,63445.718750,63463.015625,63469.441406,63491.617188,63445.476562,63458.437500,63468.691406,63439.097656,63385.707031,63375.921875,63424.023438</t>
@@ -1408,6 +1464,49 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>62994.042969,62922.128906,62861.070312,62830.296875,62766.835938,62741.250000,62728.726562,62698.937500,62700.218750,62656.199219,62647.425781,62671.406250,62658.953125,62633.031250,62645.140625,62614.367188,62585.203125,62545.179688,62509.960938,62494.125000,62458.335938,62425.882812,62422.261719,62412.812500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:32</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>63838.675781,63846.726562,63863.460938,63857.562500,63878.863281,63868.500000,63858.835938,63869.734375,63868.203125,63862.574219,63883.613281,63872.757812,63915.679688,63928.664062,63936.335938,63942.136719,63942.664062,63936.804688,63928.195312,63935.976562,63923.062500,63911.789062,63908.550781,63897.976562</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>63847.257812,63846.417969,63887.164062,63848.937500,63869.492188,63869.984375,63866.500000,63842.484375,63860.007812,63848.335938,63844.671875,63846.914062,63869.789062,63903.007812,63932.718750,63909.054688,63907.968750,63900.171875,63901.011719,63879.351562,63877.882812,63821.421875,63876.628906,63831.000000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>63492.718750,63421.257812,63334.593750,63265.929688,63239.433594,63173.031250,63117.046875,63054.218750,63023.558594,62969.804688,62963.695312,62898.539062,62902.492188,62859.007812,62876.878906,62839.625000,62804.007812,62783.171875,62686.140625,62672.988281,62634.367188,62607.687500,62602.062500,62538.156250</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>63632.812500,63593.890625,63538.898438,63507.468750,63484.281250,63439.562500,63409.191406,63380.257812,63370.843750,63319.992188,63304.554688,63306.046875,63299.539062,63267.039062,63305.164062,63288.382812,63237.023438,63205.781250,63184.242188,63189.910156,63171.742188,63140.085938,63141.125000,63098.683594</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,44 @@
       </c>
       <c r="F11" t="n">
         <v>63897.9765625</v>
+      </c>
+      <c r="G11" t="n">
+        <v>64086.19921875</v>
+      </c>
+      <c r="H11" t="n">
+        <v>188.22265625</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2937023236586807</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.513966098064856</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:57:51</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="n">
+        <v>64157.546875</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1532,24 @@
           <t>63838.675781,63846.726562,63863.460938,63857.562500,63878.863281,63868.500000,63858.835938,63869.734375,63868.203125,63862.574219,63883.613281,63872.757812,63915.679688,63928.664062,63936.335938,63942.136719,63942.664062,63936.804688,63928.195312,63935.976562,63923.062500,63911.789062,63908.550781,63897.976562</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>63878.160156,63976.871094,64352.601562,64477.691406,64342.351562,64611.281250,64395.339844,64437.000000,64201.910156,64585.761719,64016.070312,63867.929688,63717.058594,64183.019531,64430.519531,63526.828125,63439.988281,63778.140625,63853.988281,63875.851562,63586.230469,64187.648438,64086.199219,64086.199219</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>39.484375,130.144532,489.140625,620.128906,463.488282,742.781250,536.503906,567.265625,333.707031,723.187500,132.457032,4.828125,198.621094,254.355469,494.183593,415.308594,502.675781,158.664063,74.207031,60.125000,336.832031,275.859375,177.648438,188.222657</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.061812,0.203424,0.760095,0.961773,0.720347,1.149615,0.833141,0.880341,0.519777,1.119732,0.206912,0.007560,0.311724,0.396297,0.767002,0.653753,0.792364,0.248775,0.116214,0.094128,0.529725,0.429770,0.277202,0.293702</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.513966098064856</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>63847.257812,63846.417969,63887.164062,63848.937500,63869.492188,63869.984375,63866.500000,63842.484375,63860.007812,63848.335938,63844.671875,63846.914062,63869.789062,63903.007812,63932.718750,63909.054688,63907.968750,63900.171875,63901.011719,63879.351562,63877.882812,63821.421875,63876.628906,63831.000000</t>
@@ -1507,6 +1563,49 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>63632.812500,63593.890625,63538.898438,63507.468750,63484.281250,63439.562500,63409.191406,63380.257812,63370.843750,63319.992188,63304.554688,63306.046875,63299.539062,63267.039062,63305.164062,63288.382812,63237.023438,63205.781250,63184.242188,63189.910156,63171.742188,63140.085938,63141.125000,63098.683594</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:57:51</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>64066.664062,64073.296875,64086.773438,64096.746094,64092.324219,64117.843750,64124.250000,64119.761719,64115.265625,64120.976562,64103.132812,64121.500000,64139.562500,64146.140625,64154.347656,64173.804688,64180.234375,64191.472656,64183.257812,64175.406250,64170.929688,64150.476562,64153.148438,64157.546875</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>64080.398438,64078.359375,64074.316406,64102.109375,64135.343750,64122.910156,64146.242188,64089.660156,64112.515625,64081.695312,64090.742188,64107.101562,64126.148438,64129.101562,64143.593750,64134.074219,64148.460938,64159.914062,64179.734375,64110.101562,64099.609375,64069.085938,64137.175781,64094.933594</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>63699.039062,63630.085938,63566.921875,63523.558594,63456.187500,63440.390625,63394.648438,63317.238281,63276.605469,63230.734375,63187.789062,63153.652344,63138.785156,63098.386719,63093.507812,63078.925781,63050.328125,63042.000000,62972.031250,62936.148438,62924.406250,62889.496094,62886.699219,62864.750000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>63841.621094,63796.625000,63758.339844,63742.585938,63690.128906,63687.265625,63665.656250,63623.796875,63596.820312,63565.500000,63511.328125,63539.738281,63538.734375,63497.078125,63517.390625,63517.953125,63493.019531,63473.472656,63454.917969,63439.578125,63427.292969,63398.343750,63410.121094,63395.660156</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,44 @@
       </c>
       <c r="F12" t="n">
         <v>64157.546875</v>
+      </c>
+      <c r="G12" t="n">
+        <v>64230.03125</v>
+      </c>
+      <c r="H12" t="n">
+        <v>72.484375</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1128512217561781</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6433616736897686</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:44</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="n">
+        <v>64143.13671875</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +1631,24 @@
           <t>64066.664062,64073.296875,64086.773438,64096.746094,64092.324219,64117.843750,64124.250000,64119.761719,64115.265625,64120.976562,64103.132812,64121.500000,64139.562500,64146.140625,64154.347656,64173.804688,64180.234375,64191.472656,64183.257812,64175.406250,64170.929688,64150.476562,64153.148438,64157.546875</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>64071.421875,63933.281250,63947.718750,63915.308594,63918.308594,64211.878906,64480.570312,64472.289062,64700.839844,64839.601562,64950.000000,64614.519531,64658.410156,64750.441406,64809.660156,64634.019531,64727.519531,64711.328125,64670.679688,64788.789062,64721.890625,64677.121094,64493.679688,64230.031250</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.757813,140.015625,139.054688,181.437500,174.015625,94.035156,356.320312,352.527343,585.574219,718.625000,846.867188,493.019531,518.847656,604.300781,655.312500,460.214843,547.285156,519.855469,487.421875,613.382812,550.960937,526.644532,340.531250,72.484375</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.007426,0.219003,0.217451,0.283872,0.272247,0.146445,0.552601,0.546789,0.905049,1.108312,1.303876,0.763017,0.802444,0.933277,1.011134,0.712032,0.845522,0.803345,0.753698,0.946742,0.851274,0.814267,0.528007,0.112851</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6433616736897686</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>64080.398438,64078.359375,64074.316406,64102.109375,64135.343750,64122.910156,64146.242188,64089.660156,64112.515625,64081.695312,64090.742188,64107.101562,64126.148438,64129.101562,64143.593750,64134.074219,64148.460938,64159.914062,64179.734375,64110.101562,64099.609375,64069.085938,64137.175781,64094.933594</t>
@@ -1606,6 +1662,49 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>63841.621094,63796.625000,63758.339844,63742.585938,63690.128906,63687.265625,63665.656250,63623.796875,63596.820312,63565.500000,63511.328125,63539.738281,63538.734375,63497.078125,63517.390625,63517.953125,63493.019531,63473.472656,63454.917969,63439.578125,63427.292969,63398.343750,63410.121094,63395.660156</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:44</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>64277.402344,64251.273438,64240.929688,64238.687500,64240.843750,64248.417969,64247.718750,64236.425781,64231.265625,64233.937500,64223.226562,64234.906250,64230.820312,64216.382812,64211.582031,64205.414062,64208.523438,64203.070312,64195.734375,64179.105469,64157.335938,64149.710938,64145.320312,64143.136719</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>64254.031250,64261.304688,64236.070312,64230.812500,64262.828125,64241.355469,64228.265625,64214.570312,64206.203125,64225.203125,64177.945312,64216.246094,64198.671875,64160.148438,64191.250000,64191.851562,64159.515625,64163.890625,64152.710938,64160.640625,64122.039062,64081.746094,64080.273438,64086.937500</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>64014.734375,63899.164062,63792.460938,63720.343750,63662.410156,63623.113281,63560.789062,63498.050781,63459.839844,63418.765625,63383.089844,63355.039062,63319.734375,63267.367188,63230.175781,63180.093750,63168.054688,63135.250000,63056.421875,63008.582031,62970.937500,62953.773438,62952.003906,62925.136719</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>64124.101562,64042.246094,63962.175781,63926.218750,63880.046875,63851.550781,63817.964844,63777.332031,63754.875000,63725.257812,63682.953125,63690.031250,63665.554688,63626.867188,63604.523438,63573.820312,63566.937500,63537.699219,63506.570312,63476.136719,63437.644531,63421.390625,63432.187500,63421.074219</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,44 @@
       </c>
       <c r="F13" t="n">
         <v>64143.13671875</v>
+      </c>
+      <c r="G13" t="n">
+        <v>62919.48828125</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1223.6484375</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.944784471275885</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.485744134187818</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:39:53</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>63015.82421875</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1730,24 @@
           <t>64277.402344,64251.273438,64240.929688,64238.687500,64240.843750,64248.417969,64247.718750,64236.425781,64231.265625,64233.937500,64223.226562,64234.906250,64230.820312,64216.382812,64211.582031,64205.414062,64208.523438,64203.070312,64195.734375,64179.105469,64157.335938,64149.710938,64145.320312,64143.136719</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>64239.468750,64290.140625,64171.070312,63872.109375,63754.531250,63646.699219,63850.421875,63738.750000,63677.859375,63201.859375,62601.449219,62625.761719,62800.640625,63179.171875,63026.468750,62892.000000,62892.398438,62894.820312,62884.949219,62825.820312,62875.738281,62903.039062,62999.800781,62919.488281</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>37.933594,38.867187,69.859375,366.578125,486.312500,601.718750,397.296875,497.675781,553.406250,1032.078125,1621.777343,1609.144531,1430.179687,1037.210937,1185.113281,1313.414062,1316.125000,1308.250000,1310.785156,1353.285157,1281.597657,1246.671875,1145.519531,1223.648438</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.059050,0.060456,0.108864,0.573925,0.762789,0.945404,0.622231,0.780806,0.869072,1.632987,2.590639,2.569461,2.277333,1.641698,1.880342,2.088364,2.092661,2.080060,2.084418,2.154027,2.038302,1.981895,1.818291,1.944784</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.485744134187818</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>64254.031250,64261.304688,64236.070312,64230.812500,64262.828125,64241.355469,64228.265625,64214.570312,64206.203125,64225.203125,64177.945312,64216.246094,64198.671875,64160.148438,64191.250000,64191.851562,64159.515625,64163.890625,64152.710938,64160.640625,64122.039062,64081.746094,64080.273438,64086.937500</t>
@@ -1705,6 +1761,49 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>64124.101562,64042.246094,63962.175781,63926.218750,63880.046875,63851.550781,63817.964844,63777.332031,63754.875000,63725.257812,63682.953125,63690.031250,63665.554688,63626.867188,63604.523438,63573.820312,63566.937500,63537.699219,63506.570312,63476.136719,63437.644531,63421.390625,63432.187500,63421.074219</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:39:53</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>62927.257812,62924.820312,62929.585938,62928.250000,62932.558594,62946.789062,62959.078125,62954.468750,62952.789062,62963.375000,62966.085938,62975.445312,62985.019531,62995.179688,62996.242188,62987.468750,62987.050781,63000.078125,63009.015625,62995.257812,62999.593750,62995.773438,63000.949219,63015.824219</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>62928.890625,62956.789062,62958.859375,62965.929688,63021.410156,63006.480469,63045.875000,62988.203125,63020.964844,63038.289062,63025.875000,63046.625000,63096.203125,63084.851562,63081.585938,63045.820312,63109.171875,63115.078125,63105.898438,63092.054688,63092.546875,63020.636719,63127.539062,63134.234375</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>62711.992188,62661.601562,62596.945312,62556.476562,62503.703125,62485.898438,62475.265625,62421.242188,62392.382812,62371.511719,62371.265625,62358.164062,62332.261719,62306.984375,62304.562500,62277.539062,62266.406250,62266.007812,62217.527344,62168.843750,62167.609375,62140.820312,62151.281250,62165.894531</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>62779.937500,62753.429688,62713.269531,62677.468750,62662.015625,62639.429688,62647.164062,62610.921875,62594.375000,62580.039062,62562.601562,62592.125000,62566.195312,62546.390625,62553.542969,62524.199219,62510.875000,62516.621094,62491.964844,62463.718750,62454.558594,62457.421875,62454.625000,62478.824219</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,44 @@
       </c>
       <c r="F14" t="n">
         <v>63015.82421875</v>
+      </c>
+      <c r="G14" t="n">
+        <v>63397.51171875</v>
+      </c>
+      <c r="H14" t="n">
+        <v>381.6875</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6020543861299761</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2936109240864482</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:44</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>63787.8203125</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1829,24 @@
           <t>62927.257812,62924.820312,62929.585938,62928.250000,62932.558594,62946.789062,62959.078125,62954.468750,62952.789062,62963.375000,62966.085938,62975.445312,62985.019531,62995.179688,62996.242188,62987.468750,62987.050781,63000.078125,63009.015625,62995.257812,62999.593750,62995.773438,63000.949219,63015.824219</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>63035.710938,62965.769531,63013.199219,62988.589844,63061.339844,62993.289062,62999.441406,63016.468750,63039.621094,63005.121094,63066.238281,62938.820312,62879.148438,62652.578125,62523.789062,62471.531250,62604.921875,62761.359375,62765.359375,62766.671875,62775.000000,62921.050781,63381.988281,63397.511719</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>108.453125,40.949219,83.613281,60.339844,128.781250,46.500000,40.363281,62.000000,86.832032,41.746094,100.152343,36.625000,105.871093,342.601563,472.453125,515.937500,382.128906,238.718750,243.656250,228.585937,224.593750,74.722657,381.039062,381.687500</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.172050,0.065034,0.132692,0.095795,0.204216,0.073817,0.064069,0.098387,0.137742,0.066258,0.158805,0.058191,0.168372,0.546828,0.755637,0.825876,0.610382,0.380359,0.388202,0.364184,0.357776,0.118756,0.601179,0.602054</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2936109240864482</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>62928.890625,62956.789062,62958.859375,62965.929688,63021.410156,63006.480469,63045.875000,62988.203125,63020.964844,63038.289062,63025.875000,63046.625000,63096.203125,63084.851562,63081.585938,63045.820312,63109.171875,63115.078125,63105.898438,63092.054688,63092.546875,63020.636719,63127.539062,63134.234375</t>
@@ -1804,6 +1860,49 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>62779.937500,62753.429688,62713.269531,62677.468750,62662.015625,62639.429688,62647.164062,62610.921875,62594.375000,62580.039062,62562.601562,62592.125000,62566.195312,62546.390625,62553.542969,62524.199219,62510.875000,62516.621094,62491.964844,62463.718750,62454.558594,62457.421875,62454.625000,62478.824219</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:44</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>63367.687500,63404.359375,63436.984375,63464.417969,63500.160156,63520.257812,63544.406250,63560.464844,63566.101562,63578.742188,63578.437500,63580.558594,63598.585938,63609.203125,63616.679688,63633.148438,63659.523438,63688.031250,63697.582031,63730.761719,63734.101562,63747.546875,63772.039062,63787.820312</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>63364.601562,63424.585938,63453.148438,63482.156250,63533.671875,63580.117188,63604.632812,63605.617188,63588.160156,63633.515625,63623.144531,63615.632812,63660.156250,63686.867188,63697.500000,63722.351562,63731.546875,63806.699219,63792.632812,63772.429688,63785.941406,63791.875000,63867.820312,63838.570312</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>63115.894531,63078.570312,63027.039062,62992.929688,62953.328125,62905.210938,62887.015625,62846.125000,62800.140625,62762.648438,62734.210938,62704.085938,62674.953125,62670.500000,62646.109375,62637.359375,62644.812500,62644.917969,62593.730469,62590.843750,62591.101562,62607.765625,62630.789062,62632.343750</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>63217.457031,63197.875000,63161.585938,63154.062500,63145.085938,63113.429688,63116.734375,63089.867188,63079.531250,63052.582031,63010.500000,63006.218750,62981.062500,62984.187500,62980.093750,62982.914062,62974.960938,62987.339844,62975.992188,63004.867188,62995.609375,62984.339844,63026.773438,63047.031250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,44 @@
       </c>
       <c r="F15" t="n">
         <v>63787.8203125</v>
+      </c>
+      <c r="G15" t="n">
+        <v>62971.609375</v>
+      </c>
+      <c r="H15" t="n">
+        <v>816.2109375</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.296157023142622</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6001310448494185</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:41:53</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>63281.109375</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1928,24 @@
           <t>63367.687500,63404.359375,63436.984375,63464.417969,63500.160156,63520.257812,63544.406250,63560.464844,63566.101562,63578.742188,63578.437500,63580.558594,63598.585938,63609.203125,63616.679688,63633.148438,63659.523438,63688.031250,63697.582031,63730.761719,63734.101562,63747.546875,63772.039062,63787.820312</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>63519.609375,63394.921875,63409.730469,63448.261719,63130.039062,63206.230469,63136.648438,62964.218750,63062.089844,63053.988281,63002.308594,63041.429688,63119.281250,63227.941406,63307.601562,63380.179688,63424.089844,63501.191406,63351.050781,63493.351562,63244.398438,63130.878906,63065.519531,62971.609375</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>151.921875,9.437500,27.253906,16.156250,370.121093,314.027343,407.757812,596.246094,504.011718,524.753907,576.128906,539.128907,479.304688,381.261719,309.078125,252.968750,235.433594,186.839844,346.531250,237.410157,489.703125,616.667969,706.519531,816.210937</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.239173,0.014887,0.042981,0.025464,0.586284,0.496830,0.645834,0.946960,0.799231,0.832230,0.914457,0.855198,0.759363,0.602996,0.488216,0.399129,0.371205,0.294230,0.547002,0.373913,0.774303,0.976809,1.120294,1.296157</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6001310448494185</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>63364.601562,63424.585938,63453.148438,63482.156250,63533.671875,63580.117188,63604.632812,63605.617188,63588.160156,63633.515625,63623.144531,63615.632812,63660.156250,63686.867188,63697.500000,63722.351562,63731.546875,63806.699219,63792.632812,63772.429688,63785.941406,63791.875000,63867.820312,63838.570312</t>
@@ -1903,6 +1959,49 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>63217.457031,63197.875000,63161.585938,63154.062500,63145.085938,63113.429688,63116.734375,63089.867188,63079.531250,63052.582031,63010.500000,63006.218750,62981.062500,62984.187500,62980.093750,62982.914062,62974.960938,62987.339844,62975.992188,63004.867188,62995.609375,62984.339844,63026.773438,63047.031250</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:41:53</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>62961.976562,62969.039062,62978.097656,62988.679688,63013.101562,63030.757812,63039.968750,63059.648438,63073.515625,63093.781250,63107.171875,63135.593750,63161.234375,63193.750000,63204.343750,63228.281250,63240.437500,63251.414062,63264.992188,63268.562500,63267.265625,63271.832031,63277.976562,63281.109375</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>62983.148438,63019.359375,63012.968750,63019.347656,63080.304688,63103.593750,63130.203125,63120.070312,63131.421875,63165.734375,63192.386719,63227.804688,63287.136719,63274.429688,63305.398438,63305.351562,63343.285156,63396.535156,63371.902344,63375.894531,63375.585938,63331.148438,63396.156250,63401.242188</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>62749.468750,62695.085938,62631.859375,62596.875000,62572.367188,62534.925781,62513.437500,62475.382812,62464.898438,62449.757812,62451.203125,62453.152344,62452.261719,62445.496094,62436.929688,62423.593750,62429.300781,62425.082031,62390.382812,62369.835938,62359.113281,62364.375000,62367.054688,62356.507812</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>62836.207031,62797.664062,62749.441406,62736.062500,62730.011719,62718.605469,62704.460938,62688.078125,62691.054688,62688.851562,62677.679688,62714.621094,62696.312500,62713.710938,62714.250000,62713.867188,62706.425781,62699.148438,62710.148438,62711.402344,62686.148438,62689.789062,62695.769531,62704.406250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,44 @@
       </c>
       <c r="F16" t="n">
         <v>63281.109375</v>
+      </c>
+      <c r="G16" t="n">
+        <v>63661.44140625</v>
+      </c>
+      <c r="H16" t="n">
+        <v>380.33203125</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5974291860954639</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6677575796612895</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>63719.5390625</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1989,6 +2027,24 @@
           <t>62961.976562,62969.039062,62978.097656,62988.679688,63013.101562,63030.757812,63039.968750,63059.648438,63073.515625,63093.781250,63107.171875,63135.593750,63161.234375,63193.750000,63204.343750,63228.281250,63240.437500,63251.414062,63264.992188,63268.562500,63267.265625,63271.832031,63277.976562,63281.109375</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>62707.750000,62743.539062,62541.839844,62524.601562,62457.589844,62749.359375,62656.000000,62481.289062,62622.738281,63267.199219,63899.031250,63624.261719,63708.480469,63852.750000,63808.058594,63802.781250,63736.750000,63540.410156,63553.429688,63466.519531,63302.050781,63782.300781,63758.988281,63661.441406</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>254.226562,225.500000,436.257812,464.078125,555.511718,281.398437,383.968750,578.359375,450.777344,173.417969,791.859375,488.667969,547.246094,659.000000,603.714844,574.500000,496.312500,288.996094,288.437500,197.957031,34.785156,510.468750,481.011719,380.332031</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.405415,0.359400,0.697546,0.742233,0.889422,0.448448,0.612820,0.925652,0.719830,0.274104,1.239235,0.768053,0.858985,1.032062,0.946142,0.900431,0.778691,0.454823,0.453850,0.311908,0.054951,0.800330,0.754422,0.597429</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6677575796612895</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>62983.148438,63019.359375,63012.968750,63019.347656,63080.304688,63103.593750,63130.203125,63120.070312,63131.421875,63165.734375,63192.386719,63227.804688,63287.136719,63274.429688,63305.398438,63305.351562,63343.285156,63396.535156,63371.902344,63375.894531,63375.585938,63331.148438,63396.156250,63401.242188</t>
@@ -2002,6 +2058,49 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>62836.207031,62797.664062,62749.441406,62736.062500,62730.011719,62718.605469,62704.460938,62688.078125,62691.054688,62688.851562,62677.679688,62714.621094,62696.312500,62713.710938,62714.250000,62713.867188,62706.425781,62699.148438,62710.148438,62711.402344,62686.148438,62689.789062,62695.769531,62704.406250</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>63638.093750,63621.671875,63610.945312,63594.097656,63596.687500,63605.890625,63614.031250,63647.101562,63653.148438,63676.855469,63710.687500,63741.015625,63776.750000,63799.000000,63803.687500,63792.167969,63794.601562,63793.628906,63786.828125,63787.710938,63763.187500,63735.835938,63717.296875,63719.539062</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>63649.343750,63633.769531,63611.476562,63605.203125,63617.300781,63620.125000,63632.226562,63671.679688,63685.835938,63693.171875,63747.281250,63773.949219,63844.320312,63825.351562,63844.148438,63842.050781,63853.875000,63855.152344,63819.078125,63825.656250,63797.824219,63779.371094,63767.562500,63775.460938</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>63328.406250,63241.718750,63163.226562,63092.101562,63046.156250,63002.593750,62977.695312,62963.546875,62938.722656,62917.195312,62928.382812,62927.496094,62931.945312,62926.531250,62919.921875,62881.089844,62863.843750,62853.511719,62795.945312,62781.382812,62755.875000,62734.554688,62716.992188,62706.617188</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>63464.507812,63395.089844,63326.484375,63289.585938,63254.886719,63229.906250,63222.453125,63228.214844,63221.019531,63206.601562,63199.765625,63232.703125,63224.695312,63240.656250,63242.117188,63211.996094,63189.886719,63176.609375,63155.625000,63157.570312,63126.226562,63090.191406,63074.378906,63082.656250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,44 @@
       </c>
       <c r="F17" t="n">
         <v>63719.5390625</v>
+      </c>
+      <c r="G17" t="n">
+        <v>64109.44921875</v>
+      </c>
+      <c r="H17" t="n">
+        <v>389.91015625</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.6081945189071497</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3958510919665481</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:20:54</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="n">
+        <v>64023.8515625</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2126,24 @@
           <t>63638.093750,63621.671875,63610.945312,63594.097656,63596.687500,63605.890625,63614.031250,63647.101562,63653.148438,63676.855469,63710.687500,63741.015625,63776.750000,63799.000000,63803.687500,63792.167969,63794.601562,63793.628906,63786.828125,63787.710938,63763.187500,63735.835938,63717.296875,63719.539062</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>63975.449219,63768.851562,63607.160156,63617.410156,63514.769531,63534.578125,63694.148438,63853.320312,63840.640625,63619.851562,64069.250000,64068.738281,63899.718750,63919.718750,64261.410156,64181.000000,64299.078125,64148.511719,64189.621094,63934.531250,63934.531250,64284.789062,64315.949219,64109.449219</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>337.355469,147.179688,3.785156,23.312500,81.917969,71.312500,80.117188,206.218750,187.492187,57.003907,358.562500,327.722656,122.968750,120.718750,457.722656,388.832031,504.476563,354.882813,402.792969,146.820312,171.343750,548.953125,598.652344,389.910157</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.527320,0.230802,0.005951,0.036645,0.128975,0.112242,0.125784,0.322957,0.293688,0.089601,0.559648,0.511517,0.192440,0.188860,0.712282,0.605837,0.784578,0.553221,0.627505,0.229642,0.267999,0.853939,0.930799,0.608195</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3958510919665481</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>63649.343750,63633.769531,63611.476562,63605.203125,63617.300781,63620.125000,63632.226562,63671.679688,63685.835938,63693.171875,63747.281250,63773.949219,63844.320312,63825.351562,63844.148438,63842.050781,63853.875000,63855.152344,63819.078125,63825.656250,63797.824219,63779.371094,63767.562500,63775.460938</t>
@@ -2101,6 +2157,49 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>63464.507812,63395.089844,63326.484375,63289.585938,63254.886719,63229.906250,63222.453125,63228.214844,63221.019531,63206.601562,63199.765625,63232.703125,63224.695312,63240.656250,63242.117188,63211.996094,63189.886719,63176.609375,63155.625000,63157.570312,63126.226562,63090.191406,63074.378906,63082.656250</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:20:54</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>64100.980469,64100.222656,64090.820312,64085.226562,64085.421875,64083.773438,64081.304688,64073.500000,64067.742188,64066.222656,64081.437500,64090.042969,64108.929688,64111.960938,64122.093750,64106.953125,64113.796875,64114.722656,64100.585938,64091.726562,64070.593750,64053.527344,64033.464844,64023.851562</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>64101.648438,64084.781250,64081.007812,64081.625000,64073.812500,64050.914062,64062.343750,64056.960938,64049.828125,64039.828125,64063.835938,64082.187500,64086.796875,64094.289062,64103.679688,64096.691406,64117.152344,64077.437500,64056.671875,64066.781250,64030.910156,64042.898438,64021.859375,63992.382812</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>63800.625000,63726.632812,63638.648438,63572.152344,63512.199219,63461.144531,63416.742188,63355.628906,63322.242188,63287.398438,63286.093750,63241.820312,63242.066406,63188.656250,63181.757812,63132.792969,63118.093750,63104.515625,63035.796875,63007.789062,62979.414062,62952.757812,62917.976562,62900.234375</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>63920.328125,63868.890625,63802.367188,63770.644531,63728.417969,63696.421875,63674.382812,63634.640625,63598.976562,63581.148438,63574.867188,63580.546875,63554.703125,63534.289062,63533.824219,63494.117188,63476.148438,63472.140625,63435.867188,63415.941406,63395.398438,63360.882812,63335.570312,63328.964844</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,44 @@
       </c>
       <c r="F18" t="n">
         <v>64023.8515625</v>
+      </c>
+      <c r="G18" t="n">
+        <v>64470.26171875</v>
+      </c>
+      <c r="H18" t="n">
+        <v>446.41015625</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6924280192896591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5209518427636119</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:41</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>64441.1953125</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,6 +2225,24 @@
           <t>64100.980469,64100.222656,64090.820312,64085.226562,64085.421875,64083.773438,64081.304688,64073.500000,64067.742188,64066.222656,64081.437500,64090.042969,64108.929688,64111.960938,64122.093750,64106.953125,64113.796875,64114.722656,64100.585938,64091.726562,64070.593750,64053.527344,64033.464844,64023.851562</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>64113.968750,64275.218750,64199.308594,64109.980469,64063.031250,64097.269531,64004.269531,64018.289062,64277.039062,64361.238281,64426.839844,64328.250000,64606.019531,64695.351562,64741.109375,64794.628906,64778.601562,64671.679688,64573.531250,64597.859375,64582.300781,64520.621094,64516.679688,64470.261719</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>12.988281,174.996094,108.488282,24.753907,22.390625,13.496093,77.035157,55.210938,209.296875,295.015625,345.402344,238.207031,497.089843,583.390625,619.015625,687.675781,664.804688,556.957032,472.945312,506.132813,511.707031,467.093750,483.214843,446.410157</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.020258,0.272261,0.168987,0.038612,0.034951,0.021056,0.120359,0.086242,0.325617,0.458375,0.536116,0.370299,0.769417,0.901750,0.956140,1.061316,1.026272,0.861207,0.732414,0.783513,0.792333,0.723945,0.748977,0.692428</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5209518427636119</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>64101.648438,64084.781250,64081.007812,64081.625000,64073.812500,64050.914062,64062.343750,64056.960938,64049.828125,64039.828125,64063.835938,64082.187500,64086.796875,64094.289062,64103.679688,64096.691406,64117.152344,64077.437500,64056.671875,64066.781250,64030.910156,64042.898438,64021.859375,63992.382812</t>
@@ -2200,6 +2256,49 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>63920.328125,63868.890625,63802.367188,63770.644531,63728.417969,63696.421875,63674.382812,63634.640625,63598.976562,63581.148438,63574.867188,63580.546875,63554.703125,63534.289062,63533.824219,63494.117188,63476.148438,63472.140625,63435.867188,63415.941406,63395.398438,63360.882812,63335.570312,63328.964844</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:41</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>64482.832031,64469.734375,64456.781250,64457.617188,64453.453125,64438.367188,64434.875000,64426.320312,64436.277344,64447.593750,64454.480469,64454.207031,64463.976562,64466.882812,64475.242188,64469.335938,64473.359375,64479.265625,64459.734375,64465.148438,64457.914062,64455.285156,64441.140625,64441.195312</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>64492.648438,64468.718750,64444.117188,64446.968750,64429.097656,64426.605469,64408.695312,64414.437500,64407.492188,64431.992188,64413.781250,64410.242188,64394.742188,64422.910156,64425.675781,64409.828125,64405.539062,64404.335938,64377.453125,64407.054688,64393.023438,64398.773438,64396.285156,64361.542969</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>64278.171875,64181.613281,64088.882812,64027.398438,63964.312500,63905.250000,63856.000000,63791.324219,63779.261719,63762.320312,63750.140625,63704.941406,63695.492188,63652.089844,63633.421875,63589.128906,63573.523438,63541.953125,63450.964844,63426.796875,63413.992188,63393.718750,63365.925781,63351.277344</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>64369.101562,64297.039062,64223.421875,64200.132812,64159.117188,64113.890625,64085.273438,64050.109375,64040.226562,64039.945312,64018.390625,64016.433594,63986.937500,63969.921875,63966.234375,63937.281250,63929.792969,63906.609375,63868.847656,63863.398438,63853.253906,63825.507812,63821.640625,63809.687500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,44 @@
       </c>
       <c r="F19" t="n">
         <v>64441.1953125</v>
+      </c>
+      <c r="G19" t="n">
+        <v>64319.37109375</v>
+      </c>
+      <c r="H19" t="n">
+        <v>121.82421875</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1894051771315249</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2669441201277834</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:10:52</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="n">
+        <v>64317.66015625</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2324,24 @@
           <t>64482.832031,64469.734375,64456.781250,64457.617188,64453.453125,64438.367188,64434.875000,64426.320312,64436.277344,64447.593750,64454.480469,64454.207031,64463.976562,64466.882812,64475.242188,64469.335938,64473.359375,64479.265625,64459.734375,64465.148438,64457.914062,64455.285156,64441.140625,64441.195312</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>64666.289062,64845.378906,64798.089844,64744.410156,64873.601562,64615.941406,64546.789062,64552.621094,64346.011719,64360.519531,64709.550781,64570.921875,64690.128906,64557.160156,64356.351562,64397.949219,64381.398438,64388.371094,64296.378906,64267.300781,64258.820312,64364.250000,64337.968750,64319.371094</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>183.457032,375.644531,341.308594,286.792968,420.148438,177.574218,111.914062,126.300782,90.265625,87.074219,255.070312,116.714844,226.152344,90.277344,118.890625,71.386719,91.960938,90.894531,163.355469,197.847657,199.093750,91.035156,103.171875,121.824218</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.283698,0.579293,0.526726,0.442962,0.647642,0.274815,0.173384,0.195656,0.140282,0.135291,0.394177,0.180754,0.349593,0.139841,0.184738,0.110852,0.142838,0.141166,0.254066,0.307851,0.309831,0.141437,0.160359,0.189405</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2669441201277834</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>64492.648438,64468.718750,64444.117188,64446.968750,64429.097656,64426.605469,64408.695312,64414.437500,64407.492188,64431.992188,64413.781250,64410.242188,64394.742188,64422.910156,64425.675781,64409.828125,64405.539062,64404.335938,64377.453125,64407.054688,64393.023438,64398.773438,64396.285156,64361.542969</t>
@@ -2299,6 +2355,49 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>64369.101562,64297.039062,64223.421875,64200.132812,64159.117188,64113.890625,64085.273438,64050.109375,64040.226562,64039.945312,64018.390625,64016.433594,63986.937500,63969.921875,63966.234375,63937.281250,63929.792969,63906.609375,63868.847656,63863.398438,63853.253906,63825.507812,63821.640625,63809.687500</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:10:52</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>64321.906250,64311.589844,64300.421875,64291.109375,64297.148438,64291.097656,64296.132812,64282.273438,64278.468750,64283.140625,64301.562500,64310.167969,64331.402344,64336.351562,64345.250000,64339.250000,64344.937500,64359.132812,64343.996094,64342.320312,64321.664062,64321.113281,64323.937500,64317.660156</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>64328.304688,64301.382812,64287.718750,64269.820312,64292.398438,64273.632812,64305.218750,64268.453125,64267.812500,64274.152344,64271.554688,64289.074219,64306.367188,64319.625000,64349.597656,64329.929688,64345.273438,64318.308594,64322.093750,64335.710938,64307.203125,64300.136719,64287.265625,64295.910156</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>64160.890625,64078.601562,64001.316406,63938.914062,63895.710938,63851.191406,63820.203125,63754.546875,63728.378906,63694.484375,63686.941406,63666.117188,63662.656250,63620.796875,63601.476562,63564.953125,63524.609375,63515.671875,63420.554688,63389.273438,63354.710938,63331.945312,63325.968750,63300.609375</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>64225.960938,64180.164062,64116.023438,64085.664062,64054.242188,64029.625000,64013.984375,63969.027344,63953.289062,63934.507812,63919.625000,63937.687500,63911.472656,63890.308594,63891.941406,63877.414062,63850.070312,63843.695312,63804.109375,63794.527344,63756.375000,63745.835938,63749.750000,63727.542969</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,6 +1177,44 @@
       </c>
       <c r="F20" t="n">
         <v>64317.66015625</v>
+      </c>
+      <c r="G20" t="n">
+        <v>64873.8203125</v>
+      </c>
+      <c r="H20" t="n">
+        <v>556.16015625</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8572952133402234</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7255492423437573</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:07:52</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="n">
+        <v>64619.77734375</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2423,24 @@
           <t>64321.906250,64311.589844,64300.421875,64291.109375,64297.148438,64291.097656,64296.132812,64282.273438,64278.468750,64283.140625,64301.562500,64310.167969,64331.402344,64336.351562,64345.250000,64339.250000,64344.937500,64359.132812,64343.996094,64342.320312,64321.664062,64321.113281,64323.937500,64317.660156</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>64191.671875,64276.050781,64254.398438,64264.191406,64552.898438,64794.058594,64849.109375,64975.628906,65250.558594,64960.890625,64906.859375,64852.910156,64758.070312,64713.890625,64667.820312,64914.789062,64935.718750,64960.921875,64960.921875,64878.218750,64878.218750,64868.859375,64873.820312,64873.820312</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>130.234375,35.539063,46.023438,26.917969,255.750000,502.960938,552.976563,693.355468,972.089844,677.750000,605.296875,542.742187,426.667968,377.539063,322.570312,575.539062,590.781250,601.789063,616.925781,535.898438,556.554688,547.746094,549.882812,556.160157</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.202884,0.055291,0.071627,0.041886,0.396187,0.776245,0.852713,1.067101,1.489780,1.043320,0.932562,0.836882,0.658865,0.583397,0.498811,0.886607,0.909794,0.926386,0.949688,0.826007,0.857845,0.844390,0.847619,0.857295</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7255492423437573</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>64328.304688,64301.382812,64287.718750,64269.820312,64292.398438,64273.632812,64305.218750,64268.453125,64267.812500,64274.152344,64271.554688,64289.074219,64306.367188,64319.625000,64349.597656,64329.929688,64345.273438,64318.308594,64322.093750,64335.710938,64307.203125,64300.136719,64287.265625,64295.910156</t>
@@ -2398,6 +2454,49 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>64225.960938,64180.164062,64116.023438,64085.664062,64054.242188,64029.625000,64013.984375,63969.027344,63953.289062,63934.507812,63919.625000,63937.687500,63911.472656,63890.308594,63891.941406,63877.414062,63850.070312,63843.695312,63804.109375,63794.527344,63756.375000,63745.835938,63749.750000,63727.542969</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:07:52</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>64864.914062,64852.023438,64843.007812,64835.195312,64820.179688,64806.812500,64804.171875,64788.960938,64804.902344,64802.785156,64807.808594,64793.070312,64768.914062,64757.367188,64749.746094,64724.468750,64725.242188,64712.804688,64682.062500,64665.023438,64650.226562,64638.320312,64637.605469,64619.777344</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>64853.781250,64810.882812,64835.562500,64799.148438,64760.726562,64752.980469,64752.148438,64756.277344,64715.210938,64746.632812,64732.453125,64697.941406,64682.929688,64664.531250,64670.695312,64656.765625,64630.445312,64581.289062,64569.359375,64579.593750,64558.375000,64567.804688,64516.062500,64517.449219</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>64662.906250,64571.199219,64491.500000,64419.023438,64344.691406,64281.757812,64207.398438,64140.843750,64117.382812,64069.566406,64033.640625,63992.929688,63956.382812,63888.757812,63837.171875,63771.500000,63744.117188,63700.472656,63612.792969,63571.570312,63544.683594,63522.156250,63513.035156,63471.000000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>64744.332031,64684.093750,64627.796875,64589.011719,64537.191406,64483.160156,64439.640625,64386.742188,64382.007812,64354.730469,64336.398438,64303.578125,64249.632812,64221.242188,64181.421875,64144.898438,64123.441406,64091.492188,64038.371094,64010.449219,63992.687500,63952.000000,63954.765625,63924.718750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,44 @@
       </c>
       <c r="F21" t="n">
         <v>64619.77734375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>64782.26953125</v>
+      </c>
+      <c r="H21" t="n">
+        <v>162.4921875</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2508281798025248</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3178364721492561</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:18:55</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="n">
+        <v>64630.3359375</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2522,24 @@
           <t>64864.914062,64852.023438,64843.007812,64835.195312,64820.179688,64806.812500,64804.171875,64788.960938,64804.902344,64802.785156,64807.808594,64793.070312,64768.914062,64757.367188,64749.746094,64724.468750,64725.242188,64712.804688,64682.062500,64665.023438,64650.226562,64638.320312,64637.605469,64619.777344</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>64989.859375,64974.140625,64961.000000,64968.730469,64928.800781,64957.718750,64955.289062,64966.679688,64922.839844,64960.890625,64973.609375,65082.738281,65029.660156,65039.988281,65073.140625,64992.851562,65025.421875,65032.179688,64968.031250,64892.511719,64905.281250,64922.078125,64806.000000,64782.269531</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>124.945313,122.117187,117.992188,133.535157,108.621093,150.906250,151.117188,177.718750,117.937500,158.105469,165.800781,289.667969,260.746094,282.621093,323.394531,268.382812,300.179687,319.375000,285.968750,227.488281,255.054688,283.757813,168.394531,162.492187</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.192254,0.187947,0.181635,0.205538,0.167293,0.232315,0.232648,0.273554,0.181658,0.243386,0.255182,0.445076,0.400965,0.434534,0.496971,0.412942,0.461634,0.491103,0.440168,0.350562,0.392964,0.437074,0.259844,0.250828</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3178364721492561</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>64853.781250,64810.882812,64835.562500,64799.148438,64760.726562,64752.980469,64752.148438,64756.277344,64715.210938,64746.632812,64732.453125,64697.941406,64682.929688,64664.531250,64670.695312,64656.765625,64630.445312,64581.289062,64569.359375,64579.593750,64558.375000,64567.804688,64516.062500,64517.449219</t>
@@ -2497,6 +2553,49 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>64744.332031,64684.093750,64627.796875,64589.011719,64537.191406,64483.160156,64439.640625,64386.742188,64382.007812,64354.730469,64336.398438,64303.578125,64249.632812,64221.242188,64181.421875,64144.898438,64123.441406,64091.492188,64038.371094,64010.449219,63992.687500,63952.000000,63954.765625,63924.718750</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:18:55</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>64797.171875,64773.875000,64770.515625,64763.062500,64754.203125,64757.558594,64762.203125,64755.273438,64763.617188,64764.335938,64759.968750,64761.601562,64745.339844,64732.085938,64722.429688,64703.863281,64710.125000,64695.410156,64669.648438,64661.960938,64655.500000,64643.656250,64643.796875,64630.335938</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>64784.593750,64751.914062,64770.234375,64777.476562,64728.304688,64729.265625,64733.230469,64736.359375,64717.906250,64727.679688,64700.835938,64704.445312,64665.152344,64669.195312,64653.164062,64644.843750,64625.531250,64609.156250,64555.906250,64616.117188,64570.812500,64579.335938,64538.726562,64531.976562</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>64649.765625,64585.992188,64534.144531,64483.304688,64428.277344,64391.835938,64348.671875,64302.882812,64277.660156,64248.093750,64204.945312,64175.480469,64145.835938,64091.179688,64043.417969,63998.921875,63981.796875,63943.609375,63859.078125,63823.328125,63810.378906,63780.183594,63754.082031,63704.750000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>64707.468750,64657.890625,64620.968750,64594.210938,64556.218750,64529.667969,64505.281250,64473.917969,64463.757812,64449.230469,64415.617188,64416.031250,64370.734375,64337.437500,64312.218750,64281.312500,64277.929688,64245.039062,64201.585938,64177.484375,64172.429688,64124.222656,64120.109375,64088.882812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,44 @@
       </c>
       <c r="F22" t="n">
         <v>64630.3359375</v>
+      </c>
+      <c r="G22" t="n">
+        <v>64920.48046875</v>
+      </c>
+      <c r="H22" t="n">
+        <v>290.14453125</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.446922957370384</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3971868228225469</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:14</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>64813.4375</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2621,24 @@
           <t>64797.171875,64773.875000,64770.515625,64763.062500,64754.203125,64757.558594,64762.203125,64755.273438,64763.617188,64764.335938,64759.968750,64761.601562,64745.339844,64732.085938,64722.429688,64703.863281,64710.125000,64695.410156,64669.648438,64661.960938,64655.500000,64643.656250,64643.796875,64630.335938</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>64734.968750,64735.429688,64754.320312,64792.898438,64770.871094,64770.070312,64832.308594,64905.460938,64899.968750,64906.589844,65178.679688,65214.289062,65174.988281,65181.968750,65142.000000,65147.121094,65130.738281,65095.570312,65143.699219,65023.078125,64848.691406,64916.980469,65146.851562,64920.480469</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>62.203125,38.445312,16.195312,29.835938,16.667969,12.511718,70.105469,150.187500,136.351562,142.253906,418.710938,452.687500,429.648437,449.882812,419.570312,443.257813,420.613281,400.160157,474.050781,361.117187,193.191406,273.324219,503.054688,290.144531</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.096089,0.059388,0.025010,0.046048,0.025734,0.019317,0.108134,0.231394,0.210095,0.219167,0.642405,0.694154,0.659223,0.690195,0.644086,0.680395,0.645798,0.614727,0.727700,0.555368,0.297911,0.421037,0.772186,0.446923</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3971868228225469</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>64784.593750,64751.914062,64770.234375,64777.476562,64728.304688,64729.265625,64733.230469,64736.359375,64717.906250,64727.679688,64700.835938,64704.445312,64665.152344,64669.195312,64653.164062,64644.843750,64625.531250,64609.156250,64555.906250,64616.117188,64570.812500,64579.335938,64538.726562,64531.976562</t>
@@ -2596,6 +2652,49 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>64707.468750,64657.890625,64620.968750,64594.210938,64556.218750,64529.667969,64505.281250,64473.917969,64463.757812,64449.230469,64415.617188,64416.031250,64370.734375,64337.437500,64312.218750,64281.312500,64277.929688,64245.039062,64201.585938,64177.484375,64172.429688,64124.222656,64120.109375,64088.882812</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:14</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>64917.101562,64892.433594,64893.210938,64897.843750,64887.855469,64881.593750,64888.968750,64880.765625,64883.445312,64882.828125,64885.500000,64885.125000,64888.554688,64880.570312,64879.484375,64863.476562,64860.843750,64860.910156,64838.210938,64834.027344,64819.859375,64828.621094,64823.632812,64813.437500</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>64890.542969,64861.164062,64871.980469,64872.859375,64881.398438,64864.468750,64849.976562,64854.656250,64857.828125,64846.378906,64839.671875,64831.957031,64811.070312,64814.664062,64822.546875,64802.867188,64812.437500,64764.843750,64747.878906,64777.000000,64757.812500,64772.921875,64729.578125,64727.355469</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>64749.078125,64676.394531,64618.226562,64576.968750,64525.851562,64480.777344,64442.750000,64392.203125,64364.398438,64331.761719,64309.304688,64282.781250,64275.285156,64228.359375,64203.898438,64158.648438,64122.996094,64106.660156,64029.144531,64014.390625,63989.000000,63973.085938,63959.460938,63923.519531</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>64813.355469,64760.792969,64717.234375,64706.777344,64666.039062,64633.203125,64612.695312,64574.757812,64565.042969,64544.878906,64523.625000,64530.312500,64510.101562,64479.328125,64469.125000,64441.542969,64423.710938,64405.757812,64369.367188,64365.078125,64344.812500,64324.156250,64324.632812,64287.226562</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,44 @@
       </c>
       <c r="F23" t="n">
         <v>64813.4375</v>
+      </c>
+      <c r="G23" t="n">
+        <v>63978.359375</v>
+      </c>
+      <c r="H23" t="n">
+        <v>835.078125</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.305250921026763</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8322720472592023</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:50</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>63901.765625</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2720,24 @@
           <t>64917.101562,64892.433594,64893.210938,64897.843750,64887.855469,64881.593750,64888.968750,64880.765625,64883.445312,64882.828125,64885.500000,64885.125000,64888.554688,64880.570312,64879.484375,64863.476562,64860.843750,64860.910156,64838.210938,64834.027344,64819.859375,64828.621094,64823.632812,64813.437500</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>64921.089844,64950.769531,65085.601562,65248.078125,65149.839844,65190.351562,64907.648438,64956.261719,65069.460938,64817.101562,64494.730469,64562.761719,64235.851562,63833.921875,63884.980469,63815.898438,63975.878906,64096.859375,63929.390625,63929.390625,63972.089844,63972.089844,63993.250000,63978.359375</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.988282,58.335937,192.390625,350.234375,261.984375,308.757812,18.679688,75.496094,186.015625,65.726562,390.769531,322.363281,652.703125,1046.648437,994.503906,1047.578125,884.964844,764.050781,908.820313,904.636719,847.769531,856.531250,830.382812,835.078125</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.006143,0.089816,0.295596,0.536773,0.402126,0.473625,0.028779,0.116226,0.285872,0.101403,0.605894,0.499302,1.016104,1.639643,1.556710,1.641563,1.383279,1.192025,1.421600,1.415056,1.325218,1.338914,1.297610,1.305251</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8322720472592023</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>64890.542969,64861.164062,64871.980469,64872.859375,64881.398438,64864.468750,64849.976562,64854.656250,64857.828125,64846.378906,64839.671875,64831.957031,64811.070312,64814.664062,64822.546875,64802.867188,64812.437500,64764.843750,64747.878906,64777.000000,64757.812500,64772.921875,64729.578125,64727.355469</t>
@@ -2695,6 +2751,49 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>64813.355469,64760.792969,64717.234375,64706.777344,64666.039062,64633.203125,64612.695312,64574.757812,64565.042969,64544.878906,64523.625000,64530.312500,64510.101562,64479.328125,64469.125000,64441.542969,64423.710938,64405.757812,64369.367188,64365.078125,64344.812500,64324.156250,64324.632812,64287.226562</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:50</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>63944.492188,63935.421875,63938.675781,63932.859375,63932.441406,63929.234375,63912.351562,63896.226562,63886.125000,63874.707031,63861.921875,63856.937500,63843.320312,63833.109375,63845.835938,63832.414062,63833.945312,63845.183594,63840.113281,63848.875000,63869.046875,63870.195312,63880.742188,63901.765625</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>63952.156250,63941.003906,63944.335938,63956.789062,63968.023438,63926.425781,63909.312500,63870.023438,63889.515625,63849.152344,63849.929688,63869.515625,63845.351562,63867.812500,63873.558594,63840.253906,63874.660156,63842.828125,63857.074219,63870.820312,63884.843750,63863.722656,63873.554688,63899.289062</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>63740.710938,63665.164062,63591.093750,63529.648438,63469.406250,63421.250000,63351.250000,63278.699219,63236.148438,63183.015625,63148.281250,63120.007812,63091.695312,63058.007812,63067.890625,63054.550781,63034.718750,63033.468750,62974.195312,62970.117188,63003.531250,62986.773438,62998.500000,63008.839844</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>63811.140625,63771.566406,63714.140625,63679.703125,63640.656250,63596.015625,63559.054688,63497.566406,63467.750000,63427.921875,63382.265625,63398.566406,63356.109375,63328.921875,63338.078125,63335.023438,63303.906250,63312.410156,63285.828125,63298.687500,63316.570312,63306.507812,63320.496094,63333.968750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,44 @@
       </c>
       <c r="F24" t="n">
         <v>63901.765625</v>
+      </c>
+      <c r="G24" t="n">
+        <v>63793.30859375</v>
+      </c>
+      <c r="H24" t="n">
+        <v>108.45703125</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1700131779348184</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3651258048231474</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:35</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>63960.296875</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,6 +2819,24 @@
           <t>63944.492188,63935.421875,63938.675781,63932.859375,63932.441406,63929.234375,63912.351562,63896.226562,63886.125000,63874.707031,63861.921875,63856.937500,63843.320312,63833.109375,63845.835938,63832.414062,63833.945312,63845.183594,63840.113281,63848.875000,63869.046875,63870.195312,63880.742188,63901.765625</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>64074.718750,63960.210938,63926.890625,63897.941406,63999.171875,64073.851562,64242.449219,64171.171875,64327.171875,64266.519531,64139.988281,63713.960938,63541.371094,63440.589844,63537.121094,63305.789062,63477.968750,63682.160156,63615.578125,63604.660156,63482.839844,63685.039062,63760.898438,63793.308594</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>130.226562,24.789062,11.785156,34.917969,66.730469,144.617188,330.097657,274.945313,441.046875,391.812500,278.066406,142.976562,301.949218,392.519531,308.714844,526.625000,355.976562,163.023438,224.535156,244.214844,386.207031,185.156250,119.843750,108.457031</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.203242,0.038757,0.018435,0.054646,0.104268,0.225704,0.513831,0.428456,0.685631,0.609668,0.433530,0.224404,0.475201,0.618720,0.485881,0.831875,0.560788,0.255995,0.352956,0.383957,0.608364,0.290737,0.187958,0.170013</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3651258048231474</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>63952.156250,63941.003906,63944.335938,63956.789062,63968.023438,63926.425781,63909.312500,63870.023438,63889.515625,63849.152344,63849.929688,63869.515625,63845.351562,63867.812500,63873.558594,63840.253906,63874.660156,63842.828125,63857.074219,63870.820312,63884.843750,63863.722656,63873.554688,63899.289062</t>
@@ -2794,6 +2850,49 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>63811.140625,63771.566406,63714.140625,63679.703125,63640.656250,63596.015625,63559.054688,63497.566406,63467.750000,63427.921875,63382.265625,63398.566406,63356.109375,63328.921875,63338.078125,63335.023438,63303.906250,63312.410156,63285.828125,63298.687500,63316.570312,63306.507812,63320.496094,63333.968750</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:35</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>63768.296875,63789.820312,63806.226562,63820.503906,63828.843750,63846.679688,63832.875000,63847.984375,63856.601562,63853.875000,63843.304688,63861.085938,63843.554688,63848.179688,63860.328125,63857.914062,63873.238281,63879.007812,63893.152344,63908.437500,63929.914062,63924.304688,63934.199219,63960.296875</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>63782.906250,63806.695312,63817.046875,63857.648438,63852.570312,63841.421875,63837.152344,63853.984375,63855.609375,63846.859375,63851.031250,63879.773438,63866.625000,63887.109375,63898.390625,63885.132812,63908.000000,63915.117188,63933.085938,63930.523438,63946.386719,63950.824219,63945.937500,63951.539062</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>63500.234375,63466.812500,63423.550781,63399.945312,63364.351562,63346.750000,63290.546875,63276.632812,63243.609375,63194.578125,63147.898438,63159.117188,63106.253906,63085.679688,63066.425781,63056.375000,63053.980469,63041.859375,62997.101562,62992.511719,63008.003906,62995.453125,62988.156250,63004.906250</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>63611.824219,63593.546875,63556.679688,63555.671875,63528.570312,63521.828125,63484.648438,63475.519531,63467.007812,63441.695312,63398.507812,63414.234375,63364.148438,63365.078125,63354.437500,63352.882812,63339.171875,63341.171875,63334.679688,63349.476562,63357.960938,63324.531250,63339.761719,63367.859375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,44 @@
       </c>
       <c r="F25" t="n">
         <v>63960.296875</v>
+      </c>
+      <c r="G25" t="n">
+        <v>63329.359375</v>
+      </c>
+      <c r="H25" t="n">
+        <v>630.9375</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9962796185319853</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5253076743286842</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="n">
+        <v>63591.22265625</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,6 +2918,24 @@
           <t>63768.296875,63789.820312,63806.226562,63820.503906,63828.843750,63846.679688,63832.875000,63847.984375,63856.601562,63853.875000,63843.304688,63861.085938,63843.554688,63848.179688,63860.328125,63857.914062,63873.238281,63879.007812,63893.152344,63908.437500,63929.914062,63924.304688,63934.199219,63960.296875</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>63762.019531,63713.621094,63786.769531,63650.691406,63767.031250,63730.500000,64052.339844,64079.988281,64175.898438,64066.441406,63780.558594,63296.710938,63368.640625,63427.449219,63398.820312,63309.609375,63345.718750,63535.468750,63403.191406,63361.570312,63413.058594,63489.839844,63385.511719,63329.359375</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6.277344,76.199218,19.457031,169.812500,61.812500,116.179688,219.464844,232.003906,319.296875,212.566406,62.746094,564.375000,474.914063,420.730469,461.507812,548.304687,527.519531,343.539062,489.960938,546.867188,516.855468,434.464844,548.687500,630.937500</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.009845,0.119596,0.030503,0.266788,0.096935,0.182298,0.342634,0.362054,0.497534,0.331791,0.098378,0.891634,0.749447,0.663326,0.727944,0.866069,0.832763,0.540704,0.772770,0.863090,0.815062,0.684306,0.865636,0.996280</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5253076743286842</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>63782.906250,63806.695312,63817.046875,63857.648438,63852.570312,63841.421875,63837.152344,63853.984375,63855.609375,63846.859375,63851.031250,63879.773438,63866.625000,63887.109375,63898.390625,63885.132812,63908.000000,63915.117188,63933.085938,63930.523438,63946.386719,63950.824219,63945.937500,63951.539062</t>
@@ -2893,6 +2949,49 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>63611.824219,63593.546875,63556.679688,63555.671875,63528.570312,63521.828125,63484.648438,63475.519531,63467.007812,63441.695312,63398.507812,63414.234375,63364.148438,63365.078125,63354.437500,63352.882812,63339.171875,63341.171875,63334.679688,63349.476562,63357.960938,63324.531250,63339.761719,63367.859375</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>63345.007812,63357.109375,63379.671875,63389.546875,63411.691406,63434.394531,63446.148438,63470.078125,63484.175781,63489.140625,63484.789062,63486.562500,63479.089844,63475.867188,63465.570312,63466.171875,63471.949219,63488.152344,63514.589844,63521.554688,63552.695312,63565.101562,63568.425781,63591.222656</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>63363.546875,63390.062500,63398.171875,63420.449219,63414.140625,63448.757812,63460.601562,63488.796875,63507.585938,63524.769531,63520.035156,63543.890625,63521.070312,63518.984375,63508.093750,63498.140625,63522.007812,63564.039062,63567.910156,63575.914062,63585.417969,63604.820312,63607.859375,63614.789062</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>63130.218750,63093.132812,63067.851562,63041.996094,63019.656250,63003.882812,62985.218750,62973.632812,62952.437500,62923.648438,62886.187500,62876.406250,62855.023438,62836.511719,62810.679688,62802.031250,62799.507812,62806.105469,62787.878906,62795.738281,62815.597656,62821.546875,62804.750000,62816.953125</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>63217.882812,63194.781250,63176.265625,63172.210938,63154.304688,63155.703125,63142.929688,63151.007812,63146.156250,63132.664062,63088.257812,63093.953125,63073.820312,63071.039062,63052.195312,63049.941406,63045.507812,63047.351562,63066.507812,63079.179688,63104.242188,63081.621094,63084.406250,63107.906250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,44 @@
       </c>
       <c r="F26" t="n">
         <v>63591.22265625</v>
+      </c>
+      <c r="G26" t="n">
+        <v>63483.828125</v>
+      </c>
+      <c r="H26" t="n">
+        <v>107.39453125</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1691683290404914</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3343285736400246</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:50</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="n">
+        <v>63643.0234375</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2979,6 +3017,24 @@
           <t>63345.007812,63357.109375,63379.671875,63389.546875,63411.691406,63434.394531,63446.148438,63470.078125,63484.175781,63489.140625,63484.789062,63486.562500,63479.089844,63475.867188,63465.570312,63466.171875,63471.949219,63488.152344,63514.589844,63521.554688,63552.695312,63565.101562,63568.425781,63591.222656</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>63580.261719,63627.449219,63806.000000,63875.761719,63803.980469,63708.019531,63718.121094,63582.410156,63414.898438,63621.640625,63653.039062,63801.511719,63358.121094,63092.441406,63070.019531,63235.828125,63335.078125,63349.179688,63409.171875,63463.339844,63425.351562,63480.941406,63511.089844,63483.828125</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>235.253907,270.339844,426.328125,486.214844,392.289063,273.625000,271.972656,112.332031,69.277343,132.500000,168.250000,314.949219,120.968750,383.425782,395.550781,230.343750,136.871094,138.972657,105.417969,58.214844,127.343750,84.160156,57.335937,107.394531</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.370011,0.424879,0.668163,0.761188,0.614835,0.429499,0.426837,0.176672,0.109245,0.208262,0.264324,0.493639,0.190929,0.607721,0.627161,0.364261,0.216106,0.219376,0.166250,0.091730,0.200777,0.132575,0.090277,0.169168</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3343285736400246</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>63363.546875,63390.062500,63398.171875,63420.449219,63414.140625,63448.757812,63460.601562,63488.796875,63507.585938,63524.769531,63520.035156,63543.890625,63521.070312,63518.984375,63508.093750,63498.140625,63522.007812,63564.039062,63567.910156,63575.914062,63585.417969,63604.820312,63607.859375,63614.789062</t>
@@ -2992,6 +3048,49 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>63217.882812,63194.781250,63176.265625,63172.210938,63154.304688,63155.703125,63142.929688,63151.007812,63146.156250,63132.664062,63088.257812,63093.953125,63073.820312,63071.039062,63052.195312,63049.941406,63045.507812,63047.351562,63066.507812,63079.179688,63104.242188,63081.621094,63084.406250,63107.906250</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:50</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>63477.554688,63495.609375,63503.882812,63517.023438,63521.617188,63533.867188,63548.398438,63555.058594,63558.296875,63570.535156,63560.839844,63550.187500,63543.265625,63536.265625,63526.144531,63547.226562,63548.531250,63567.250000,63590.886719,63592.742188,63608.765625,63628.343750,63638.828125,63643.023438</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>63489.019531,63493.156250,63511.914062,63518.890625,63532.355469,63549.648438,63566.730469,63565.019531,63599.015625,63576.863281,63592.207031,63612.078125,63592.570312,63566.335938,63545.710938,63583.300781,63580.734375,63623.386719,63649.816406,63639.386719,63650.757812,63643.289062,63664.242188,63661.101562</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>63268.039062,63231.539062,63186.210938,63158.320312,63113.687500,63088.046875,63072.867188,63049.375000,63029.851562,63017.062500,62984.574219,62969.625000,62950.734375,62929.968750,62909.812500,62925.921875,62917.855469,62921.546875,62909.261719,62917.710938,62928.875000,62946.179688,62941.250000,62926.589844</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>63353.929688,63334.769531,63299.843750,63292.679688,63249.378906,63248.414062,63240.074219,63226.109375,63225.125000,63208.109375,63169.707031,63168.707031,63150.503906,63138.070312,63131.601562,63147.800781,63136.316406,63132.226562,63160.781250,63163.988281,63174.511719,63183.117188,63191.054688,63179.550781</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,44 @@
       </c>
       <c r="F27" t="n">
         <v>63643.0234375</v>
+      </c>
+      <c r="G27" t="n">
+        <v>62957.44140625</v>
+      </c>
+      <c r="H27" t="n">
+        <v>685.58203125</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.088961075825963</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.046572713701928</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:49</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="n">
+        <v>63183.04296875</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3116,24 @@
           <t>63477.554688,63495.609375,63503.882812,63517.023438,63521.617188,63533.867188,63548.398438,63555.058594,63558.296875,63570.535156,63560.839844,63550.187500,63543.265625,63536.265625,63526.144531,63547.226562,63548.531250,63567.250000,63590.886719,63592.742188,63608.765625,63628.343750,63638.828125,63643.023438</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>63246.691406,63307.140625,63314.500000,62909.761719,62848.679688,62870.480469,62723.910156,62746.128906,62793.300781,62661.851562,62584.320312,62547.980469,62913.050781,63071.089844,62951.691406,62855.910156,62895.820312,62835.148438,62843.210938,62843.210938,62950.718750,62950.718750,62957.441406,62957.441406</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>230.863282,188.468750,189.382812,607.261719,672.937500,663.386719,824.488282,808.929688,764.996094,908.683593,976.519532,1002.207031,630.214844,465.175781,574.453125,691.316406,652.710938,732.101562,747.675782,749.531250,658.046875,677.625000,681.386719,685.582032</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.365020,0.297705,0.299114,0.965290,1.070727,1.055164,1.314472,1.289211,1.218277,1.450138,1.560326,1.602301,1.001724,0.737542,0.912530,1.099843,1.037765,1.165115,1.189748,1.192700,1.045337,1.076437,1.082297,1.088961</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1.046572713701928</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>63489.019531,63493.156250,63511.914062,63518.890625,63532.355469,63549.648438,63566.730469,63565.019531,63599.015625,63576.863281,63592.207031,63612.078125,63592.570312,63566.335938,63545.710938,63583.300781,63580.734375,63623.386719,63649.816406,63639.386719,63650.757812,63643.289062,63664.242188,63661.101562</t>
@@ -3091,6 +3147,49 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>63353.929688,63334.769531,63299.843750,63292.679688,63249.378906,63248.414062,63240.074219,63226.109375,63225.125000,63208.109375,63169.707031,63168.707031,63150.503906,63138.070312,63131.601562,63147.800781,63136.316406,63132.226562,63160.781250,63163.988281,63174.511719,63183.117188,63191.054688,63179.550781</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:49</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>62953.265625,62978.304688,62973.941406,62983.414062,62990.847656,63000.562500,62991.691406,62997.074219,62999.976562,63018.484375,63029.773438,63039.105469,63046.742188,63067.617188,63065.777344,63073.992188,63067.199219,63100.492188,63119.332031,63126.519531,63138.644531,63152.820312,63158.835938,63183.042969</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>62977.644531,63000.433594,63000.417969,62992.023438,63015.898438,63040.597656,63027.468750,63021.976562,63071.554688,63047.648438,63105.304688,63111.539062,63124.812500,63134.539062,63133.976562,63132.625000,63116.671875,63194.234375,63228.093750,63198.203125,63212.578125,63214.117188,63253.789062,63276.085938</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>62746.738281,62719.257812,62667.867188,62638.929688,62601.656250,62578.906250,62536.894531,62508.550781,62486.046875,62471.617188,62463.742188,62473.648438,62463.000000,62455.460938,62439.804688,62438.718750,62413.007812,62435.914062,62407.101562,62431.558594,62433.042969,62447.679688,62421.296875,62429.890625</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>62833.156250,62822.296875,62770.937500,62768.140625,62737.664062,62737.953125,62703.125000,62680.000000,62679.191406,62670.570312,62650.546875,62673.976562,62651.914062,62665.898438,62667.445312,62657.011719,62635.878906,62643.593750,62670.476562,62682.812500,62689.906250,62683.671875,62685.574219,62695.359375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,44 @@
       </c>
       <c r="F28" t="n">
         <v>63183.04296875</v>
+      </c>
+      <c r="G28" t="n">
+        <v>62996.96875</v>
+      </c>
+      <c r="H28" t="n">
+        <v>186.07421875</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2953701145342807</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.119090314743222</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:51</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="n">
+        <v>63086.69921875</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3215,24 @@
           <t>62953.265625,62978.304688,62973.941406,62983.414062,62990.847656,63000.562500,62991.691406,62997.074219,62999.976562,63018.484375,63029.773438,63039.105469,63046.742188,63067.617188,63065.777344,63073.992188,63067.199219,63100.492188,63119.332031,63126.519531,63138.644531,63152.820312,63158.835938,63183.042969</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>63071.390625,62988.390625,63052.019531,63016.101562,63045.539062,63005.660156,62869.070312,62957.640625,62976.031250,62949.218750,62985.929688,62985.921875,62966.421875,63022.949219,63024.058594,63000.339844,62989.121094,63051.378906,63030.671875,63030.671875,63012.929688,63012.929688,63012.929688,62996.968750</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>118.125000,10.085937,78.078125,32.687500,54.691407,5.097656,122.621093,39.433594,23.945312,69.265625,43.843750,53.183594,80.320313,44.667969,41.718750,73.652344,78.078125,49.113282,88.660156,95.847656,125.714843,139.890625,145.906250,186.074219</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.187288,0.016012,0.123831,0.051872,0.086749,0.008091,0.195042,0.062635,0.038023,0.110034,0.069609,0.084437,0.127561,0.070876,0.066195,0.116908,0.123955,0.077894,0.140662,0.152065,0.199506,0.222003,0.231550,0.295370</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.119090314743222</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>62977.644531,63000.433594,63000.417969,62992.023438,63015.898438,63040.597656,63027.468750,63021.976562,63071.554688,63047.648438,63105.304688,63111.539062,63124.812500,63134.539062,63133.976562,63132.625000,63116.671875,63194.234375,63228.093750,63198.203125,63212.578125,63214.117188,63253.789062,63276.085938</t>
@@ -3190,6 +3246,49 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>62833.156250,62822.296875,62770.937500,62768.140625,62737.664062,62737.953125,62703.125000,62680.000000,62679.191406,62670.570312,62650.546875,62673.976562,62651.914062,62665.898438,62667.445312,62657.011719,62635.878906,62643.593750,62670.476562,62682.812500,62689.906250,62683.671875,62685.574219,62695.359375</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:51</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>62999.250000,63009.414062,63008.890625,63015.765625,63023.656250,63022.890625,63009.585938,63020.902344,63021.996094,63026.691406,63027.691406,63031.429688,63030.468750,63046.769531,63036.421875,63042.671875,63045.398438,63055.816406,63062.519531,63066.851562,63071.343750,63075.992188,63075.128906,63086.699219</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>63009.281250,63027.390625,63019.394531,63012.437500,63044.867188,63051.265625,63040.082031,63043.460938,63082.417969,63070.921875,63081.656250,63114.351562,63121.578125,63115.835938,63122.250000,63140.570312,63141.789062,63182.652344,63184.320312,63166.902344,63166.523438,63177.476562,63179.457031,63193.273438</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>62907.953125,62881.199219,62858.421875,62854.953125,62834.343750,62813.656250,62785.976562,62780.203125,62753.617188,62742.984375,62723.359375,62726.421875,62702.226562,62715.425781,62679.140625,62686.242188,62678.882812,62692.421875,62662.945312,62675.437500,62668.152344,62667.910156,62644.265625,62635.976562</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>62947.453125,62937.515625,62912.734375,62909.507812,62896.800781,62893.648438,62856.742188,62857.492188,62858.921875,62837.929688,62817.687500,62829.144531,62806.792969,62822.179688,62810.898438,62804.605469,62799.062500,62803.609375,62812.417969,62816.664062,62803.523438,62796.312500,62783.929688,62789.914062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,44 @@
       </c>
       <c r="F29" t="n">
         <v>63086.69921875</v>
+      </c>
+      <c r="G29" t="n">
+        <v>63106.4609375</v>
+      </c>
+      <c r="H29" t="n">
+        <v>19.76171875</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.03131488988040671</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1290365377619963</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:22</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>63071.140625</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3314,24 @@
           <t>62999.250000,63009.414062,63008.890625,63015.765625,63023.656250,63022.890625,63009.585938,63020.902344,63021.996094,63026.691406,63027.691406,63031.429688,63030.468750,63046.769531,63036.421875,63042.671875,63045.398438,63055.816406,63062.519531,63066.851562,63071.343750,63075.992188,63075.128906,63086.699219</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>63054.449219,63059.429688,63016.929688,62997.828125,62993.718750,62991.230469,63001.910156,62917.519531,62940.191406,62945.320312,62948.000000,62993.628906,63034.539062,63070.031250,63186.921875,63087.421875,63074.289062,63040.171875,63000.730469,62862.800781,62730.320312,62840.550781,62840.550781,63106.460938</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>55.199219,50.015625,8.039062,17.937500,29.937500,31.660156,7.675782,103.382813,81.804688,81.371093,79.691406,37.800782,4.070312,23.261719,150.500000,44.750000,28.890625,15.644531,61.789062,204.050781,341.023438,235.441407,234.578125,19.761718</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.087542,0.079315,0.012757,0.028473,0.047525,0.050261,0.012183,0.164315,0.129972,0.129273,0.126599,0.060007,0.006457,0.036882,0.238182,0.070933,0.045804,0.024817,0.098077,0.324597,0.543634,0.374665,0.373291,0.031315</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1290365377619963</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>63009.281250,63027.390625,63019.394531,63012.437500,63044.867188,63051.265625,63040.082031,63043.460938,63082.417969,63070.921875,63081.656250,63114.351562,63121.578125,63115.835938,63122.250000,63140.570312,63141.789062,63182.652344,63184.320312,63166.902344,63166.523438,63177.476562,63179.457031,63193.273438</t>
@@ -3289,6 +3345,49 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>62947.453125,62937.515625,62912.734375,62909.507812,62896.800781,62893.648438,62856.742188,62857.492188,62858.921875,62837.929688,62817.687500,62829.144531,62806.792969,62822.179688,62810.898438,62804.605469,62799.062500,62803.609375,62812.417969,62816.664062,62803.523438,62796.312500,62783.929688,62789.914062</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:22</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>63104.636719,63107.273438,63098.046875,63084.875000,63086.976562,63087.679688,63076.609375,63087.226562,63074.375000,63077.011719,63064.160156,63070.453125,63070.492188,63075.531250,63065.320312,63072.886719,63064.562500,63069.648438,63069.652344,63073.472656,63076.367188,63069.289062,63067.015625,63071.140625</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>63130.679688,63115.292969,63116.617188,63088.421875,63109.308594,63107.218750,63120.964844,63125.082031,63124.445312,63110.925781,63108.074219,63130.367188,63150.988281,63132.531250,63117.179688,63140.402344,63140.121094,63174.921875,63155.117188,63166.132812,63141.687500,63167.359375,63151.734375,63158.742188</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>62946.128906,62912.371094,62864.484375,62825.492188,62808.289062,62778.070312,62749.945312,62736.945312,62711.554688,62702.953125,62686.378906,62691.242188,62686.734375,62688.972656,62661.421875,62666.320312,62636.054688,62645.531250,62612.312500,62614.773438,62614.058594,62590.984375,62585.343750,62579.507812</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>63002.058594,62986.710938,62947.093750,62914.960938,62894.578125,62890.968750,62862.339844,62851.210938,62842.171875,62827.343750,62798.312500,62824.218750,62815.390625,62820.539062,62814.960938,62811.515625,62781.789062,62789.531250,62781.414062,62783.839844,62773.789062,62758.136719,62750.820312,62754.800781</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,44 @@
       </c>
       <c r="F30" t="n">
         <v>63071.140625</v>
+      </c>
+      <c r="G30" t="n">
+        <v>64227.94921875</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1156.80859375</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.801098443623192</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.203413043595197</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:42</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="n">
+        <v>64238.8828125</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,6 +3413,24 @@
           <t>63104.636719,63107.273438,63098.046875,63084.875000,63086.976562,63087.679688,63076.609375,63087.226562,63074.375000,63077.011719,63064.160156,63070.453125,63070.492188,63075.531250,63065.320312,63072.886719,63064.562500,63069.648438,63069.652344,63073.472656,63076.367188,63069.289062,63067.015625,63071.140625</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>63335.738281,63367.808594,63479.980469,63456.601562,63603.339844,63461.460938,63307.859375,63246.199219,63627.281250,63559.890625,63478.250000,63601.390625,63830.781250,64139.699219,64060.351562,64276.808594,64380.578125,64266.441406,64341.769531,64337.371094,64337.371094,64322.289062,64322.289062,64227.949219</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>231.101562,260.535156,381.933594,371.726562,516.363282,373.781250,231.250000,158.972657,552.906250,482.878906,414.089844,530.937500,760.289062,1064.167969,995.031250,1203.921875,1316.015625,1196.792968,1272.117187,1263.898438,1261.003906,1253.000000,1255.273438,1156.808594</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.364883,0.411147,0.601660,0.585797,0.811849,0.588989,0.365279,0.251355,0.868977,0.759723,0.652333,0.834789,1.191101,1.659141,1.553272,1.873027,2.044119,1.862236,1.977125,1.964486,1.959987,1.948003,1.951537,1.801098</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1.203413043595197</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>63130.679688,63115.292969,63116.617188,63088.421875,63109.308594,63107.218750,63120.964844,63125.082031,63124.445312,63110.925781,63108.074219,63130.367188,63150.988281,63132.531250,63117.179688,63140.402344,63140.121094,63174.921875,63155.117188,63166.132812,63141.687500,63167.359375,63151.734375,63158.742188</t>
@@ -3388,6 +3444,49 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>63002.058594,62986.710938,62947.093750,62914.960938,62894.578125,62890.968750,62862.339844,62851.210938,62842.171875,62827.343750,62798.312500,62824.218750,62815.390625,62820.539062,62814.960938,62811.515625,62781.789062,62789.531250,62781.414062,62783.839844,62773.789062,62758.136719,62750.820312,62754.800781</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:42</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>64239.523438,64255.976562,64257.402344,64258.718750,64252.945312,64261.445312,64255.039062,64272.757812,64261.980469,64249.445312,64238.906250,64233.937500,64226.121094,64230.730469,64228.132812,64233.523438,64231.398438,64243.757812,64264.515625,64263.636719,64258.500000,64260.687500,64253.625000,64238.882812</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>64226.328125,64240.421875,64252.179688,64227.578125,64228.265625,64212.414062,64213.433594,64258.894531,64226.359375,64207.929688,64215.953125,64179.386719,64179.453125,64202.148438,64177.835938,64244.554688,64214.089844,64223.195312,64207.980469,64270.785156,64240.367188,64296.718750,64218.917969,64201.687500</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>64003.066406,63971.832031,63909.953125,63860.125000,63808.707031,63769.210938,63717.445312,63722.308594,63670.710938,63619.226562,63570.808594,63562.375000,63550.812500,63522.906250,63489.820312,63471.339844,63446.531250,63459.312500,63424.941406,63389.414062,63363.187500,63359.609375,63349.281250,63326.503906</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>64092.640625,64073.984375,64036.199219,64010.679688,63963.621094,63946.996094,63905.476562,63900.492188,63880.742188,63836.636719,63802.632812,63787.402344,63772.968750,63773.656250,63743.617188,63733.960938,63711.257812,63727.121094,63727.171875,63726.632812,63690.582031,63658.375000,63654.570312,63643.296875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1595,44 @@
       </c>
       <c r="F31" t="n">
         <v>64238.8828125</v>
+      </c>
+      <c r="G31" t="n">
+        <v>64360.05078125</v>
+      </c>
+      <c r="H31" t="n">
+        <v>121.16796875</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1882658066287602</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.3483452745153985</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:26</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>64456.578125</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3512,24 @@
           <t>64239.523438,64255.976562,64257.402344,64258.718750,64252.945312,64261.445312,64255.039062,64272.757812,64261.980469,64249.445312,64238.906250,64233.937500,64226.121094,64230.730469,64228.132812,64233.523438,64231.398438,64243.757812,64264.515625,64263.636719,64258.500000,64260.687500,64253.625000,64238.882812</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>64036.128906,64117.210938,64149.691406,64169.460938,64266.410156,64139.781250,64228.640625,64110.011719,64134.539062,64288.179688,64161.671875,64155.929688,64668.140625,64808.000000,64795.179688,64629.558594,64737.171875,64603.929688,64538.480469,64556.320312,64556.320312,64445.429688,64445.429688,64360.050781</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>203.394532,138.765625,107.710938,89.257812,13.464844,121.664062,26.398437,162.746093,127.441407,38.734375,77.234375,78.007812,442.019531,577.269531,567.046875,396.035156,505.773437,360.171875,273.964844,292.683593,297.820312,184.742188,191.804688,121.167969</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.317625,0.216425,0.167906,0.139097,0.020952,0.189686,0.041101,0.253854,0.198709,0.060251,0.120375,0.121591,0.683520,0.890738,0.875137,0.612777,0.781272,0.557508,0.424498,0.453377,0.461334,0.286665,0.297623,0.188266</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.3483452745153985</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>64226.328125,64240.421875,64252.179688,64227.578125,64228.265625,64212.414062,64213.433594,64258.894531,64226.359375,64207.929688,64215.953125,64179.386719,64179.453125,64202.148438,64177.835938,64244.554688,64214.089844,64223.195312,64207.980469,64270.785156,64240.367188,64296.718750,64218.917969,64201.687500</t>
@@ -3487,6 +3543,49 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>64092.640625,64073.984375,64036.199219,64010.679688,63963.621094,63946.996094,63905.476562,63900.492188,63880.742188,63836.636719,63802.632812,63787.402344,63772.968750,63773.656250,63743.617188,63733.960938,63711.257812,63727.121094,63727.171875,63726.632812,63690.582031,63658.375000,63654.570312,63643.296875</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:26</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>64385.515625,64397.316406,64395.339844,64405.980469,64412.703125,64423.835938,64447.394531,64453.484375,64472.570312,64467.875000,64482.585938,64480.203125,64477.078125,64485.359375,64491.523438,64491.812500,64492.269531,64503.218750,64501.203125,64486.941406,64481.796875,64488.921875,64481.164062,64456.578125</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>64372.375000,64403.710938,64399.343750,64386.792969,64379.445312,64415.070312,64417.363281,64465.335938,64456.578125,64459.453125,64465.492188,64432.781250,64432.191406,64434.390625,64452.398438,64457.234375,64445.742188,64425.250000,64441.171875,64471.156250,64467.882812,64491.242188,64428.472656,64435.515625</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>64201.984375,64156.812500,64102.578125,64074.449219,64042.914062,64017.867188,63993.437500,63963.578125,63966.257812,63932.476562,63905.976562,63898.687500,63892.351562,63857.460938,63820.085938,63792.734375,63765.640625,63772.601562,63715.492188,63684.210938,63661.343750,63650.433594,63634.851562,63600.019531</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>64272.648438,64241.699219,64214.636719,64203.863281,64177.773438,64169.722656,64162.402344,64142.605469,64153.609375,64127.000000,64128.863281,64123.488281,64096.523438,64097.652344,64074.441406,64057.328125,64040.160156,64044.187500,64027.914062,64016.449219,63994.968750,63972.097656,63961.492188,63928.062500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,44 @@
       </c>
       <c r="F32" t="n">
         <v>64456.578125</v>
+      </c>
+      <c r="G32" t="n">
+        <v>69566.4375</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5109.859375</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.345294021991568</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.163970751874906</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:26</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="n">
+        <v>68954.5625</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3611,24 @@
           <t>64385.515625,64397.316406,64395.339844,64405.980469,64412.703125,64423.835938,64447.394531,64453.484375,64472.570312,64467.875000,64482.585938,64480.203125,64477.078125,64485.359375,64491.523438,64491.812500,64492.269531,64503.218750,64501.203125,64486.941406,64481.796875,64488.921875,64481.164062,64456.578125</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>64295.839844,64269.359375,64255.101562,64185.230469,64289.820312,64243.550781,64357.121094,64371.570312,64393.800781,64459.109375,64830.890625,64966.718750,65886.250000,68519.632812,68453.976562,68168.312500,68389.117188,68406.132812,69043.250000,69700.000000,69219.546875,69300.007812,69387.773438,69566.437500</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>89.675781,127.957031,140.238282,220.750000,122.882812,180.285157,90.273437,81.914062,78.769531,8.765625,348.304687,486.515625,1409.171875,4034.273438,3962.453125,3676.500000,3896.847657,3902.914062,4542.046875,5213.058594,4737.750000,4811.085938,4906.609375,5109.859375</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.139474,0.199095,0.218252,0.343926,0.191139,0.280628,0.140270,0.127252,0.122325,0.013599,0.537251,0.748869,2.138795,5.887763,5.788492,5.393268,5.698052,5.705503,6.578553,7.479281,6.844526,6.942403,7.071288,7.345294</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3.163970751874906</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>64372.375000,64403.710938,64399.343750,64386.792969,64379.445312,64415.070312,64417.363281,64465.335938,64456.578125,64459.453125,64465.492188,64432.781250,64432.191406,64434.390625,64452.398438,64457.234375,64445.742188,64425.250000,64441.171875,64471.156250,64467.882812,64491.242188,64428.472656,64435.515625</t>
@@ -3586,6 +3642,49 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>64272.648438,64241.699219,64214.636719,64203.863281,64177.773438,64169.722656,64162.402344,64142.605469,64153.609375,64127.000000,64128.863281,64123.488281,64096.523438,64097.652344,64074.441406,64057.328125,64040.160156,64044.187500,64027.914062,64016.449219,63994.968750,63972.097656,63961.492188,63928.062500</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:26</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69550.109375,69554.078125,69486.984375,69511.015625,69451.492188,69477.328125,69457.265625,69398.546875,69363.976562,69296.414062,69255.851562,69215.468750,69133.703125,69192.382812,69197.601562,69147.921875,69122.796875,69107.546875,69114.039062,69039.359375,69038.648438,69038.976562,69014.062500,68954.562500</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>69426.585938,69397.953125,69465.640625,69365.609375,69190.375000,69185.125000,69112.992188,69178.578125,68951.882812,69007.562500,68896.015625,68737.203125,68728.539062,68756.359375,68756.421875,68842.664062,68664.507812,68715.343750,68621.289062,68569.992188,68548.062500,68669.703125,68554.390625,68457.007812</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>68920.765625,68756.484375,68512.703125,68290.515625,68127.515625,67969.328125,67758.484375,67578.875000,67565.617188,67419.937500,67294.914062,67071.359375,67119.203125,66991.757812,66896.859375,66843.718750,66754.843750,66689.171875,66610.335938,66390.609375,66410.242188,66334.343750,66266.898438,66236.546875</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>69162.335938,69071.351562,68886.062500,68823.335938,68626.093750,68541.531250,68451.507812,68303.242188,68253.031250,68148.484375,68029.359375,67962.882812,67841.968750,67825.570312,67753.218750,67742.265625,67671.656250,67622.015625,67590.578125,67478.945312,67478.625000,67371.250000,67366.062500,67286.218750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1671,44 @@
       </c>
       <c r="F33" t="n">
         <v>68954.5625</v>
+      </c>
+      <c r="G33" t="n">
+        <v>75464.0234375</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6509.4609375</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8.625912906553673</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.558564960401447</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:47</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="n">
+        <v>73476.8046875</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3710,24 @@
           <t>69550.109375,69554.078125,69486.984375,69511.015625,69451.492188,69477.328125,69457.265625,69398.546875,69363.976562,69296.414062,69255.851562,69215.468750,69133.703125,69192.382812,69197.601562,69147.921875,69122.796875,69107.546875,69114.039062,69039.359375,69038.648438,69038.976562,69014.062500,68954.562500</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>69258.562500,69139.992188,69442.523438,69356.000000,69813.992188,69783.609375,71527.937500,71740.890625,71943.578125,71875.273438,71894.507812,71639.273438,71780.289062,72439.671875,72808.562500,72715.328125,72410.921875,72627.921875,72660.226562,72725.632812,72663.906250,72998.320312,73686.929688,75464.023438</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>291.546875,414.085938,44.460938,155.015625,362.499999,306.281250,2070.671875,2342.343750,2579.601563,2578.859376,2638.656251,2423.804688,2646.585938,3247.289063,3610.960938,3567.406250,3288.125000,3520.375000,3546.187501,3686.273438,3625.257812,3959.343751,4672.867188,6509.460938</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.420954,0.598909,0.064026,0.223507,0.519237,0.438901,2.894913,3.265005,3.585590,3.587965,3.670178,3.383346,3.687065,4.482750,4.959528,4.905989,4.540924,4.847137,4.880507,5.068740,4.989076,5.423883,6.341514,8.625913</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3.558564960401447</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>69426.585938,69397.953125,69465.640625,69365.609375,69190.375000,69185.125000,69112.992188,69178.578125,68951.882812,69007.562500,68896.015625,68737.203125,68728.539062,68756.359375,68756.421875,68842.664062,68664.507812,68715.343750,68621.289062,68569.992188,68548.062500,68669.703125,68554.390625,68457.007812</t>
@@ -3685,6 +3741,49 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>69162.335938,69071.351562,68886.062500,68823.335938,68626.093750,68541.531250,68451.507812,68303.242188,68253.031250,68148.484375,68029.359375,67962.882812,67841.968750,67825.570312,67753.218750,67742.265625,67671.656250,67622.015625,67590.578125,67478.945312,67478.625000,67371.250000,67366.062500,67286.218750</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:47</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>75680.648438,75754.093750,75721.789062,75720.531250,75729.304688,75771.296875,75705.320312,75657.328125,75542.515625,75399.687500,75305.125000,75214.351562,74887.625000,74746.265625,74676.343750,74399.875000,74311.109375,74154.054688,74089.859375,74007.593750,73816.851562,73650.562500,73579.312500,73476.804688</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>75539.562500,75544.257812,75687.953125,75438.390625,75436.375000,75384.328125,75069.289062,75315.500000,74906.187500,74936.132812,74749.250000,74459.156250,74262.109375,74292.632812,74111.328125,74027.960938,73827.843750,73573.156250,73497.289062,73304.171875,73126.156250,73150.539062,72710.703125,72791.859375</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>74522.085938,74235.250000,73798.718750,73291.687500,72966.437500,72700.289062,72070.125000,71727.296875,71509.937500,71183.312500,70808.984375,70417.265625,70250.296875,69718.085938,69499.312500,69176.789062,68924.171875,68625.726562,68346.171875,68009.968750,67816.109375,67655.203125,67492.734375,67481.492188</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>74956.359375,74819.187500,74471.171875,74279.335938,74004.117188,73807.945312,73527.578125,73184.976562,72948.195312,72716.843750,72459.351562,72297.664062,71807.718750,71580.539062,71324.765625,71112.296875,70873.609375,70638.234375,70479.382812,70278.460938,70010.468750,69822.789062,69712.554688,69633.468750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,44 @@
       </c>
       <c r="F34" t="n">
         <v>73476.8046875</v>
+      </c>
+      <c r="G34" t="n">
+        <v>77995.0078125</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4518.203125</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.792938870987436</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.201042607096483</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:47</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="n">
+        <v>77676.5859375</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,6 +3809,24 @@
           <t>75680.648438,75754.093750,75721.789062,75720.531250,75729.304688,75771.296875,75705.320312,75657.328125,75542.515625,75399.687500,75305.125000,75214.351562,74887.625000,74746.265625,74676.343750,74399.875000,74311.109375,74154.054688,74089.859375,74007.593750,73816.851562,73650.562500,73579.312500,73476.804688</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>74412.851562,74478.953125,74999.992188,75438.093750,75615.789062,76288.117188,79250.007812,77888.179688,77812.820312,76709.632812,77188.773438,77251.867188,77369.320312,77191.796875,77451.343750,77370.281250,77110.523438,77003.921875,77497.968750,78546.851562,78546.851562,77934.062500,77934.062500,77995.007812</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1267.796876,1275.140625,721.796874,282.437500,113.515626,516.820312,3544.687501,2230.851562,2270.304688,1309.945312,1883.648438,2037.515626,2481.695312,2445.531250,2775.000000,2970.406250,2799.414062,2849.867187,3408.109375,4539.257812,4730.000001,4283.500000,4354.750000,4518.203124</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.703734,1.712082,0.962396,0.374396,0.150122,0.677458,4.472791,2.864172,2.917649,1.707667,2.440314,2.637497,3.207596,3.168123,3.582895,3.839208,3.630392,3.700938,4.397676,5.779045,6.021884,5.496313,5.587736,5.792939</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3.201042607096483</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>75539.562500,75544.257812,75687.953125,75438.390625,75436.375000,75384.328125,75069.289062,75315.500000,74906.187500,74936.132812,74749.250000,74459.156250,74262.109375,74292.632812,74111.328125,74027.960938,73827.843750,73573.156250,73497.289062,73304.171875,73126.156250,73150.539062,72710.703125,72791.859375</t>
@@ -3784,6 +3840,49 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>74956.359375,74819.187500,74471.171875,74279.335938,74004.117188,73807.945312,73527.578125,73184.976562,72948.195312,72716.843750,72459.351562,72297.664062,71807.718750,71580.539062,71324.765625,71112.296875,70873.609375,70638.234375,70479.382812,70278.460938,70010.468750,69822.789062,69712.554688,69633.468750</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:47</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>78108.781250,78115.500000,78118.546875,78169.671875,78096.328125,78122.578125,78103.218750,78108.968750,78107.296875,78002.406250,77976.468750,78001.468750,77916.812500,77782.578125,77838.359375,77767.250000,77774.125000,77768.101562,77689.015625,77639.218750,77639.625000,77622.843750,77734.953125,77676.585938</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>78044.828125,77999.398438,78129.929688,78041.500000,77923.953125,78007.671875,77760.484375,78031.671875,77886.398438,77792.632812,77646.218750,77537.250000,77404.562500,77528.609375,77429.000000,77403.906250,77389.921875,77194.234375,77287.859375,77211.359375,77226.765625,77228.625000,76905.562500,77078.171875</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>77412.492188,77358.468750,77086.609375,76954.390625,76674.890625,76613.273438,76271.750000,75979.750000,75986.562500,75782.500000,75561.976562,75278.000000,75326.890625,74915.507812,74784.414062,74695.562500,74470.187500,74292.843750,73924.226562,73598.625000,73550.937500,73428.640625,73375.750000,73317.914062</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>77687.187500,77624.609375,77432.218750,77494.953125,77219.960938,77186.156250,77079.000000,76921.828125,76884.734375,76746.804688,76616.781250,76538.171875,76333.468750,76163.281250,76047.687500,76040.265625,75890.296875,75806.375000,75588.484375,75484.117188,75396.375000,75285.757812,75366.109375,75252.578125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,44 @@
       </c>
       <c r="F35" t="n">
         <v>77676.5859375</v>
+      </c>
+      <c r="G35" t="n">
+        <v>77254.09375</v>
+      </c>
+      <c r="H35" t="n">
+        <v>422.4921875</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5468864716311554</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8277835162548012</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:42</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="n">
+        <v>77064.359375</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3908,24 @@
           <t>78108.781250,78115.500000,78118.546875,78169.671875,78096.328125,78122.578125,78103.218750,78108.968750,78107.296875,78002.406250,77976.468750,78001.468750,77916.812500,77782.578125,77838.359375,77767.250000,77774.125000,77768.101562,77689.015625,77639.218750,77639.625000,77622.843750,77734.953125,77676.585938</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>78462.796875,78402.617188,78475.710938,77351.187500,77477.250000,77286.242188,77195.492188,77049.398438,76964.882812,77114.351562,77300.007812,77277.296875,76995.593750,76970.562500,77282.460938,77270.523438,77261.921875,77419.937500,77312.976562,76847.367188,76979.992188,77289.000000,77289.000000,77254.093750</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>354.015625,287.117188,357.164062,818.484375,619.078125,836.335938,907.726562,1059.570312,1142.414062,888.054688,676.460938,724.171875,921.218750,812.015625,555.898438,496.726562,512.203125,348.164062,376.039062,791.851562,659.632812,333.843750,445.953125,422.492188</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.451189,0.366209,0.455127,1.058141,0.799045,1.082128,1.175880,1.375183,1.484332,1.151608,0.875111,0.937108,1.196456,1.054969,0.719307,0.642841,0.662944,0.449709,0.486385,1.030421,0.856889,0.431942,0.576994,0.546886</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8277835162548012</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>78044.828125,77999.398438,78129.929688,78041.500000,77923.953125,78007.671875,77760.484375,78031.671875,77886.398438,77792.632812,77646.218750,77537.250000,77404.562500,77528.609375,77429.000000,77403.906250,77389.921875,77194.234375,77287.859375,77211.359375,77226.765625,77228.625000,76905.562500,77078.171875</t>
@@ -3883,6 +3939,49 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>77687.187500,77624.609375,77432.218750,77494.953125,77219.960938,77186.156250,77079.000000,76921.828125,76884.734375,76746.804688,76616.781250,76538.171875,76333.468750,76163.281250,76047.687500,76040.265625,75890.296875,75806.375000,75588.484375,75484.117188,75396.375000,75285.757812,75366.109375,75252.578125</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:42</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>77232.859375,77210.015625,77181.281250,77246.265625,77245.718750,77265.984375,77201.125000,77170.687500,77178.437500,77106.156250,77119.859375,77141.648438,77136.500000,77068.812500,77092.312500,77129.835938,77152.437500,77114.085938,77047.546875,77121.179688,77097.859375,77105.359375,77060.328125,77064.359375</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>77165.937500,77129.953125,77083.468750,77156.828125,77122.171875,77288.046875,76978.437500,77024.742188,77176.945312,77066.875000,77015.468750,76955.648438,76836.656250,76912.414062,76756.859375,76909.851562,76709.421875,76810.093750,76772.664062,76817.585938,76921.750000,76830.789062,76687.250000,76781.335938</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>76949.187500,76875.062500,76742.359375,76760.632812,76568.484375,76562.484375,76410.421875,76246.796875,76275.500000,76175.812500,76099.835938,75886.570312,75868.664062,75671.656250,75623.101562,75640.070312,75518.015625,75442.070312,75145.156250,75143.398438,75064.007812,74983.445312,74836.421875,74864.007812</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>77134.906250,77004.921875,76945.742188,76993.960938,76860.125000,76855.273438,76776.343750,76679.828125,76718.453125,76617.156250,76586.203125,76535.843750,76444.468750,76298.828125,76291.445312,76330.656250,76318.210938,76165.687500,76016.890625,76097.710938,75997.765625,75921.484375,75906.093750,75861.539062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,44 @@
       </c>
       <c r="F36" t="n">
         <v>77064.359375</v>
+      </c>
+      <c r="G36" t="n">
+        <v>77230.1796875</v>
+      </c>
+      <c r="H36" t="n">
+        <v>165.8203125</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2147092149351022</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5882646077469477</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:21</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="n">
+        <v>76651.7734375</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +4007,24 @@
           <t>77232.859375,77210.015625,77181.281250,77246.265625,77245.718750,77265.984375,77201.125000,77170.687500,77178.437500,77106.156250,77119.859375,77141.648438,77136.500000,77068.812500,77092.312500,77129.835938,77152.437500,77114.085938,77047.546875,77121.179688,77097.859375,77105.359375,77060.328125,77064.359375</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>77064.679688,76916.992188,76599.437500,76058.070312,76090.820312,75986.992188,76464.937500,76540.000000,76776.937500,77288.156250,77201.593750,77477.242188,77179.281250,77141.093750,77405.671875,77171.648438,77325.000000,77328.296875,77393.187500,77832.500000,77600.656250,77725.593750,77668.242188,77230.179688</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>168.179688,293.023438,581.843750,1188.195312,1154.898438,1278.992188,736.187500,630.687500,401.500000,182.000000,81.734375,335.593749,42.781250,72.281250,313.359375,41.812499,172.562500,214.210937,345.640625,711.320312,502.796875,620.234375,607.914062,165.820312</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.218232,0.380961,0.759593,1.562221,1.517789,1.683173,0.962778,0.823997,0.522943,0.235482,0.105871,0.433151,0.055431,0.093700,0.404827,0.054181,0.223165,0.277015,0.446603,0.913912,0.647929,0.797980,0.782706,0.214709</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5882646077469477</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>77165.937500,77129.953125,77083.468750,77156.828125,77122.171875,77288.046875,76978.437500,77024.742188,77176.945312,77066.875000,77015.468750,76955.648438,76836.656250,76912.414062,76756.859375,76909.851562,76709.421875,76810.093750,76772.664062,76817.585938,76921.750000,76830.789062,76687.250000,76781.335938</t>
@@ -3982,6 +4038,49 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>77134.906250,77004.921875,76945.742188,76993.960938,76860.125000,76855.273438,76776.343750,76679.828125,76718.453125,76617.156250,76586.203125,76535.843750,76444.468750,76298.828125,76291.445312,76330.656250,76318.210938,76165.687500,76016.890625,76097.710938,75997.765625,75921.484375,75906.093750,75861.539062</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:21</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>77225.726562,77144.640625,77074.835938,77196.437500,77115.578125,77094.031250,77068.867188,77047.460938,77035.062500,76979.781250,76967.226562,76987.109375,76952.921875,76880.039062,76861.078125,76890.570312,76874.593750,76798.171875,76741.421875,76825.023438,76737.968750,76746.148438,76620.687500,76651.773438</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>77113.046875,77069.109375,76989.406250,77108.000000,77040.640625,77161.734375,76889.117188,76902.179688,76972.906250,76964.945312,76871.281250,76852.937500,76701.546875,76706.226562,76588.398438,76756.250000,76343.554688,76495.187500,76484.867188,76587.851562,76528.726562,76510.304688,76334.750000,76461.109375</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>76743.843750,76588.250000,76404.210938,76515.320312,76208.773438,76061.171875,75972.898438,75850.609375,75722.734375,75615.218750,75509.687500,75416.703125,75359.085938,75160.156250,75035.320312,75070.726562,74932.765625,74823.507812,74626.054688,74733.765625,74575.023438,74515.335938,74299.312500,74324.546875</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>77001.609375,76804.210938,76699.250000,76784.156250,76546.164062,76464.320312,76334.148438,76254.414062,76245.921875,76127.492188,76050.835938,76007.406250,75899.203125,75770.312500,75704.234375,75709.367188,75686.960938,75530.406250,75440.359375,75621.031250,75453.507812,75387.210938,75261.242188,75266.031250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,44 @@
       </c>
       <c r="F37" t="n">
         <v>76651.7734375</v>
+      </c>
+      <c r="G37" t="n">
+        <v>79720.4765625</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3068.703125</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.849328625869628</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.888287958159358</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:43</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="n">
+        <v>79628.453125</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,6 +4106,24 @@
           <t>77225.726562,77144.640625,77074.835938,77196.437500,77115.578125,77094.031250,77068.867188,77047.460938,77035.062500,76979.781250,76967.226562,76987.109375,76952.921875,76880.039062,76861.078125,76890.570312,76874.593750,76798.171875,76741.421875,76825.023438,76737.968750,76746.148438,76620.687500,76651.773438</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>77466.328125,76933.460938,76893.226562,77159.593750,77459.132812,77297.867188,77032.906250,77540.882812,77608.859375,78434.023438,79137.039062,78562.398438,79484.320312,79079.500000,79041.039062,78744.937500,78926.492188,78744.359375,78913.781250,78868.007812,78868.007812,79743.828125,79743.828125,79720.476562</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>240.601563,211.179688,181.609376,36.843750,343.554688,203.835938,35.960938,493.421874,573.796875,1454.242188,2169.812501,1575.289062,2531.398438,2199.460938,2179.960938,1854.367188,2051.898438,1946.187500,2172.359375,2042.984374,2130.039062,2997.679687,3123.140625,3068.703124</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.310589,0.274497,0.236184,0.047750,0.443530,0.263702,0.046683,0.636338,0.739345,1.854096,2.741842,2.005144,3.184777,2.781329,2.758011,2.354903,2.599759,2.471526,2.752826,2.590384,2.700764,3.759137,3.916467,3.849329</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1.888287958159358</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>77113.046875,77069.109375,76989.406250,77108.000000,77040.640625,77161.734375,76889.117188,76902.179688,76972.906250,76964.945312,76871.281250,76852.937500,76701.546875,76706.226562,76588.398438,76756.250000,76343.554688,76495.187500,76484.867188,76587.851562,76528.726562,76510.304688,76334.750000,76461.109375</t>
@@ -4081,6 +4137,49 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>77001.609375,76804.210938,76699.250000,76784.156250,76546.164062,76464.320312,76334.148438,76254.414062,76245.921875,76127.492188,76050.835938,76007.406250,75899.203125,75770.312500,75704.234375,75709.367188,75686.960938,75530.406250,75440.359375,75621.031250,75453.507812,75387.210938,75261.242188,75266.031250</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:43</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>79715.531250,79701.062500,79672.828125,79844.921875,79692.953125,79788.406250,79785.359375,79802.859375,79770.796875,79773.093750,79732.156250,79839.890625,79735.953125,79699.156250,79721.500000,79818.968750,79709.273438,79665.031250,79582.921875,79702.203125,79605.562500,79582.921875,79545.078125,79628.453125</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>79609.625000,79641.109375,79649.703125,79760.140625,79662.648438,79729.687500,79525.109375,79696.296875,79622.023438,79603.726562,79624.609375,79537.203125,79434.296875,79508.828125,79453.609375,79641.437500,79231.382812,79272.281250,79314.273438,79350.789062,79337.125000,79390.390625,79158.789062,79436.351562</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>78932.046875,78875.156250,78699.546875,78855.835938,78487.273438,78419.687500,78367.593750,78283.750000,78098.734375,77977.718750,77833.703125,77824.312500,77726.906250,77549.562500,77486.351562,77637.296875,77351.945312,77333.781250,77061.859375,77171.171875,76976.851562,76909.812500,76776.601562,76868.312500</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>79285.390625,79184.593750,79090.093750,79248.765625,78950.304688,78959.984375,78887.750000,78820.796875,78799.109375,78684.859375,78585.671875,78623.015625,78503.835938,78372.125000,78341.046875,78442.539062,78312.984375,78189.578125,78077.203125,78251.632812,78039.773438,77938.359375,77929.562500,77973.093750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,44 @@
       </c>
       <c r="F38" t="n">
         <v>79628.453125</v>
+      </c>
+      <c r="G38" t="n">
+        <v>78824.7265625</v>
+      </c>
+      <c r="H38" t="n">
+        <v>803.7265625</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.019637615695027</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9045104332594235</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:08</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="n">
+        <v>78499.421875</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4205,24 @@
           <t>79715.531250,79701.062500,79672.828125,79844.921875,79692.953125,79788.406250,79785.359375,79802.859375,79770.796875,79773.093750,79732.156250,79839.890625,79735.953125,79699.156250,79721.500000,79818.968750,79709.273438,79665.031250,79582.921875,79702.203125,79605.562500,79582.921875,79545.078125,79628.453125</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>80634.398438,80468.968750,80348.070312,80702.000000,80533.773438,79674.210938,79905.812500,79177.828125,79293.179688,79118.992188,78966.960938,78627.359375,79225.007812,79506.226562,79153.296875,79234.101562,79135.679688,78923.812500,78184.046875,78550.578125,78823.531250,78632.359375,78632.359375,78824.726562</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>918.867188,767.906250,675.242188,857.078125,840.820312,114.195312,120.453125,625.031250,477.617188,654.101562,765.195312,1212.531250,510.945312,192.929688,568.203125,584.867188,573.593751,741.218750,1398.875000,1151.625000,782.031250,950.562500,912.718750,803.726562</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1.139547,0.954289,0.840396,1.062028,1.044059,0.143328,0.150744,0.789402,0.602343,0.826731,0.969007,1.542124,0.644929,0.242660,0.717851,0.738151,0.724823,0.939157,1.789208,1.466094,0.992129,1.208869,1.160742,1.019638</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9045104332594235</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>79609.625000,79641.109375,79649.703125,79760.140625,79662.648438,79729.687500,79525.109375,79696.296875,79622.023438,79603.726562,79624.609375,79537.203125,79434.296875,79508.828125,79453.609375,79641.437500,79231.382812,79272.281250,79314.273438,79350.789062,79337.125000,79390.390625,79158.789062,79436.351562</t>
@@ -4180,6 +4236,49 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>79285.390625,79184.593750,79090.093750,79248.765625,78950.304688,78959.984375,78887.750000,78820.796875,78799.109375,78684.859375,78585.671875,78623.015625,78503.835938,78372.125000,78341.046875,78442.539062,78312.984375,78189.578125,78077.203125,78251.632812,78039.773438,77938.359375,77929.562500,77973.093750</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:08</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>78818.640625,78724.593750,78730.453125,78710.625000,78670.539062,78608.656250,78589.765625,78578.140625,78564.843750,78499.843750,78516.390625,78523.453125,78510.859375,78424.789062,78476.882812,78503.421875,78467.312500,78419.390625,78447.234375,78460.625000,78479.203125,78410.546875,78407.218750,78499.421875</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>78637.125000,78617.125000,78613.828125,78715.460938,78720.445312,78575.093750,78404.500000,78381.562500,78485.851562,78444.679688,78463.984375,78247.078125,78223.781250,78252.421875,78250.515625,78315.640625,78236.328125,78084.710938,78222.171875,78239.101562,78314.093750,78229.656250,78206.085938,78323.046875</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>78103.820312,77967.281250,77884.593750,77917.421875,77689.609375,77536.218750,77491.476562,77412.843750,77232.945312,77061.015625,76934.171875,76849.226562,76801.859375,76647.992188,76612.375000,76668.343750,76456.015625,76347.984375,76168.000000,76138.414062,76183.031250,76013.289062,76050.007812,76113.539062</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>78418.015625,78239.476562,78211.671875,78195.015625,78049.421875,77929.218750,77863.492188,77765.593750,77807.429688,77622.640625,77545.375000,77481.031250,77440.382812,77285.796875,77295.601562,77346.695312,77289.523438,77112.695312,77068.953125,77129.156250,77117.179688,76953.718750,77014.843750,77052.406250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,44 @@
       </c>
       <c r="F39" t="n">
         <v>78499.421875</v>
+      </c>
+      <c r="G39" t="n">
+        <v>78893.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>394.078125</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4995064549043964</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.3128614854633781</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:14</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="n">
+        <v>79331.875</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,6 +4304,24 @@
           <t>78818.640625,78724.593750,78730.453125,78710.625000,78670.539062,78608.656250,78589.765625,78578.140625,78564.843750,78499.843750,78516.390625,78523.453125,78510.859375,78424.789062,78476.882812,78503.421875,78467.312500,78419.390625,78447.234375,78460.625000,78479.203125,78410.546875,78407.218750,78499.421875</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>79098.250000,79075.523438,78823.851562,79080.250000,78934.023438,78915.976562,78690.976562,78434.750000,78707.890625,78467.421875,78300.148438,78446.781250,77787.539062,78013.359375,77982.226562,78441.453125,78471.382812,78463.007812,78448.546875,78720.898438,78704.171875,79026.179688,78695.117188,78893.500000</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>279.609375,350.929688,93.398438,369.625000,263.484376,307.320312,101.210938,143.390625,143.046875,32.421875,216.242188,76.671875,723.320312,411.429687,494.656249,61.968750,4.070312,43.617188,1.312500,260.273438,224.968750,615.632812,287.898438,394.078125</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.353496,0.443791,0.118490,0.467405,0.333803,0.389427,0.128618,0.182815,0.181744,0.041319,0.276171,0.097737,0.929867,0.527384,0.634319,0.079000,0.005187,0.055589,0.001673,0.330628,0.285841,0.779024,0.365840,0.499506</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.3128614854633781</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>78637.125000,78617.125000,78613.828125,78715.460938,78720.445312,78575.093750,78404.500000,78381.562500,78485.851562,78444.679688,78463.984375,78247.078125,78223.781250,78252.421875,78250.515625,78315.640625,78236.328125,78084.710938,78222.171875,78239.101562,78314.093750,78229.656250,78206.085938,78323.046875</t>
@@ -4279,6 +4335,49 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>78418.015625,78239.476562,78211.671875,78195.015625,78049.421875,77929.218750,77863.492188,77765.593750,77807.429688,77622.640625,77545.375000,77481.031250,77440.382812,77285.796875,77295.601562,77346.695312,77289.523438,77112.695312,77068.953125,77129.156250,77117.179688,76953.718750,77014.843750,77052.406250</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:14</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>79816.695312,79725.515625,79817.671875,79821.593750,79839.906250,79776.781250,79795.851562,79739.421875,79774.015625,79658.265625,79731.007812,79716.593750,79740.125000,79573.312500,79623.671875,79573.453125,79608.593750,79497.273438,79500.984375,79476.054688,79511.898438,79373.054688,79353.031250,79331.875000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>79701.656250,79802.664062,79794.648438,79797.796875,79884.421875,79756.531250,79676.296875,79569.906250,79763.781250,79665.570312,79775.218750,79503.015625,79490.101562,79627.875000,79471.828125,79466.812500,79435.671875,79249.984375,79409.625000,79338.890625,79254.140625,79260.437500,79318.625000,79173.054688</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>79112.062500,78995.093750,79033.640625,79164.367188,78976.156250,78839.492188,78913.515625,78894.703125,78724.539062,78518.156250,78527.914062,78552.445312,78502.914062,78212.195312,78186.500000,78139.601562,78004.187500,78008.093750,77815.460938,77648.046875,77757.625000,77470.781250,77479.695312,77476.375000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>79395.859375,79267.398438,79397.750000,79330.218750,79301.890625,79133.523438,79199.546875,79085.906250,79192.546875,78969.820312,78997.187500,78967.781250,78950.250000,78660.351562,78724.960938,78684.109375,78648.960938,78562.265625,78427.296875,78416.929688,78391.773438,78174.109375,78147.921875,78156.031250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +1937,44 @@
       </c>
       <c r="F40" t="n">
         <v>79331.875</v>
+      </c>
+      <c r="G40" t="n">
+        <v>79520.046875</v>
+      </c>
+      <c r="H40" t="n">
+        <v>188.171875</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2366345121699854</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.5624873567726952</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="n">
+        <v>79465.6953125</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4403,24 @@
           <t>79816.695312,79725.515625,79817.671875,79821.593750,79839.906250,79776.781250,79795.851562,79739.421875,79774.015625,79658.265625,79731.007812,79716.593750,79740.125000,79573.312500,79623.671875,79573.453125,79608.593750,79497.273438,79500.984375,79476.054688,79511.898438,79373.054688,79353.031250,79331.875000</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>79988.742188,79619.492188,79476.343750,79276.062500,79533.000000,80221.312500,80320.570312,80384.789062,80445.132812,80174.531250,79932.531250,80111.046875,80202.156250,80322.046875,80269.390625,80597.593750,80509.109375,79937.492188,79824.703125,79649.226562,79691.539062,79909.078125,79677.000000,79520.046875</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>172.046876,106.023438,341.328125,545.531250,306.906250,444.531250,524.718751,645.367188,671.117188,516.265625,201.523438,394.453125,462.031250,748.734375,645.718750,1024.140625,900.515625,440.218749,323.718750,173.171874,179.640624,536.023437,323.968750,188.171875</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.215089,0.133163,0.429471,0.688141,0.385885,0.554131,0.653281,0.802847,0.834255,0.643927,0.252117,0.492383,0.576083,0.932165,0.804440,1.270684,1.118526,0.550704,0.405537,0.217418,0.225420,0.670792,0.406603,0.236635</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.5624873567726952</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>79701.656250,79802.664062,79794.648438,79797.796875,79884.421875,79756.531250,79676.296875,79569.906250,79763.781250,79665.570312,79775.218750,79503.015625,79490.101562,79627.875000,79471.828125,79466.812500,79435.671875,79249.984375,79409.625000,79338.890625,79254.140625,79260.437500,79318.625000,79173.054688</t>
@@ -4378,6 +4434,49 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>79395.859375,79267.398438,79397.750000,79330.218750,79301.890625,79133.523438,79199.546875,79085.906250,79192.546875,78969.820312,78997.187500,78967.781250,78950.250000,78660.351562,78724.960938,78684.109375,78648.960938,78562.265625,78427.296875,78416.929688,78391.773438,78174.109375,78147.921875,78156.031250</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>79666.429688,79589.632812,79599.515625,79652.890625,79616.218750,79609.578125,79599.031250,79573.515625,79596.976562,79571.218750,79534.929688,79547.375000,79579.406250,79493.851562,79498.671875,79520.078125,79548.796875,79452.859375,79452.312500,79484.906250,79491.671875,79413.328125,79400.093750,79465.695312</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>79558.218750,79626.093750,79502.710938,79578.664062,79583.648438,79525.656250,79495.437500,79399.140625,79498.281250,79506.898438,79549.664062,79339.273438,79350.820312,79383.281250,79298.078125,79310.710938,79299.750000,79254.835938,79262.625000,79255.382812,79257.187500,79193.289062,79268.054688,79197.625000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>79249.375000,79207.312500,79185.406250,79303.046875,79097.429688,79052.789062,79047.687500,78975.726562,78899.140625,78823.164062,78688.710938,78704.382812,78739.226562,78546.718750,78494.843750,78484.156250,78450.960938,78376.945312,78206.781250,78172.726562,78170.640625,78044.562500,78014.117188,78070.054688</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>79456.054688,79349.085938,79374.617188,79393.453125,79291.203125,79224.109375,79199.578125,79123.406250,79194.718750,79081.929688,78993.687500,79001.320312,79058.828125,78865.117188,78847.656250,78886.664062,78916.117188,78750.609375,78713.210938,78727.101562,78717.375000,78553.945312,78571.609375,78599.343750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,44 @@
       </c>
       <c r="F41" t="n">
         <v>79465.6953125</v>
+      </c>
+      <c r="G41" t="n">
+        <v>77469.2109375</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1996.484375</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.577132709678311</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.161712348291232</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:44</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="n">
+        <v>77337.3984375</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,6 +4502,24 @@
           <t>79666.429688,79589.632812,79599.515625,79652.890625,79616.218750,79609.578125,79599.031250,79573.515625,79596.976562,79571.218750,79534.929688,79547.375000,79579.406250,79493.851562,79498.671875,79520.078125,79548.796875,79452.859375,79452.312500,79484.906250,79491.671875,79413.328125,79400.093750,79465.695312</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>79417.593750,79490.156250,79546.460938,78324.226562,77788.492188,77900.976562,77543.546875,77533.640625,77399.992188,77365.476562,77749.343750,77838.671875,77734.476562,77792.039062,77668.093750,77501.046875,77640.421875,77635.429688,77469.210938,77469.210938,77469.210938,77469.210938,77469.210938,77469.210938</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>248.835938,99.476562,53.054688,1328.664062,1827.726562,1708.601562,2055.484375,2039.875000,2196.984374,2205.742188,1785.585938,1708.703125,1844.929688,1701.812499,1830.578125,2019.031250,1908.375000,1817.429688,1983.101562,2015.695312,2022.460938,1944.117188,1930.882812,1996.484374</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.313326,0.125143,0.066696,1.696364,2.349610,2.193299,2.650748,2.630955,2.838481,2.851068,2.296593,2.195185,2.373374,2.187644,2.356924,2.605166,2.457966,2.340980,2.559858,2.601931,2.610664,2.509535,2.492452,2.577133</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2.161712348291232</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>79558.218750,79626.093750,79502.710938,79578.664062,79583.648438,79525.656250,79495.437500,79399.140625,79498.281250,79506.898438,79549.664062,79339.273438,79350.820312,79383.281250,79298.078125,79310.710938,79299.750000,79254.835938,79262.625000,79255.382812,79257.187500,79193.289062,79268.054688,79197.625000</t>
@@ -4477,6 +4533,49 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>79456.054688,79349.085938,79374.617188,79393.453125,79291.203125,79224.109375,79199.578125,79123.406250,79194.718750,79081.929688,78993.687500,79001.320312,79058.828125,78865.117188,78847.656250,78886.664062,78916.117188,78750.609375,78713.210938,78727.101562,78717.375000,78553.945312,78571.609375,78599.343750</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:44</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>77503.265625,77444.218750,77367.085938,77429.234375,77372.234375,77399.171875,77368.968750,77321.828125,77363.960938,77371.679688,77277.054688,77309.351562,77320.632812,77300.812500,77314.851562,77316.921875,77319.875000,77301.460938,77322.234375,77314.671875,77349.562500,77335.640625,77249.187500,77337.398438</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>77458.695312,77544.343750,77300.953125,77443.453125,77457.265625,77313.390625,77312.773438,77170.328125,77412.421875,77264.500000,77319.000000,77231.992188,77172.562500,77280.718750,77257.609375,77076.734375,77170.984375,77269.203125,77337.289062,77150.617188,77169.640625,77055.437500,77193.875000,77051.593750</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>77046.945312,77019.921875,76847.843750,76938.593750,76752.070312,76691.046875,76711.062500,76595.765625,76468.648438,76413.882812,76196.304688,76202.796875,76135.046875,76010.125000,75961.492188,75885.398438,75816.351562,75768.171875,75647.625000,75564.890625,75557.703125,75480.078125,75343.296875,75385.546875</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>77273.898438,77185.187500,77090.195312,77103.531250,76961.585938,76978.421875,76900.703125,76796.023438,76884.164062,76796.789062,76595.265625,76632.562500,76644.062500,76485.812500,76521.257812,76493.585938,76426.156250,76350.093750,76321.984375,76342.015625,76317.828125,76198.921875,76126.046875,76229.656250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,44 @@
       </c>
       <c r="F42" t="n">
         <v>77337.3984375</v>
+      </c>
+      <c r="G42" t="n">
+        <v>78213.390625</v>
+      </c>
+      <c r="H42" t="n">
+        <v>875.9921875</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.120002828799496</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.8089294616326967</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:28</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="n">
+        <v>78178.28125</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,6 +4601,24 @@
           <t>77503.265625,77444.218750,77367.085938,77429.234375,77372.234375,77399.171875,77368.968750,77321.828125,77363.960938,77371.679688,77277.054688,77309.351562,77320.632812,77300.812500,77314.851562,77316.921875,77319.875000,77301.460938,77322.234375,77314.671875,77349.562500,77335.640625,77249.187500,77337.398438</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>77619.000000,77641.781250,77642.406250,77628.460938,77575.406250,77584.617188,77692.757812,78001.562500,77855.578125,78018.257812,78096.406250,78153.000000,78193.601562,78119.671875,78164.218750,78221.859375,78233.929688,78175.921875,78076.906250,78097.648438,78135.101562,78116.148438,78213.390625,78213.390625</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>115.734375,197.562500,275.320312,199.226562,203.171875,185.445312,323.789062,679.734375,491.617187,646.578124,819.351562,843.648438,872.968751,818.859375,849.367188,904.937500,914.054688,874.460937,754.671875,782.976562,785.539062,780.507812,964.203125,875.992187</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.149106,0.254454,0.354600,0.256641,0.261902,0.239023,0.416756,0.871437,0.631448,0.828752,1.049154,1.079483,1.116420,1.048211,1.086645,1.156886,1.168361,1.118581,0.966575,1.002561,1.005360,0.999163,1.232785,1.120003</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.8089294616326967</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>77458.695312,77544.343750,77300.953125,77443.453125,77457.265625,77313.390625,77312.773438,77170.328125,77412.421875,77264.500000,77319.000000,77231.992188,77172.562500,77280.718750,77257.609375,77076.734375,77170.984375,77269.203125,77337.289062,77150.617188,77169.640625,77055.437500,77193.875000,77051.593750</t>
@@ -4576,6 +4632,49 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>77273.898438,77185.187500,77090.195312,77103.531250,76961.585938,76978.421875,76900.703125,76796.023438,76884.164062,76796.789062,76595.265625,76632.562500,76644.062500,76485.812500,76521.257812,76493.585938,76426.156250,76350.093750,76321.984375,76342.015625,76317.828125,76198.921875,76126.046875,76229.656250</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:28</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>78300.085938,78253.437500,78250.609375,78360.140625,78295.234375,78315.726562,78322.500000,78357.882812,78390.187500,78380.468750,78355.117188,78402.867188,78372.765625,78291.757812,78350.101562,78326.945312,78300.890625,78233.937500,78262.539062,78225.546875,78235.843750,78186.468750,78140.492188,78178.281250</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>78209.101562,78204.468750,78146.968750,78277.906250,78414.695312,78184.226562,78254.250000,78264.328125,78238.859375,78284.781250,78288.898438,78244.343750,78296.539062,78305.742188,78242.828125,78131.179688,78132.148438,78076.671875,78166.531250,78083.039062,78057.250000,77978.585938,78053.296875,77913.218750</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>77919.203125,77863.304688,77762.828125,77957.101562,77713.656250,77666.250000,77689.132812,77704.546875,77646.078125,77585.132812,77452.539062,77408.335938,77286.687500,77255.289062,77282.203125,77262.890625,77136.601562,77051.984375,76907.398438,76848.953125,76857.242188,76792.734375,76754.304688,76772.312500</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>78145.125000,78068.664062,78048.312500,78140.132812,77943.757812,77932.085938,77941.312500,77972.390625,78038.828125,77961.437500,77833.515625,77804.070312,77782.140625,77650.171875,77689.890625,77693.453125,77664.960938,77480.710938,77486.015625,77454.359375,77422.187500,77340.976562,77331.429688,77449.031250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,6 +2051,44 @@
       </c>
       <c r="F43" t="n">
         <v>78178.28125</v>
+      </c>
+      <c r="G43" t="n">
+        <v>77689.7265625</v>
+      </c>
+      <c r="H43" t="n">
+        <v>488.5546875</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6288536581564185</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5313840102939447</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>77837.0546875</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4700,24 @@
           <t>78300.085938,78253.437500,78250.609375,78360.140625,78295.234375,78315.726562,78322.500000,78357.882812,78390.187500,78380.468750,78355.117188,78402.867188,78372.765625,78291.757812,78350.101562,78326.945312,78300.890625,78233.937500,78262.539062,78225.546875,78235.843750,78186.468750,78140.492188,78178.281250</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>78275.093750,78103.023438,78065.203125,77992.140625,78144.937500,78163.406250,78746.820312,78849.773438,78778.398438,78821.687500,79331.679688,79011.742188,79028.046875,78856.109375,78582.296875,78646.773438,78425.960938,77683.500000,77921.523438,77632.203125,77453.578125,77744.828125,77603.898438,77689.726562</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>24.992188,150.414062,185.406250,368.000000,150.296875,152.320312,424.320312,491.890626,388.210938,441.218750,976.562499,608.874999,655.281250,564.351563,232.195313,319.828126,125.070312,550.437500,341.015624,593.343750,782.265625,441.640625,536.593751,488.554688</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.031929,0.192584,0.237502,0.471842,0.192331,0.194874,0.538841,0.623833,0.492789,0.559768,1.230987,0.770613,0.829176,0.715673,0.295480,0.406664,0.159476,0.708564,0.437640,0.764301,1.009980,0.568064,0.691452,0.628854</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5313840102939447</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>78209.101562,78204.468750,78146.968750,78277.906250,78414.695312,78184.226562,78254.250000,78264.328125,78238.859375,78284.781250,78288.898438,78244.343750,78296.539062,78305.742188,78242.828125,78131.179688,78132.148438,78076.671875,78166.531250,78083.039062,78057.250000,77978.585938,78053.296875,77913.218750</t>
@@ -4675,6 +4731,49 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>78145.125000,78068.664062,78048.312500,78140.132812,77943.757812,77932.085938,77941.312500,77972.390625,78038.828125,77961.437500,77833.515625,77804.070312,77782.140625,77650.171875,77689.890625,77693.453125,77664.960938,77480.710938,77486.015625,77454.359375,77422.187500,77340.976562,77331.429688,77449.031250</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>77767.273438,77733.109375,77693.265625,77754.523438,77705.312500,77739.710938,77743.921875,77747.656250,77752.875000,77749.828125,77734.875000,77765.804688,77762.804688,77743.687500,77768.968750,77765.664062,77796.562500,77723.718750,77782.906250,77785.960938,77787.734375,77796.164062,77768.593750,77837.054688</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>77702.546875,77745.500000,77646.187500,77679.906250,77745.585938,77704.312500,77708.812500,77675.570312,77655.148438,77665.578125,77729.312500,77647.828125,77674.046875,77672.609375,77646.312500,77560.851562,77600.843750,77605.625000,77657.031250,77620.656250,77671.804688,77566.765625,77749.296875,77632.406250</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>77426.171875,77363.492188,77215.968750,77335.390625,77111.257812,77064.984375,77016.359375,76966.812500,76885.125000,76855.859375,76738.203125,76685.773438,76615.820312,76619.867188,76607.312500,76587.781250,76544.335938,76423.445312,76309.804688,76311.843750,76286.117188,76294.046875,76267.187500,76308.343750</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>77612.367188,77521.523438,77437.375000,77486.328125,77313.992188,77293.929688,77253.851562,77244.390625,77250.039062,77220.945312,77111.773438,77090.390625,77069.140625,77001.156250,77024.875000,77019.476562,77039.406250,76893.421875,76915.234375,76923.804688,76884.953125,76850.109375,76858.804688,76974.664062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,44 @@
       </c>
       <c r="F44" t="n">
         <v>77837.0546875</v>
+      </c>
+      <c r="G44" t="n">
+        <v>78741.1484375</v>
+      </c>
+      <c r="H44" t="n">
+        <v>904.09375</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.148184612417249</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.9906148823656638</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:48</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="n">
+        <v>78799.90625</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4799,24 @@
           <t>77767.273438,77733.109375,77693.265625,77754.523438,77705.312500,77739.710938,77743.921875,77747.656250,77752.875000,77749.828125,77734.875000,77765.804688,77762.804688,77743.687500,77768.968750,77765.664062,77796.562500,77723.718750,77782.906250,77785.960938,77787.734375,77796.164062,77768.593750,77837.054688</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>78083.523438,78178.976562,78459.796875,78493.312500,78675.617188,78286.968750,77913.421875,77837.398438,78548.523438,78559.078125,78616.601562,78888.593750,79003.953125,78878.859375,78842.687500,78944.773438,78568.328125,78562.726562,78628.031250,78377.171875,78422.460938,78653.929688,78741.148438,78741.148438</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>316.249999,445.867188,766.531250,738.789062,970.304688,547.257812,169.500000,89.742188,795.648438,809.250000,881.726562,1122.789062,1241.148437,1135.171875,1073.718750,1179.109376,771.765625,839.007812,845.125000,591.210937,634.726562,857.765626,972.554688,904.093749</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.405015,0.570316,0.976973,0.941213,1.233298,0.699041,0.217549,0.115294,1.012939,1.030116,1.121553,1.423259,1.570995,1.439133,1.361850,1.493588,0.982286,1.067946,1.074839,0.754315,0.809368,1.090557,1.235129,1.148185</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.9906148823656638</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>77702.546875,77745.500000,77646.187500,77679.906250,77745.585938,77704.312500,77708.812500,77675.570312,77655.148438,77665.578125,77729.312500,77647.828125,77674.046875,77672.609375,77646.312500,77560.851562,77600.843750,77605.625000,77657.031250,77620.656250,77671.804688,77566.765625,77749.296875,77632.406250</t>
@@ -4774,6 +4830,49 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>77612.367188,77521.523438,77437.375000,77486.328125,77313.992188,77293.929688,77253.851562,77244.390625,77250.039062,77220.945312,77111.773438,77090.390625,77069.140625,77001.156250,77024.875000,77019.476562,77039.406250,76893.421875,76915.234375,76923.804688,76884.953125,76850.109375,76858.804688,76974.664062</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:48</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>78804.187500,78812.781250,78790.695312,78876.117188,78848.703125,78880.906250,78855.437500,78886.257812,78860.781250,78845.039062,78848.179688,78858.453125,78868.312500,78865.703125,78882.921875,78868.328125,78880.656250,78834.710938,78808.656250,78829.914062,78773.867188,78794.750000,78756.406250,78799.906250</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>78732.562500,78821.156250,78782.429688,78791.867188,78913.382812,78788.578125,78812.937500,78764.093750,78730.156250,78748.226562,78812.015625,78743.843750,78756.296875,78846.929688,78761.265625,78660.093750,78728.640625,78723.742188,78732.734375,78658.812500,78631.046875,78577.125000,78680.250000,78572.000000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>78436.671875,78418.265625,78326.039062,78465.789062,78302.921875,78282.203125,78230.828125,78193.773438,78120.171875,78042.187500,77955.789062,77900.046875,77863.726562,77852.156250,77851.851562,77808.109375,77752.039062,77688.921875,77549.960938,77517.078125,77498.820312,77514.851562,77515.140625,77514.851562</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>78628.039062,78580.617188,78549.992188,78602.156250,78487.609375,78454.617188,78447.890625,78449.062500,78451.070312,78366.937500,78271.921875,78253.984375,78268.484375,78191.976562,78246.171875,78222.195312,78247.664062,78124.937500,78084.492188,78089.671875,78034.312500,78008.187500,77998.820312,78068.187500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,44 @@
       </c>
       <c r="F45" t="n">
         <v>78799.90625</v>
+      </c>
+      <c r="G45" t="n">
+        <v>77327.390625</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1472.515625</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.904261365989938</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.506011557915166</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:09:59</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="n">
+        <v>78038.5234375</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4898,24 @@
           <t>78804.187500,78812.781250,78790.695312,78876.117188,78848.703125,78880.906250,78855.437500,78886.257812,78860.781250,78845.039062,78848.179688,78858.453125,78868.312500,78865.703125,78882.921875,78868.328125,78880.656250,78834.710938,78808.656250,78829.914062,78773.867188,78794.750000,78756.406250,78799.906250</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>79136.062500,78708.718750,78609.921875,77858.359375,77893.242188,77989.078125,78061.710938,77968.976562,78041.093750,78139.750000,77881.429688,77565.437500,77238.203125,77126.929688,77267.890625,77403.812500,77165.929688,77224.976562,77258.843750,77171.562500,76965.726562,77277.156250,77512.453125,77327.390625</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>331.875000,104.062500,180.773437,1017.757813,955.460938,891.828125,793.726562,917.281249,819.687500,705.289062,966.750001,1293.015625,1630.109375,1738.773438,1615.031250,1464.515625,1714.726562,1609.734376,1549.812500,1658.351562,1808.140626,1517.593750,1243.953125,1472.515625</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.419373,0.132212,0.229963,1.307191,1.226629,1.143530,1.016794,1.176470,1.050328,0.902600,1.241310,1.667000,2.110496,2.254431,2.090171,1.892046,2.222129,2.084474,2.006000,2.148915,2.349280,1.963832,1.604843,1.904261</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1.506011557915166</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>78732.562500,78821.156250,78782.429688,78791.867188,78913.382812,78788.578125,78812.937500,78764.093750,78730.156250,78748.226562,78812.015625,78743.843750,78756.296875,78846.929688,78761.265625,78660.093750,78728.640625,78723.742188,78732.734375,78658.812500,78631.046875,78577.125000,78680.250000,78572.000000</t>
@@ -4873,6 +4929,49 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>78628.039062,78580.617188,78549.992188,78602.156250,78487.609375,78454.617188,78447.890625,78449.062500,78451.070312,78366.937500,78271.921875,78253.984375,78268.484375,78191.976562,78246.171875,78222.195312,78247.664062,78124.937500,78084.492188,78089.671875,78034.312500,78008.187500,77998.820312,78068.187500</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:09:59</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>77287.515625,77299.250000,77302.484375,77381.562500,77360.351562,77394.125000,77433.093750,77440.421875,77475.007812,77508.250000,77547.203125,77607.523438,77627.445312,77680.421875,77739.125000,77720.304688,77769.710938,77787.789062,77831.625000,77900.101562,77915.593750,77959.476562,77977.148438,78038.523438</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>77246.140625,77309.875000,77270.742188,77363.000000,77424.328125,77383.015625,77534.609375,77361.507812,77443.281250,77450.742188,77578.195312,77587.523438,77652.250000,77781.164062,77705.289062,77544.218750,77724.421875,77811.953125,77869.843750,77765.046875,77858.859375,77750.171875,78070.875000,77955.601562</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>76923.718750,76901.882812,76808.671875,76916.351562,76760.289062,76715.046875,76737.812500,76659.140625,76591.921875,76568.218750,76520.953125,76497.781250,76395.500000,76415.914062,76481.398438,76403.726562,76416.390625,76398.828125,76316.812500,76318.789062,76331.328125,76379.351562,76378.500000,76404.921875</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>77098.726562,77041.062500,77011.859375,77056.843750,76967.445312,76914.460938,76948.562500,76906.210938,76977.953125,76919.250000,76865.593750,76889.273438,76861.562500,76856.835938,76979.906250,76921.835938,76944.132812,76893.320312,76916.656250,76980.703125,76960.835938,76961.703125,76968.968750,77053.601562</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,44 @@
       </c>
       <c r="F46" t="n">
         <v>78038.5234375</v>
+      </c>
+      <c r="G46" t="n">
+        <v>77724.0234375</v>
+      </c>
+      <c r="H46" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.4046367983676218</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.6090151924760555</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:06:57</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="n">
+        <v>77605.3125</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,6 +4997,24 @@
           <t>77287.515625,77299.250000,77302.484375,77381.562500,77360.351562,77394.125000,77433.093750,77440.421875,77475.007812,77508.250000,77547.203125,77607.523438,77627.445312,77680.421875,77739.125000,77720.304688,77769.710938,77787.789062,77831.625000,77900.101562,77915.593750,77959.476562,77977.148438,78038.523438</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>77605.398438,77573.687500,77436.242188,76802.007812,76711.070312,76638.812500,76778.492188,76567.937500,77112.640625,77025.328125,77253.039062,77139.937500,77351.460938,77348.281250,77324.640625,77378.109375,77264.906250,77003.601562,77316.101562,77027.843750,77323.523438,77786.976562,77673.960938,77724.023438</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>317.882812,274.437500,133.757812,579.554688,649.281249,755.312500,654.601562,872.484375,362.367187,482.921875,294.164062,467.585938,275.984374,332.140625,414.484375,342.195313,504.804688,784.187499,515.523438,872.257812,592.070312,172.499999,303.187501,314.500001</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.409614,0.353777,0.172733,0.754609,0.846398,0.985548,0.852585,1.139491,0.469919,0.626965,0.380780,0.606153,0.356793,0.429409,0.536031,0.442238,0.653343,1.018378,0.666774,1.132393,0.765705,0.221759,0.390334,0.404637</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.6090151924760555</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>77246.140625,77309.875000,77270.742188,77363.000000,77424.328125,77383.015625,77534.609375,77361.507812,77443.281250,77450.742188,77578.195312,77587.523438,77652.250000,77781.164062,77705.289062,77544.218750,77724.421875,77811.953125,77869.843750,77765.046875,77858.859375,77750.171875,78070.875000,77955.601562</t>
@@ -4972,6 +5028,49 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>77098.726562,77041.062500,77011.859375,77056.843750,76967.445312,76914.460938,76948.562500,76906.210938,76977.953125,76919.250000,76865.593750,76889.273438,76861.562500,76856.835938,76979.906250,76921.835938,76944.132812,76893.320312,76916.656250,76980.703125,76960.835938,76961.703125,76968.968750,77053.601562</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:06:57</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>77727.640625,77743.742188,77724.203125,77790.515625,77732.343750,77735.164062,77727.882812,77716.945312,77695.078125,77667.820312,77647.742188,77678.750000,77649.390625,77650.023438,77660.984375,77652.023438,77637.804688,77606.195312,77632.320312,77587.218750,77633.578125,77616.421875,77547.640625,77605.312500</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>77623.523438,77747.789062,77703.132812,77735.914062,77736.851562,77692.484375,77728.976562,77647.835938,77537.265625,77642.640625,77633.656250,77556.125000,77621.234375,77694.640625,77586.640625,77531.906250,77459.718750,77630.359375,77635.578125,77470.156250,77530.625000,77529.156250,77582.515625,77526.445312</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>77243.859375,77238.304688,77108.750000,77207.281250,77056.242188,76982.617188,76965.343750,76891.109375,76796.765625,76725.382812,76656.015625,76578.531250,76461.734375,76503.359375,76541.320312,76507.140625,76470.476562,76431.273438,76325.578125,76238.148438,76327.335938,76343.828125,76275.562500,76289.453125</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>77468.906250,77409.695312,77370.140625,77415.125000,77296.796875,77233.515625,77233.453125,77206.398438,77205.187500,77120.867188,76997.867188,76996.984375,76962.531250,76927.617188,76974.773438,76965.695312,76923.468750,76842.539062,76850.781250,76824.000000,76866.718750,76801.046875,76759.585938,76850.968750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,44 @@
       </c>
       <c r="F47" t="n">
         <v>77605.3125</v>
+      </c>
+      <c r="G47" t="n">
+        <v>80872.6484375</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3267.3359375</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.040100084053836</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.835794171448488</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:36</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="n">
+        <v>79575.1015625</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5096,24 @@
           <t>77727.640625,77743.742188,77724.203125,77790.515625,77732.343750,77735.164062,77727.882812,77716.945312,77695.078125,77667.820312,77647.742188,77678.750000,77649.390625,77650.023438,77660.984375,77652.023438,77637.804688,77606.195312,77632.320312,77587.218750,77633.578125,77616.421875,77547.640625,77605.312500</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>77781.093750,77797.992188,77621.710938,77803.132812,77572.937500,77708.609375,77910.273438,78621.289062,78815.742188,80550.007812,81358.210938,80973.953125,81052.492188,81268.421875,81760.179688,81482.851562,81626.632812,81155.570312,81270.828125,80977.312500,80975.296875,80830.476562,80850.500000,80872.648438</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>53.453125,54.249999,102.492188,12.617188,159.406250,26.554687,182.390626,904.343751,1120.664062,2882.187501,3710.468749,3295.203125,3403.101562,3618.398437,4099.195312,3830.828124,3988.828124,3549.375001,3638.507813,3390.093750,3341.718750,3214.054688,3302.859375,3267.335938</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.068723,0.069732,0.132041,0.016217,0.205492,0.034172,0.234103,1.150253,1.421878,3.578134,4.560657,4.069461,4.198639,4.452404,5.013682,4.701392,4.886675,4.373545,4.477016,4.186474,4.126837,3.976291,4.085144,4.040100</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2.835794171448488</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>77623.523438,77747.789062,77703.132812,77735.914062,77736.851562,77692.484375,77728.976562,77647.835938,77537.265625,77642.640625,77633.656250,77556.125000,77621.234375,77694.640625,77586.640625,77531.906250,77459.718750,77630.359375,77635.578125,77470.156250,77530.625000,77529.156250,77582.515625,77526.445312</t>
@@ -5071,6 +5127,49 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>77468.906250,77409.695312,77370.140625,77415.125000,77296.796875,77233.515625,77233.453125,77206.398438,77205.187500,77120.867188,76997.867188,76996.984375,76962.531250,76927.617188,76974.773438,76965.695312,76923.468750,76842.539062,76850.781250,76824.000000,76866.718750,76801.046875,76759.585938,76850.968750</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:36</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>80923.054688,80879.781250,80902.445312,80936.820312,80833.765625,80792.765625,80773.382812,80703.460938,80657.070312,80568.109375,80581.078125,80507.101562,80429.289062,80317.148438,80288.687500,80206.914062,80129.359375,79986.218750,79881.359375,79854.078125,79738.898438,79691.179688,79588.578125,79575.101562</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>80845.750000,80861.773438,80869.992188,80803.929688,80721.992188,80775.437500,80663.539062,80580.921875,80492.210938,80520.476562,80437.765625,80358.375000,80241.921875,80293.718750,80116.671875,80035.968750,79934.265625,79680.195312,79701.406250,79678.984375,79541.789062,79529.289062,79441.437500,79316.687500</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>80409.703125,80341.507812,80162.289062,80156.046875,79947.000000,79769.078125,79530.992188,79408.054688,79282.421875,79137.640625,79004.171875,78851.375000,78656.593750,78605.914062,78505.046875,78393.031250,78253.101562,78077.546875,77769.203125,77763.062500,77574.648438,77637.984375,77446.625000,77433.750000</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>80710.328125,80566.132812,80505.421875,80521.609375,80270.656250,80120.976562,80029.101562,79922.617188,79905.421875,79779.406250,79680.718750,79513.132812,79426.328125,79265.671875,79223.921875,79120.640625,79031.898438,78775.859375,78648.226562,78620.203125,78466.265625,78344.953125,78273.265625,78334.156250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,44 @@
       </c>
       <c r="F48" t="n">
         <v>79575.1015625</v>
+      </c>
+      <c r="G48" t="n">
+        <v>79584.1875</v>
+      </c>
+      <c r="H48" t="n">
+        <v>9.0859375</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.01141676228082369</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.6284275842786603</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:34</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="n">
+        <v>78631.859375</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5195,24 @@
           <t>80923.054688,80879.781250,80902.445312,80936.820312,80833.765625,80792.765625,80773.382812,80703.460938,80657.070312,80568.109375,80581.078125,80507.101562,80429.289062,80317.148438,80288.687500,80206.914062,80129.359375,79986.218750,79881.359375,79854.078125,79738.898438,79691.179688,79588.578125,79575.101562</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>80983.203125,80792.000000,80650.843750,81140.007812,81045.210938,81179.093750,81219.593750,79434.609375,79363.000000,78894.648438,79422.953125,79747.968750,79469.851562,79617.921875,79812.523438,79723.476562,79654.117188,79654.101562,79675.117188,79584.007812,79551.007812,79584.500000,79596.273438,79584.187500</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>60.148437,87.781250,251.601562,203.187501,211.445312,386.328125,446.210938,1268.851563,1294.070312,1673.460938,1158.125000,759.132812,959.437499,699.226563,476.164062,483.437499,475.242188,332.117188,206.242188,270.070312,187.890626,106.679688,7.695312,9.085938</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.074273,0.108651,0.311964,0.250416,0.260898,0.475896,0.549388,1.597354,1.630571,2.121134,1.458174,0.951915,1.207297,0.878228,0.596603,0.606393,0.596632,0.416949,0.258854,0.339352,0.236189,0.134046,0.009668,0.011417</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.6284275842786603</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>80845.750000,80861.773438,80869.992188,80803.929688,80721.992188,80775.437500,80663.539062,80580.921875,80492.210938,80520.476562,80437.765625,80358.375000,80241.921875,80293.718750,80116.671875,80035.968750,79934.265625,79680.195312,79701.406250,79678.984375,79541.789062,79529.289062,79441.437500,79316.687500</t>
@@ -5170,6 +5226,49 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>80710.328125,80566.132812,80505.421875,80521.609375,80270.656250,80120.976562,80029.101562,79922.617188,79905.421875,79779.406250,79680.718750,79513.132812,79426.328125,79265.671875,79223.921875,79120.640625,79031.898438,78775.859375,78648.226562,78620.203125,78466.265625,78344.953125,78273.265625,78334.156250</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:34</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>79641.750000,79598.195312,79600.765625,79636.398438,79539.609375,79478.148438,79443.359375,79420.492188,79365.367188,79236.718750,79220.929688,79196.789062,79102.765625,79015.148438,79030.812500,79015.921875,78953.875000,78868.101562,78852.203125,78797.062500,78771.937500,78744.242188,78618.492188,78631.859375</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>79560.218750,79638.984375,79444.671875,79543.679688,79532.703125,79392.312500,79309.062500,79226.828125,79236.843750,79208.414062,79006.039062,79112.687500,79010.640625,79019.609375,78814.398438,78917.710938,78854.585938,78731.953125,78783.734375,78692.929688,78554.250000,78564.921875,78552.734375,78462.703125</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>79147.320312,79043.765625,78903.140625,78938.000000,78634.929688,78454.343750,78316.640625,78254.554688,78039.453125,77815.734375,77726.640625,77706.812500,77485.960938,77418.781250,77411.117188,77380.359375,77238.593750,77170.187500,76913.500000,76874.429688,76831.164062,76924.765625,76780.007812,76764.132812</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>79403.156250,79253.765625,79226.992188,79168.734375,78997.734375,78830.617188,78719.343750,78652.414062,78622.820312,78407.382812,78296.648438,78198.468750,78156.312500,78031.148438,78042.390625,78023.156250,77907.265625,77757.351562,77732.804688,77705.015625,77690.531250,77567.851562,77537.125000,77549.375000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,44 @@
       </c>
       <c r="F49" t="n">
         <v>78631.859375</v>
+      </c>
+      <c r="G49" t="n">
+        <v>79975.1484375</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1343.2890625</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.679633096961078</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8132919974625579</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="n">
+        <v>79569.25</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5294,24 @@
           <t>79641.750000,79598.195312,79600.765625,79636.398438,79539.609375,79478.148438,79443.359375,79420.492188,79365.367188,79236.718750,79220.929688,79196.789062,79102.765625,79015.148438,79030.812500,79015.921875,78953.875000,78868.101562,78852.203125,78797.062500,78771.937500,78744.242188,78618.492188,78631.859375</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>79590.320312,79660.000000,79726.796875,79653.296875,79634.992188,79621.140625,79621.921875,79710.726562,79624.507812,79723.187500,79802.007812,80040.531250,80072.187500,80000.031250,79753.210938,79740.078125,79910.343750,79790.367188,79856.648438,79872.242188,79954.320312,79906.812500,80031.867188,79975.148438</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>51.429688,61.804688,126.031250,16.898437,95.382812,142.992187,178.562500,290.234374,259.140624,486.468750,581.078124,843.742188,969.421875,984.882812,722.398438,724.156250,956.468750,922.265626,1004.445312,1075.179688,1182.382812,1162.570312,1413.374999,1343.289062</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.064618,0.077586,0.158079,0.021215,0.119775,0.179591,0.224263,0.364110,0.325453,0.610197,0.728150,1.054144,1.210685,1.231103,0.905792,0.908146,1.196927,1.155861,1.257811,1.346124,1.478823,1.454908,1.766015,1.679633</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8132919974625579</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>79560.218750,79638.984375,79444.671875,79543.679688,79532.703125,79392.312500,79309.062500,79226.828125,79236.843750,79208.414062,79006.039062,79112.687500,79010.640625,79019.609375,78814.398438,78917.710938,78854.585938,78731.953125,78783.734375,78692.929688,78554.250000,78564.921875,78552.734375,78462.703125</t>
@@ -5269,6 +5325,49 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>79403.156250,79253.765625,79226.992188,79168.734375,78997.734375,78830.617188,78719.343750,78652.414062,78622.820312,78407.382812,78296.648438,78198.468750,78156.312500,78031.148438,78042.390625,78023.156250,77907.265625,77757.351562,77732.804688,77705.015625,77690.531250,77567.851562,77537.125000,77549.375000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>79936.859375,79907.578125,79895.429688,79936.671875,79847.765625,79875.648438,79868.281250,79821.960938,79815.359375,79796.929688,79760.312500,79777.242188,79717.984375,79700.781250,79697.867188,79700.851562,79683.578125,79628.875000,79616.179688,79600.375000,79603.703125,79601.742188,79555.093750,79569.250000</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>79845.562500,79802.359375,79843.187500,79824.671875,79919.906250,79771.109375,79762.953125,79771.445312,79707.914062,79711.140625,79645.898438,79664.726562,79588.859375,79676.625000,79513.945312,79572.179688,79532.062500,79422.695312,79491.390625,79447.062500,79460.796875,79419.125000,79444.093750,79369.914062</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>79649.171875,79609.609375,79502.359375,79570.828125,79410.000000,79365.078125,79251.500000,79131.828125,79055.195312,79002.640625,78865.554688,78832.078125,78665.000000,78708.359375,78633.890625,78636.390625,78542.937500,78494.968750,78290.914062,78272.046875,78291.914062,78343.125000,78266.296875,78202.781250</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>79802.687500,79728.734375,79710.617188,79738.398438,79583.984375,79535.015625,79476.718750,79433.109375,79447.843750,79391.054688,79226.617188,79248.984375,79196.492188,79100.992188,79095.234375,79083.695312,79074.421875,78965.820312,78921.937500,78903.414062,78926.656250,78880.281250,78826.539062,78857.890625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,44 @@
       </c>
       <c r="F50" t="n">
         <v>79569.25</v>
+      </c>
+      <c r="G50" t="n">
+        <v>79678.671875</v>
+      </c>
+      <c r="H50" t="n">
+        <v>109.421875</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.1373289393825002</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.227973800696645</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:44</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="n">
+        <v>79384.734375</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,6 +5393,24 @@
           <t>79936.859375,79907.578125,79895.429688,79936.671875,79847.765625,79875.648438,79868.281250,79821.960938,79815.359375,79796.929688,79760.312500,79777.242188,79717.984375,79700.781250,79697.867188,79700.851562,79683.578125,79628.875000,79616.179688,79600.375000,79603.703125,79601.742188,79555.093750,79569.250000</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>79989.687500,79771.828125,79810.062500,79845.000000,79890.476562,80000.617188,79922.992188,79920.460938,79832.992188,79538.492188,79707.648438,79679.218750,79741.187500,79941.882812,79829.976562,79892.257812,79945.156250,80048.742188,80339.320312,80148.007812,79923.046875,79863.429688,79587.312500,79678.671875</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>52.828125,135.750000,85.367188,91.671875,42.710938,124.968749,54.710938,98.499999,17.632812,258.437501,52.664062,98.023438,23.203125,241.101562,132.109374,191.406251,261.578125,419.867188,723.140624,547.632812,319.343750,261.687499,32.218750,109.421875</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.066044,0.170173,0.106963,0.114812,0.053462,0.156210,0.068455,0.123248,0.022087,0.324921,0.066072,0.123023,0.029098,0.301596,0.165488,0.239580,0.327197,0.524514,0.900108,0.683277,0.399564,0.327669,0.040482,0.137329</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.227973800696645</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>79845.562500,79802.359375,79843.187500,79824.671875,79919.906250,79771.109375,79762.953125,79771.445312,79707.914062,79711.140625,79645.898438,79664.726562,79588.859375,79676.625000,79513.945312,79572.179688,79532.062500,79422.695312,79491.390625,79447.062500,79460.796875,79419.125000,79444.093750,79369.914062</t>
@@ -5368,6 +5424,49 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>79802.687500,79728.734375,79710.617188,79738.398438,79583.984375,79535.015625,79476.718750,79433.109375,79447.843750,79391.054688,79226.617188,79248.984375,79196.492188,79100.992188,79095.234375,79083.695312,79074.421875,78965.820312,78921.937500,78903.414062,78926.656250,78880.281250,78826.539062,78857.890625</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:44</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>79698.015625,79679.000000,79666.375000,79734.671875,79643.125000,79640.468750,79620.835938,79617.859375,79614.101562,79566.343750,79533.179688,79542.906250,79465.421875,79461.609375,79465.203125,79508.742188,79503.500000,79423.632812,79471.484375,79426.031250,79443.140625,79413.453125,79360.398438,79384.734375</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>79565.484375,79653.539062,79587.382812,79647.226562,79623.312500,79556.906250,79495.828125,79543.750000,79465.507812,79521.437500,79456.328125,79450.429688,79319.640625,79373.226562,79285.257812,79334.023438,79216.500000,79243.117188,79269.140625,79177.648438,79211.507812,79191.906250,79164.546875,79189.164062</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>79427.312500,79408.343750,79265.468750,79348.914062,79160.734375,79079.304688,79005.117188,78927.953125,78857.679688,78742.500000,78593.570312,78560.226562,78424.835938,78494.078125,78399.390625,78436.234375,78365.609375,78261.015625,78098.242188,78054.640625,78074.281250,78100.179688,78002.109375,77972.789062</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>79600.578125,79495.609375,79457.585938,79495.179688,79336.914062,79286.593750,79209.460938,79234.921875,79255.125000,79147.820312,78960.125000,78976.867188,78935.757812,78895.882812,78858.757812,78903.921875,78884.703125,78715.890625,78722.804688,78719.343750,78724.859375,78629.210938,78576.734375,78635.335938</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,44 @@
       </c>
       <c r="F51" t="n">
         <v>79384.734375</v>
+      </c>
+      <c r="G51" t="n">
+        <v>78765.96875</v>
+      </c>
+      <c r="H51" t="n">
+        <v>618.765625</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.7855748298658486</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.3911162070583583</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:28</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="n">
+        <v>78370.0859375</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,6 +5492,24 @@
           <t>79698.015625,79679.000000,79666.375000,79734.671875,79643.125000,79640.468750,79620.835938,79617.859375,79614.101562,79566.343750,79533.179688,79542.906250,79465.421875,79461.609375,79465.203125,79508.742188,79503.500000,79423.632812,79471.484375,79426.031250,79443.140625,79413.453125,79360.398438,79384.734375</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>79740.210938,79645.507812,79379.937500,79417.851562,79301.312500,79350.648438,79409.132812,79597.757812,79344.843750,79184.132812,78800.000000,79010.976562,79170.000000,79195.023438,79352.210938,79220.539062,79139.492188,78929.929688,79091.968750,79293.382812,79413.921875,78914.562500,78875.218750,78765.968750</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>42.195312,33.492188,286.437500,316.820312,341.812500,289.820312,211.703126,20.101562,269.257812,382.210938,733.179688,531.929688,295.421875,266.585938,112.992188,288.203126,364.007812,493.703124,379.515625,132.648438,29.218750,498.890625,485.179688,618.765625</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.052916,0.042052,0.360844,0.398928,0.431030,0.365240,0.266598,0.025254,0.339351,0.482686,0.930431,0.673235,0.373149,0.336620,0.142393,0.363798,0.459957,0.625495,0.479841,0.167288,0.036793,0.632191,0.615123,0.785575</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.3911162070583583</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>79565.484375,79653.539062,79587.382812,79647.226562,79623.312500,79556.906250,79495.828125,79543.750000,79465.507812,79521.437500,79456.328125,79450.429688,79319.640625,79373.226562,79285.257812,79334.023438,79216.500000,79243.117188,79269.140625,79177.648438,79211.507812,79191.906250,79164.546875,79189.164062</t>
@@ -5467,6 +5523,49 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>79600.578125,79495.609375,79457.585938,79495.179688,79336.914062,79286.593750,79209.460938,79234.921875,79255.125000,79147.820312,78960.125000,78976.867188,78935.757812,78895.882812,78858.757812,78903.921875,78884.703125,78715.890625,78722.804688,78719.343750,78724.859375,78629.210938,78576.734375,78635.335938</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:28</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>78728.375000,78684.281250,78679.382812,78707.757812,78645.375000,78632.796875,78640.476562,78642.414062,78612.296875,78578.867188,78562.765625,78567.265625,78540.500000,78510.812500,78514.273438,78540.906250,78464.164062,78436.843750,78472.789062,78442.007812,78438.515625,78412.468750,78335.460938,78370.085938</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>78625.257812,78690.171875,78629.781250,78662.890625,78693.015625,78639.968750,78588.281250,78588.218750,78519.843750,78548.210938,78464.210938,78391.382812,78452.234375,78498.328125,78465.476562,78338.703125,78392.500000,78403.484375,78346.890625,78316.289062,78382.015625,78240.257812,78192.570312,78284.015625</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>78421.664062,78417.484375,78296.648438,78303.593750,78157.609375,78093.171875,78048.765625,77994.812500,77874.039062,77768.265625,77653.375000,77607.421875,77548.781250,77553.679688,77545.835938,77517.531250,77383.812500,77336.273438,77183.500000,77234.484375,77200.593750,77229.609375,77156.570312,77135.882812</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>78588.523438,78505.062500,78449.015625,78447.000000,78321.367188,78270.109375,78249.359375,78261.132812,78265.750000,78133.593750,77985.914062,77985.968750,77962.312500,77941.671875,77967.687500,77956.882812,77856.656250,77764.390625,77773.226562,77789.656250,77806.140625,77683.062500,77648.625000,77660.117188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,44 @@
       </c>
       <c r="F52" t="n">
         <v>78370.0859375</v>
+      </c>
+      <c r="G52" t="n">
+        <v>78851.7734375</v>
+      </c>
+      <c r="H52" t="n">
+        <v>481.6875</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.610877192739106</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.2781069284541488</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:06</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="n">
+        <v>78748.8359375</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5553,6 +5591,24 @@
           <t>78728.375000,78684.281250,78679.382812,78707.757812,78645.375000,78632.796875,78640.476562,78642.414062,78612.296875,78578.867188,78562.765625,78567.265625,78540.500000,78510.812500,78514.273438,78540.906250,78464.164062,78436.843750,78472.789062,78442.007812,78438.515625,78412.468750,78335.460938,78370.085938</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>78556.789062,78299.281250,78451.078125,78380.617188,78732.882812,78540.367188,78401.882812,78414.218750,77933.046875,78537.726562,78899.992188,78730.820312,78493.179688,78423.593750,78437.101562,78482.453125,78485.851562,78545.406250,78446.882812,78765.500000,78879.703125,78717.171875,78619.710938,78851.773438</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>171.585938,385.000000,228.304687,327.140624,87.507812,92.429688,238.593749,228.195312,679.250000,41.140626,337.226562,163.554688,47.320312,87.218750,77.171876,58.453125,21.687501,108.562500,25.906249,323.492188,441.187500,304.703125,284.249999,481.687499</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.218423,0.491703,0.291015,0.417374,0.111145,0.117684,0.304321,0.291013,0.871581,0.052383,0.427410,0.207739,0.060286,0.111215,0.098387,0.074479,0.027632,0.138216,0.033024,0.410703,0.559317,0.387086,0.361551,0.610877</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.2781069284541488</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>78625.257812,78690.171875,78629.781250,78662.890625,78693.015625,78639.968750,78588.281250,78588.218750,78519.843750,78548.210938,78464.210938,78391.382812,78452.234375,78498.328125,78465.476562,78338.703125,78392.500000,78403.484375,78346.890625,78316.289062,78382.015625,78240.257812,78192.570312,78284.015625</t>
@@ -5566,6 +5622,49 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>78588.523438,78505.062500,78449.015625,78447.000000,78321.367188,78270.109375,78249.359375,78261.132812,78265.750000,78133.593750,77985.914062,77985.968750,77962.312500,77941.671875,77967.687500,77956.882812,77856.656250,77764.390625,77773.226562,77789.656250,77806.140625,77683.062500,77648.625000,77660.117188</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:06</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>78834.375000,78796.218750,78813.734375,78844.625000,78807.859375,78813.359375,78842.289062,78828.203125,78796.898438,78799.390625,78794.437500,78815.671875,78804.781250,78796.343750,78817.078125,78821.203125,78783.054688,78763.125000,78768.031250,78777.476562,78759.843750,78763.593750,78692.125000,78748.835938</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>78776.726562,78813.609375,78797.367188,78776.593750,78938.515625,78784.820312,78765.828125,78848.296875,78743.828125,78771.265625,78771.703125,78765.445312,78861.953125,78833.875000,78819.820312,78701.531250,78738.562500,78793.210938,78733.031250,78693.492188,78777.156250,78625.015625,78647.335938,78745.421875</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>78489.359375,78454.937500,78313.562500,78356.335938,78275.906250,78201.968750,78240.335938,78166.976562,78058.070312,78013.171875,77935.015625,77887.289062,77810.929688,77852.250000,77876.398438,77806.890625,77716.078125,77660.460938,77500.687500,77550.054688,77539.476562,77595.828125,77501.101562,77494.859375</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>78665.398438,78563.734375,78523.679688,78525.773438,78414.875000,78386.078125,78422.937500,78422.406250,78423.992188,78324.781250,78195.625000,78245.140625,78266.187500,78204.554688,78243.859375,78201.562500,78114.718750,78031.507812,78043.820312,78071.382812,78078.726562,78029.796875,77984.898438,78030.929688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,44 @@
       </c>
       <c r="F53" t="n">
         <v>78748.8359375</v>
+      </c>
+      <c r="G53" t="n">
+        <v>78383.828125</v>
+      </c>
+      <c r="H53" t="n">
+        <v>365.0078125</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.4656672444192391</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5301215457585315</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:19:56</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="n">
+        <v>78313.609375</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5652,6 +5690,24 @@
           <t>78834.375000,78796.218750,78813.734375,78844.625000,78807.859375,78813.359375,78842.289062,78828.203125,78796.898438,78799.390625,78794.437500,78815.671875,78804.781250,78796.343750,78817.078125,78821.203125,78783.054688,78763.125000,78768.031250,78777.476562,78759.843750,78763.593750,78692.125000,78748.835938</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>78921.789062,79150.250000,79258.796875,79695.390625,78940.000000,78901.757812,79294.257812,79580.000000,79119.226562,78941.828125,78576.406250,78783.179688,78754.882812,78399.343750,78211.257812,78303.570312,78124.757812,77897.601562,78248.812500,78151.718750,78070.406250,78326.101562,78297.148438,78383.828125</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>87.414062,354.031250,445.062500,850.765625,132.140625,88.398438,451.968751,751.796875,322.328124,142.437500,218.031250,32.492188,49.898438,397.000000,605.820312,517.632812,658.296876,865.523438,519.218750,625.757812,689.437500,437.492188,394.976562,365.007813</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.110760,0.447290,0.561531,1.067522,0.167394,0.112036,0.569989,0.944706,0.407395,0.180433,0.277477,0.041243,0.063359,0.506382,0.774595,0.661059,0.842623,1.111104,0.663548,0.800696,0.883097,0.558552,0.504458,0.465667</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5301215457585315</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>78776.726562,78813.609375,78797.367188,78776.593750,78938.515625,78784.820312,78765.828125,78848.296875,78743.828125,78771.265625,78771.703125,78765.445312,78861.953125,78833.875000,78819.820312,78701.531250,78738.562500,78793.210938,78733.031250,78693.492188,78777.156250,78625.015625,78647.335938,78745.421875</t>
@@ -5665,6 +5721,49 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>78665.398438,78563.734375,78523.679688,78525.773438,78414.875000,78386.078125,78422.937500,78422.406250,78423.992188,78324.781250,78195.625000,78245.140625,78266.187500,78204.554688,78243.859375,78201.562500,78114.718750,78031.507812,78043.820312,78071.382812,78078.726562,78029.796875,77984.898438,78030.929688</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:19:56</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>78311.273438,78290.093750,78282.585938,78316.953125,78268.500000,78243.171875,78263.570312,78259.015625,78239.437500,78225.781250,78224.617188,78263.734375,78265.585938,78259.421875,78291.500000,78290.132812,78284.328125,78264.109375,78300.375000,78290.515625,78289.343750,78324.421875,78283.539062,78313.609375</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>78248.250000,78292.710938,78211.242188,78295.640625,78342.390625,78249.406250,78291.921875,78199.031250,78141.695312,78273.398438,78220.250000,78242.656250,78251.781250,78277.320312,78268.281250,78184.460938,78257.117188,78289.273438,78290.015625,78241.656250,78300.937500,78157.468750,78245.015625,78312.875000</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>77907.093750,77895.375000,77776.234375,77812.734375,77704.453125,77623.210938,77634.070312,77551.054688,77502.671875,77420.242188,77369.250000,77297.992188,77280.593750,77308.007812,77343.531250,77297.179688,77270.765625,77216.734375,77096.156250,77101.773438,77120.882812,77191.070312,77128.484375,77089.546875</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>78108.343750,78026.500000,77979.203125,77995.890625,77904.531250,77835.000000,77836.500000,77832.492188,77853.890625,77751.578125,77634.687500,77679.195312,77680.148438,77672.468750,77733.632812,77715.687500,77638.953125,77587.281250,77606.070312,77623.429688,77636.226562,77595.375000,77580.882812,77577.531250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,44 @@
       </c>
       <c r="F54" t="n">
         <v>78313.609375</v>
+      </c>
+      <c r="G54" t="n">
+        <v>76939.90625</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1373.703125</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.785423445326852</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.24488734310314</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:42</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="n">
+        <v>76753.84375</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5751,6 +5789,24 @@
           <t>78311.273438,78290.093750,78282.585938,78316.953125,78268.500000,78243.171875,78263.570312,78259.015625,78239.437500,78225.781250,78224.617188,78263.734375,78265.585938,78259.421875,78291.500000,78290.132812,78284.328125,78264.109375,78300.375000,78290.515625,78289.343750,78324.421875,78283.539062,78313.609375</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>78499.039062,78389.703125,78079.507812,78085.460938,77941.968750,77825.726562,77820.750000,76867.242188,77145.023438,77390.796875,77218.742188,77160.218750,77294.257812,77222.531250,77119.531250,77239.007812,77110.039062,76807.109375,76531.953125,76878.718750,76948.273438,76813.679688,76863.656250,76939.906250</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>187.765624,99.609375,203.078126,231.492188,326.531250,417.445312,442.820312,1391.773438,1094.414062,834.984375,1005.875001,1103.515625,971.328126,1036.890625,1171.968750,1051.124999,1174.289062,1457.000000,1768.421875,1411.796875,1341.070312,1510.742188,1419.882812,1373.703125</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.239195,0.127069,0.260091,0.296460,0.418941,0.536385,0.569026,1.810620,1.418645,1.078919,1.302631,1.430161,1.256663,1.342731,1.519678,1.360873,1.522874,1.896960,2.310697,1.836395,1.742821,1.966762,1.847275,1.785423</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1.24488734310314</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>78248.250000,78292.710938,78211.242188,78295.640625,78342.390625,78249.406250,78291.921875,78199.031250,78141.695312,78273.398438,78220.250000,78242.656250,78251.781250,78277.320312,78268.281250,78184.460938,78257.117188,78289.273438,78290.015625,78241.656250,78300.937500,78157.468750,78245.015625,78312.875000</t>
@@ -5764,6 +5820,49 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>78108.343750,78026.500000,77979.203125,77995.890625,77904.531250,77835.000000,77836.500000,77832.492188,77853.890625,77751.578125,77634.687500,77679.195312,77680.148438,77672.468750,77733.632812,77715.687500,77638.953125,77587.281250,77606.070312,77623.429688,77636.226562,77595.375000,77580.882812,77577.531250</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:42</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>76939.937500,76925.210938,76949.656250,76927.476562,76918.273438,76897.171875,76912.531250,76901.890625,76879.242188,76866.765625,76852.921875,76844.421875,76861.242188,76834.625000,76854.343750,76847.101562,76845.328125,76827.007812,76803.960938,76792.609375,76800.398438,76780.000000,76746.148438,76753.843750</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>76934.617188,76925.085938,76870.398438,76987.398438,76945.453125,76958.820312,76938.039062,76867.609375,76757.523438,76922.687500,76797.515625,76846.929688,76784.671875,76887.062500,76872.187500,76794.820312,76905.960938,76860.421875,76905.171875,76758.742188,76850.695312,76670.765625,76744.164062,76781.851562</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>76565.226562,76520.367188,76445.648438,76451.078125,76374.890625,76309.906250,76310.351562,76234.437500,76126.687500,76024.468750,76010.468750,75927.734375,75904.820312,75856.140625,75892.117188,75795.937500,75782.054688,75721.820312,75552.804688,75560.148438,75536.031250,75526.718750,75492.000000,75436.679688</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>76752.367188,76642.468750,76659.656250,76590.289062,76568.515625,76510.265625,76503.000000,76464.960938,76489.039062,76362.109375,76305.359375,76304.335938,76284.812500,76230.742188,76321.187500,76242.359375,76190.171875,76088.593750,76050.859375,76029.062500,76076.093750,75967.171875,75990.046875,75975.148438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,44 @@
       </c>
       <c r="F55" t="n">
         <v>76753.84375</v>
+      </c>
+      <c r="G55" t="n">
+        <v>77242.0078125</v>
+      </c>
+      <c r="H55" t="n">
+        <v>488.1640625</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.6319929741922127</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.7459748809357059</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:17:51</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="n">
+        <v>77200.921875</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5888,24 @@
           <t>76939.937500,76925.210938,76949.656250,76927.476562,76918.273438,76897.171875,76912.531250,76901.890625,76879.242188,76866.765625,76852.921875,76844.421875,76861.242188,76834.625000,76854.343750,76847.101562,76845.328125,76827.007812,76803.960938,76792.609375,76800.398438,76780.000000,76746.148438,76753.843750</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>77225.289062,77268.859375,77199.531250,77337.070312,77013.960938,76970.398438,77014.882812,78001.953125,79238.179688,78783.218750,77694.351562,77904.117188,77505.179688,77033.976562,77256.617188,77329.359375,77106.226562,77121.609375,77208.640625,77271.109375,77250.023438,77278.132812,77259.226562,77242.007812</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>285.351562,343.648437,249.875000,409.593751,95.687499,73.226562,102.351562,1100.062500,2358.937499,1916.453125,841.429688,1059.695312,643.937499,199.351562,402.273438,482.257813,260.898438,294.601563,404.679687,478.500000,449.624999,498.132812,513.078124,488.164062</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.369505,0.444744,0.323674,0.529621,0.124247,0.095136,0.132898,1.410301,2.977021,2.432565,1.083000,1.360256,0.830832,0.258784,0.520698,0.623641,0.338362,0.381996,0.524138,0.619248,0.582039,0.644597,0.664099,0.631993</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.7459748809357059</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>76934.617188,76925.085938,76870.398438,76987.398438,76945.453125,76958.820312,76938.039062,76867.609375,76757.523438,76922.687500,76797.515625,76846.929688,76784.671875,76887.062500,76872.187500,76794.820312,76905.960938,76860.421875,76905.171875,76758.742188,76850.695312,76670.765625,76744.164062,76781.851562</t>
@@ -5863,6 +5919,49 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>76752.367188,76642.468750,76659.656250,76590.289062,76568.515625,76510.265625,76503.000000,76464.960938,76489.039062,76362.109375,76305.359375,76304.335938,76284.812500,76230.742188,76321.187500,76242.359375,76190.171875,76088.593750,76050.859375,76029.062500,76076.093750,75967.171875,75990.046875,75975.148438</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:17:51</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>77194.359375,77203.578125,77234.007812,77228.101562,77235.054688,77203.328125,77216.500000,77218.890625,77197.593750,77173.281250,77203.734375,77170.046875,77189.382812,77149.773438,77185.726562,77159.625000,77172.273438,77169.953125,77183.320312,77178.671875,77166.007812,77193.640625,77188.062500,77200.921875</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>77205.851562,77243.406250,77206.921875,77277.820312,77271.640625,77268.773438,77213.359375,77179.062500,77131.843750,77272.726562,77192.460938,77217.007812,77152.968750,77210.546875,77276.828125,77239.226562,77246.968750,77226.593750,77285.609375,77250.429688,77294.617188,77184.468750,77281.875000,77234.203125</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>76908.992188,76875.109375,76802.757812,76823.812500,76734.523438,76657.148438,76668.953125,76605.375000,76491.242188,76434.101562,76427.187500,76324.945312,76271.562500,76255.726562,76249.390625,76147.312500,76128.648438,76094.140625,75924.695312,75893.101562,75898.171875,75928.203125,75918.421875,75857.796875</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>77072.000000,76998.757812,76982.468750,76941.257812,76894.976562,76830.164062,76827.937500,76828.164062,76834.898438,76728.343750,76693.171875,76666.468750,76654.640625,76578.000000,76653.625000,76575.023438,76524.359375,76441.593750,76424.515625,76402.960938,76427.718750,76385.695312,76404.898438,76411.585938</t>
         </is>
       </c>
     </row>
